--- a/journal/journal_list.xlsx
+++ b/journal/journal_list.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="486">
   <si>
     <t>Category</t>
   </si>
@@ -539,7 +539,7 @@
     <t>https://journals.sagepub.com/toc/THR/0/0</t>
   </si>
   <si>
-    <t>Springer</t>
+    <t>Springer Nature</t>
   </si>
   <si>
     <t>Annals of Operations Research</t>
@@ -692,6 +692,12 @@
     <t>http://link.springer.com/journal/10100/articles</t>
   </si>
   <si>
+    <t>International Journal of Computational Intelligence Systems</t>
+  </si>
+  <si>
+    <t>https://www.springer.com/journal/44196</t>
+  </si>
+  <si>
     <t>SCIENCE CHINA Information Sciences</t>
   </si>
   <si>
@@ -758,7 +764,7 @@
     <t>http://link.springer.com/journal/41066/articles</t>
   </si>
   <si>
-    <t>IEEE/INFORMS/ACM</t>
+    <t>IEEE</t>
   </si>
   <si>
     <t>IEEE Transactions on Systems, Man, and Cybernetics: Systems</t>
@@ -890,6 +896,9 @@
     <t>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=4601496&amp;sortType=newest</t>
   </si>
   <si>
+    <t>UTD/INFORMS</t>
+  </si>
+  <si>
     <t>Management Science</t>
   </si>
   <si>
@@ -941,6 +950,9 @@
     <t>Wiley|https://onlinelibrary.wiley.com/toc/19375956/0/0</t>
   </si>
   <si>
+    <t>ACM</t>
+  </si>
+  <si>
     <t>ACM Computing Surveys</t>
   </si>
   <si>
@@ -1125,12 +1137,6 @@
   </si>
   <si>
     <t>Others</t>
-  </si>
-  <si>
-    <t>International Journal of Computational Intelligence Systems</t>
-  </si>
-  <si>
-    <t>https://www.springer.com/journal/44196</t>
   </si>
   <si>
     <t>Technological and Economic Development of Economy</t>
@@ -1964,7 +1970,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2113,13 +2119,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -4473,16 +4485,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
+        <v>170</v>
+      </c>
+      <c r="B96" t="s">
+        <v>113</v>
+      </c>
+      <c r="C96" t="s">
         <v>243</v>
       </c>
-      <c r="B96" t="s">
-        <v>7</v>
-      </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>244</v>
-      </c>
-      <c r="D96" t="s">
-        <v>245</v>
       </c>
       <c r="E96" t="s">
         <v>10</v>
@@ -4493,10 +4505,10 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B97" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C97" t="s">
         <v>246</v>
@@ -4513,10 +4525,10 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B98" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C98" t="s">
         <v>248</v>
@@ -4533,10 +4545,10 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B99" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C99" t="s">
         <v>250</v>
@@ -4553,10 +4565,10 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B100" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C100" t="s">
         <v>252</v>
@@ -4573,10 +4585,10 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B101" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C101" t="s">
         <v>254</v>
@@ -4593,10 +4605,10 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B102" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C102" t="s">
         <v>256</v>
@@ -4613,10 +4625,10 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B103" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C103" t="s">
         <v>258</v>
@@ -4633,10 +4645,10 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B104" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C104" t="s">
         <v>260</v>
@@ -4653,10 +4665,10 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B105" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C105" t="s">
         <v>262</v>
@@ -4673,10 +4685,10 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B106" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C106" t="s">
         <v>264</v>
@@ -4693,10 +4705,10 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B107" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C107" t="s">
         <v>266</v>
@@ -4713,10 +4725,10 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B108" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C108" t="s">
         <v>268</v>
@@ -4733,10 +4745,10 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B109" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C109" t="s">
         <v>270</v>
@@ -4745,7 +4757,7 @@
         <v>271</v>
       </c>
       <c r="E109" t="s">
-        <v>272</v>
+        <v>10</v>
       </c>
       <c r="F109" t="s">
         <v>10</v>
@@ -4753,19 +4765,19 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B110" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C110" t="s">
+        <v>272</v>
+      </c>
+      <c r="D110" t="s">
         <v>273</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>274</v>
-      </c>
-      <c r="E110" t="s">
-        <v>10</v>
       </c>
       <c r="F110" t="s">
         <v>10</v>
@@ -4773,10 +4785,10 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B111" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C111" t="s">
         <v>275</v>
@@ -4793,10 +4805,10 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B112" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C112" t="s">
         <v>277</v>
@@ -4813,10 +4825,10 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B113" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C113" t="s">
         <v>279</v>
@@ -4833,10 +4845,10 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B114" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C114" t="s">
         <v>281</v>
@@ -4853,10 +4865,10 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B115" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C115" t="s">
         <v>283</v>
@@ -4873,10 +4885,10 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B116" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C116" t="s">
         <v>285</v>
@@ -4893,10 +4905,10 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B117" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C117" t="s">
         <v>287</v>
@@ -4913,16 +4925,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>243</v>
-      </c>
-      <c r="B118" t="s">
-        <v>74</v>
+        <v>289</v>
+      </c>
+      <c r="B118" s="2">
+        <v>1</v>
       </c>
       <c r="C118" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D118" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E118" t="s">
         <v>10</v>
@@ -4933,16 +4945,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>243</v>
-      </c>
-      <c r="B119" t="s">
-        <v>77</v>
+        <v>289</v>
+      </c>
+      <c r="B119" s="2">
+        <v>2</v>
       </c>
       <c r="C119" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D119" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E119" t="s">
         <v>10</v>
@@ -4953,16 +4965,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>243</v>
-      </c>
-      <c r="B120" t="s">
-        <v>80</v>
+        <v>289</v>
+      </c>
+      <c r="B120" s="2">
+        <v>3</v>
       </c>
       <c r="C120" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D120" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E120" t="s">
         <v>10</v>
@@ -4973,16 +4985,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>243</v>
-      </c>
-      <c r="B121" t="s">
-        <v>83</v>
+        <v>289</v>
+      </c>
+      <c r="B121" s="2">
+        <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D121" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E121" t="s">
         <v>10</v>
@@ -4993,16 +5005,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>243</v>
-      </c>
-      <c r="B122" t="s">
-        <v>86</v>
+        <v>289</v>
+      </c>
+      <c r="B122" s="2">
+        <v>5</v>
       </c>
       <c r="C122" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D122" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E122" t="s">
         <v>10</v>
@@ -5013,16 +5025,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>243</v>
-      </c>
-      <c r="B123" t="s">
-        <v>92</v>
+        <v>289</v>
+      </c>
+      <c r="B123" s="2">
+        <v>6</v>
       </c>
       <c r="C123" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D123" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E123" t="s">
         <v>10</v>
@@ -5033,19 +5045,19 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>243</v>
-      </c>
-      <c r="B124" t="s">
-        <v>89</v>
+        <v>289</v>
+      </c>
+      <c r="B124" s="2">
+        <v>7</v>
       </c>
       <c r="C124" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D124" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E124" t="s">
-        <v>303</v>
+        <v>10</v>
       </c>
       <c r="F124" t="s">
         <v>10</v>
@@ -5053,10 +5065,10 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>243</v>
-      </c>
-      <c r="B125" t="s">
-        <v>95</v>
+        <v>289</v>
+      </c>
+      <c r="B125" s="2">
+        <v>8</v>
       </c>
       <c r="C125" t="s">
         <v>304</v>
@@ -5065,7 +5077,7 @@
         <v>305</v>
       </c>
       <c r="E125" t="s">
-        <v>10</v>
+        <v>306</v>
       </c>
       <c r="F125" t="s">
         <v>10</v>
@@ -5073,16 +5085,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>243</v>
-      </c>
-      <c r="B126" t="s">
-        <v>98</v>
+        <v>307</v>
+      </c>
+      <c r="B126" s="2">
+        <v>1</v>
       </c>
       <c r="C126" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D126" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E126" t="s">
         <v>10</v>
@@ -5093,16 +5105,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>243</v>
-      </c>
-      <c r="B127" t="s">
-        <v>101</v>
+        <v>307</v>
+      </c>
+      <c r="B127" s="2">
+        <v>2</v>
       </c>
       <c r="C127" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D127" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E127" t="s">
         <v>10</v>
@@ -5113,16 +5125,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>243</v>
-      </c>
-      <c r="B128" t="s">
-        <v>104</v>
+        <v>307</v>
+      </c>
+      <c r="B128" s="2">
+        <v>3</v>
       </c>
       <c r="C128" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D128" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E128" t="s">
         <v>10</v>
@@ -5133,16 +5145,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>243</v>
-      </c>
-      <c r="B129" t="s">
-        <v>107</v>
+        <v>307</v>
+      </c>
+      <c r="B129" s="2">
+        <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D129" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E129" t="s">
         <v>10</v>
@@ -5153,16 +5165,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>243</v>
-      </c>
-      <c r="B130" t="s">
-        <v>110</v>
+        <v>307</v>
+      </c>
+      <c r="B130" s="2">
+        <v>5</v>
       </c>
       <c r="C130" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D130" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E130" t="s">
         <v>10</v>
@@ -5173,16 +5185,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>243</v>
-      </c>
-      <c r="B131" t="s">
-        <v>113</v>
+        <v>307</v>
+      </c>
+      <c r="B131" s="2">
+        <v>6</v>
       </c>
       <c r="C131" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D131" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E131" t="s">
         <v>10</v>
@@ -5193,16 +5205,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>243</v>
-      </c>
-      <c r="B132" t="s">
-        <v>116</v>
+        <v>307</v>
+      </c>
+      <c r="B132" s="2">
+        <v>7</v>
       </c>
       <c r="C132" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D132" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E132" t="s">
         <v>10</v>
@@ -5213,16 +5225,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>243</v>
-      </c>
-      <c r="B133" t="s">
-        <v>119</v>
+        <v>307</v>
+      </c>
+      <c r="B133" s="2">
+        <v>8</v>
       </c>
       <c r="C133" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D133" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E133" t="s">
         <v>10</v>
@@ -5233,16 +5245,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>243</v>
-      </c>
-      <c r="B134" t="s">
-        <v>122</v>
+        <v>307</v>
+      </c>
+      <c r="B134" s="2">
+        <v>9</v>
       </c>
       <c r="C134" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D134" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E134" t="s">
         <v>10</v>
@@ -5253,16 +5265,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>243</v>
-      </c>
-      <c r="B135" t="s">
-        <v>125</v>
+        <v>307</v>
+      </c>
+      <c r="B135" s="2">
+        <v>10</v>
       </c>
       <c r="C135" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D135" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E135" t="s">
         <v>10</v>
@@ -5271,38 +5283,38 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" ht="14.4" spans="1:6">
+    <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>326</v>
-      </c>
-      <c r="B136" t="s">
+        <v>307</v>
+      </c>
+      <c r="B136" s="2">
+        <v>11</v>
+      </c>
+      <c r="C136" t="s">
+        <v>328</v>
+      </c>
+      <c r="D136" t="s">
+        <v>329</v>
+      </c>
+      <c r="E136" t="s">
+        <v>10</v>
+      </c>
+      <c r="F136" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" ht="14.4" spans="1:6">
+      <c r="A137" t="s">
+        <v>330</v>
+      </c>
+      <c r="B137" t="s">
         <v>7</v>
       </c>
-      <c r="C136" t="s">
-        <v>327</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="F136" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137" t="s">
-        <v>326</v>
-      </c>
-      <c r="B137" t="s">
-        <v>11</v>
-      </c>
       <c r="C137" t="s">
-        <v>329</v>
-      </c>
-      <c r="D137" t="s">
-        <v>330</v>
-      </c>
-      <c r="E137" t="s">
-        <v>10</v>
+        <v>331</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>332</v>
       </c>
       <c r="F137" t="s">
         <v>10</v>
@@ -5310,16 +5322,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B138" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C138" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D138" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E138" t="s">
         <v>10</v>
@@ -5330,16 +5342,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B139" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C139" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D139" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E139" t="s">
         <v>10</v>
@@ -5350,16 +5362,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B140" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C140" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D140" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E140" t="s">
         <v>10</v>
@@ -5370,16 +5382,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B141" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C141" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D141" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E141" t="s">
         <v>10</v>
@@ -5390,16 +5402,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B142" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C142" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D142" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
@@ -5410,16 +5422,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B143" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C143" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D143" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E143" t="s">
         <v>10</v>
@@ -5430,16 +5442,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B144" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C144" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D144" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E144" t="s">
         <v>10</v>
@@ -5450,16 +5462,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B145" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C145" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D145" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E145" t="s">
         <v>10</v>
@@ -5470,16 +5482,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B146" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C146" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D146" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E146" t="s">
         <v>10</v>
@@ -5490,16 +5502,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B147" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C147" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D147" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E147" t="s">
         <v>10</v>
@@ -5510,16 +5522,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B148" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C148" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D148" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E148" t="s">
         <v>10</v>
@@ -5530,16 +5542,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B149" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C149" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D149" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E149" t="s">
         <v>10</v>
@@ -5550,16 +5562,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B150" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C150" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D150" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E150" t="s">
         <v>10</v>
@@ -5570,16 +5582,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B151" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C151" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D151" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E151" t="s">
         <v>10</v>
@@ -5590,16 +5602,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B152" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C152" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D152" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E152" t="s">
         <v>10</v>
@@ -5610,16 +5622,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B153" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C153" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D153" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E153" t="s">
         <v>10</v>
@@ -5630,16 +5642,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B154" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C154" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D154" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E154" t="s">
         <v>10</v>
@@ -5650,16 +5662,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>365</v>
+        <v>330</v>
       </c>
       <c r="B155" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C155" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D155" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E155" t="s">
         <v>10</v>
@@ -5670,16 +5682,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>365</v>
-      </c>
-      <c r="B156" t="s">
-        <v>11</v>
+        <v>369</v>
+      </c>
+      <c r="B156" s="4">
+        <v>1</v>
       </c>
       <c r="C156" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D156" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E156" t="s">
         <v>10</v>
@@ -5690,16 +5702,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>365</v>
-      </c>
-      <c r="B157" t="s">
-        <v>14</v>
+        <v>369</v>
+      </c>
+      <c r="B157" s="4">
+        <v>2</v>
       </c>
       <c r="C157" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D157" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E157" t="s">
         <v>10</v>
@@ -5710,16 +5722,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>365</v>
-      </c>
-      <c r="B158" t="s">
-        <v>17</v>
+        <v>369</v>
+      </c>
+      <c r="B158" s="4">
+        <v>3</v>
       </c>
       <c r="C158" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D158" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E158" t="s">
         <v>10</v>
@@ -5730,16 +5742,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>365</v>
-      </c>
-      <c r="B159" t="s">
-        <v>20</v>
+        <v>369</v>
+      </c>
+      <c r="B159" s="4">
+        <v>4</v>
       </c>
       <c r="C159" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D159" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E159" t="s">
         <v>10</v>
@@ -5750,16 +5762,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>365</v>
-      </c>
-      <c r="B160" t="s">
-        <v>23</v>
+        <v>369</v>
+      </c>
+      <c r="B160" s="4">
+        <v>5</v>
       </c>
       <c r="C160" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D160" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E160" t="s">
         <v>10</v>
@@ -5770,16 +5782,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>365</v>
-      </c>
-      <c r="B161" t="s">
-        <v>26</v>
+        <v>369</v>
+      </c>
+      <c r="B161" s="4">
+        <v>6</v>
       </c>
       <c r="C161" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D161" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
@@ -5790,16 +5802,16 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>365</v>
-      </c>
-      <c r="B162" t="s">
-        <v>29</v>
+        <v>369</v>
+      </c>
+      <c r="B162" s="4">
+        <v>7</v>
       </c>
       <c r="C162" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D162" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E162" t="s">
         <v>10</v>
@@ -5810,16 +5822,16 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>365</v>
-      </c>
-      <c r="B163" t="s">
-        <v>32</v>
+        <v>369</v>
+      </c>
+      <c r="B163" s="4">
+        <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D163" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E163" t="s">
         <v>10</v>
@@ -5830,16 +5842,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>365</v>
-      </c>
-      <c r="B164" t="s">
-        <v>35</v>
+        <v>369</v>
+      </c>
+      <c r="B164" s="4">
+        <v>9</v>
       </c>
       <c r="C164" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D164" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E164" t="s">
         <v>10</v>
@@ -5850,16 +5862,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>365</v>
-      </c>
-      <c r="B165" t="s">
-        <v>38</v>
+        <v>369</v>
+      </c>
+      <c r="B165" s="4">
+        <v>10</v>
       </c>
       <c r="C165" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D165" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E165" t="s">
         <v>10</v>
@@ -5870,16 +5882,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>365</v>
-      </c>
-      <c r="B166" t="s">
-        <v>41</v>
+        <v>369</v>
+      </c>
+      <c r="B166" s="4">
+        <v>11</v>
       </c>
       <c r="C166" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D166" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E166" t="s">
         <v>10</v>
@@ -5890,16 +5902,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>365</v>
-      </c>
-      <c r="B167" t="s">
-        <v>44</v>
+        <v>369</v>
+      </c>
+      <c r="B167" s="4">
+        <v>12</v>
       </c>
       <c r="C167" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D167" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E167" t="s">
         <v>10</v>
@@ -5910,16 +5922,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>365</v>
-      </c>
-      <c r="B168" t="s">
-        <v>47</v>
+        <v>369</v>
+      </c>
+      <c r="B168" s="4">
+        <v>13</v>
       </c>
       <c r="C168" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D168" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E168" t="s">
         <v>10</v>
@@ -5930,16 +5942,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>365</v>
-      </c>
-      <c r="B169" t="s">
-        <v>50</v>
+        <v>369</v>
+      </c>
+      <c r="B169" s="4">
+        <v>14</v>
       </c>
       <c r="C169" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D169" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E169" t="s">
         <v>10</v>
@@ -5950,19 +5962,19 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B170" t="s">
         <v>7</v>
       </c>
       <c r="C170" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D170" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E170" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F170" t="s">
         <v>10</v>
@@ -5970,19 +5982,19 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B171" t="s">
         <v>11</v>
       </c>
       <c r="C171" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D171" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E171" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F171" t="s">
         <v>10</v>
@@ -5990,19 +6002,19 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B172" t="s">
         <v>14</v>
       </c>
       <c r="C172" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D172" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E172" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F172" t="s">
         <v>10</v>
@@ -6010,19 +6022,19 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B173" t="s">
         <v>17</v>
       </c>
       <c r="C173" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D173" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E173" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F173" t="s">
         <v>10</v>
@@ -6030,19 +6042,19 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B174" t="s">
         <v>20</v>
       </c>
       <c r="C174" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D174" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E174" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F174" t="s">
         <v>10</v>
@@ -6050,19 +6062,19 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B175" t="s">
         <v>23</v>
       </c>
       <c r="C175" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D175" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E175" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F175" t="s">
         <v>10</v>
@@ -6070,19 +6082,19 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B176" t="s">
         <v>26</v>
       </c>
       <c r="C176" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D176" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E176" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F176" t="s">
         <v>10</v>
@@ -6090,19 +6102,19 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B177" t="s">
         <v>29</v>
       </c>
       <c r="C177" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D177" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E177" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F177" t="s">
         <v>10</v>
@@ -6110,19 +6122,19 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B178" t="s">
         <v>32</v>
       </c>
       <c r="C178" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D178" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E178" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F178" t="s">
         <v>10</v>
@@ -6130,19 +6142,19 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B179" t="s">
         <v>35</v>
       </c>
       <c r="C179" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D179" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E179" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F179" t="s">
         <v>10</v>
@@ -6150,19 +6162,19 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B180" t="s">
         <v>38</v>
       </c>
       <c r="C180" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D180" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E180" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F180" t="s">
         <v>10</v>
@@ -6170,19 +6182,19 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B181" t="s">
         <v>41</v>
       </c>
       <c r="C181" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D181" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E181" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F181" t="s">
         <v>10</v>
@@ -6190,19 +6202,19 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B182" t="s">
         <v>44</v>
       </c>
       <c r="C182" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D182" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E182" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F182" t="s">
         <v>10</v>
@@ -6210,19 +6222,19 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B183" t="s">
         <v>47</v>
       </c>
       <c r="C183" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D183" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E183" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F183" t="s">
         <v>10</v>
@@ -6230,19 +6242,19 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B184" t="s">
         <v>50</v>
       </c>
       <c r="C184" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D184" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E184" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F184" t="s">
         <v>10</v>
@@ -6250,19 +6262,19 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B185" t="s">
         <v>53</v>
       </c>
       <c r="C185" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D185" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E185" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F185" t="s">
         <v>10</v>
@@ -6270,19 +6282,19 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B186" t="s">
         <v>56</v>
       </c>
       <c r="C186" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D186" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E186" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F186" t="s">
         <v>10</v>
@@ -6290,19 +6302,19 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B187" t="s">
         <v>59</v>
       </c>
       <c r="C187" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F187" t="s">
         <v>10</v>
@@ -6310,19 +6322,19 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B188" t="s">
         <v>62</v>
       </c>
       <c r="C188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D188" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E188" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F188" t="s">
         <v>10</v>
@@ -6330,19 +6342,19 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B189" t="s">
         <v>65</v>
       </c>
       <c r="C189" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D189" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E189" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F189" t="s">
         <v>10</v>
@@ -6350,19 +6362,19 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B190" t="s">
         <v>68</v>
       </c>
       <c r="C190" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D190" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E190" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F190" t="s">
         <v>10</v>
@@ -6370,19 +6382,19 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B191" t="s">
         <v>71</v>
       </c>
       <c r="C191" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D191" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E191" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F191" t="s">
         <v>10</v>
@@ -6390,19 +6402,19 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B192" t="s">
         <v>74</v>
       </c>
       <c r="C192" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D192" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E192" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F192" t="s">
         <v>10</v>
@@ -6410,19 +6422,19 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B193" t="s">
         <v>77</v>
       </c>
       <c r="C193" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D193" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E193" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F193" t="s">
         <v>10</v>
@@ -6430,19 +6442,19 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B194" t="s">
         <v>80</v>
       </c>
       <c r="C194" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D194" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E194" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F194" t="s">
         <v>10</v>
@@ -6450,19 +6462,19 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B195" t="s">
         <v>83</v>
       </c>
       <c r="C195" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D195" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E195" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F195" t="s">
         <v>10</v>
@@ -6470,19 +6482,19 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B196" t="s">
         <v>86</v>
       </c>
       <c r="C196" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D196" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E196" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F196" t="s">
         <v>10</v>
@@ -6490,19 +6502,19 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B197" t="s">
         <v>89</v>
       </c>
       <c r="C197" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D197" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E197" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F197" t="s">
         <v>10</v>
@@ -6510,19 +6522,19 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B198" t="s">
         <v>92</v>
       </c>
       <c r="C198" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D198" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E198" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F198" t="s">
         <v>10</v>

--- a/journal/journal_list.xlsx
+++ b/journal/journal_list.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="486">
   <si>
     <t>Category</t>
   </si>
@@ -854,18 +854,18 @@
     <t>IEEE|https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=7725587</t>
   </si>
   <si>
+    <t>IEEE Transactions on Emerging Topics in Computational Intelligence</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=7777658</t>
+  </si>
+  <si>
     <t>IEEE Transactions on Cognitive and Developmental Systems</t>
   </si>
   <si>
     <t>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=7422051</t>
   </si>
   <si>
-    <t>IEEE Transactions on Emerging Topics in Computational Intelligence</t>
-  </si>
-  <si>
-    <t>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=7777658</t>
-  </si>
-  <si>
     <t>IEEE Systems Journal</t>
   </si>
   <si>
@@ -1307,6 +1307,42 @@
     <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-of79BoeSNOewUhIo96ZMAjN8mFut9UoGSjZTP2iEpFABYwcruA3SHWcybncpeXPbpyxidSxZmHELrN_sWz_TwKPS7pW14Bd4_6sV_an3TIw==&amp;uniplatform=NZKPT; Wanfang|http://c.wanfangdata.com.cn/Periodical-glgcxb.aspx</t>
   </si>
   <si>
+    <t>科研管理</t>
+  </si>
+  <si>
+    <t>http://www.kygl.net.cn/CN/volumn/current.shtml</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-suj3LK5xOmewi2RL88KpHw_Y4IWQV_LOZn6OY_pKGmFH9FAohJfOJBLBXlxEnZMv4t3D9HHG9tzRAf1HsRr0LLg2WgmXzxmB0DsRcV4L4UA==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>情报学报</t>
+  </si>
+  <si>
+    <t>http://c.g.wanfangdata.com.cn/Periodical-qbxb.aspx</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8YKwcHxwZXR6_E831nWKL7VA3KAJM_62nvUu58_o090RvVqN70o6VSQkS3qUEV_VUpKVZXPuh6_MSWrBjvD009QGRHA63B8helTMTx8zKObw==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>工程管理科技前沿</t>
+  </si>
+  <si>
+    <t>https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-GAv0jPFKFXS8SEP2Ah0gRdsS1WKdacP65L7Jt8Llj4s_mjmxb0WQ1lZ8cjqzqp-aMY6vqJmqbd4XiZF25Ocq4q4DcD50p7qpvTJKltS_NFw==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-GAv0jPFKFXS8SEP2Ah0gRdsS1WKdacP65L7Jt8Llj4s_mjmxb0WQ1lZ8cjqzqp-aMY6vqJmqbd4XiZF25Ocq4q4DcD50p7qpvTJKltS_NFw==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>运筹与管理</t>
+  </si>
+  <si>
+    <t>http://www.jorms.net/CN/1007-3221/home.shtml</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-imVfP0-dYeXXBrc_IVJAxvFZOMzq3jmwCdvsMpISPOot7nrWj97vgMsjF53RRn6g8m1XptEIkO8hZpt33WgwzXUX2oAJdEwD1eWfkhpcbTQ==&amp;uniplatform=NZKPT; Wanfang|http://c.wanfangdata.com.cn/Periodical-ycygl.aspx</t>
+  </si>
+  <si>
     <t>南开管理评论</t>
   </si>
   <si>
@@ -1314,42 +1350,6 @@
   </si>
   <si>
     <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9Ue16OTUg-5EwLDyLEfx1_wPrOxIGe2xH33y5mqsDNofkcaL-y2W7K3uP1LsvOBXr20eEhJFLOhUI4gKsH11k050omDbMZlN9CsaeGMhwMBA==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>科研管理</t>
-  </si>
-  <si>
-    <t>http://www.kygl.net.cn/CN/volumn/current.shtml</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-suj3LK5xOmewi2RL88KpHw_Y4IWQV_LOZn6OY_pKGmFH9FAohJfOJBLBXlxEnZMv4t3D9HHG9tzRAf1HsRr0LLg2WgmXzxmB0DsRcV4L4UA==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>情报学报</t>
-  </si>
-  <si>
-    <t>http://c.g.wanfangdata.com.cn/Periodical-qbxb.aspx</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8YKwcHxwZXR6_E831nWKL7VA3KAJM_62nvUu58_o090RvVqN70o6VSQkS3qUEV_VUpKVZXPuh6_MSWrBjvD009QGRHA63B8helTMTx8zKObw==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>工程管理科技前沿</t>
-  </si>
-  <si>
-    <t>https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-GAv0jPFKFXS8SEP2Ah0gRdsS1WKdacP65L7Jt8Llj4s_mjmxb0WQ1lZ8cjqzqp-aMY6vqJmqbd4XiZF25Ocq4q4DcD50p7qpvTJKltS_NFw==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-GAv0jPFKFXS8SEP2Ah0gRdsS1WKdacP65L7Jt8Llj4s_mjmxb0WQ1lZ8cjqzqp-aMY6vqJmqbd4XiZF25Ocq4q4DcD50p7qpvTJKltS_NFw==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>运筹与管理</t>
-  </si>
-  <si>
-    <t>http://www.jorms.net/CN/1007-3221/home.shtml</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-imVfP0-dYeXXBrc_IVJAxvFZOMzq3jmwCdvsMpISPOot7nrWj97vgMsjF53RRn6g8m1XptEIkO8hZpt33WgwzXUX2oAJdEwD1eWfkhpcbTQ==&amp;uniplatform=NZKPT; Wanfang|http://c.wanfangdata.com.cn/Periodical-ycygl.aspx</t>
   </si>
   <si>
     <t>管理学报</t>
@@ -2119,10 +2119,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -4787,8 +4790,8 @@
       <c r="A111" t="s">
         <v>245</v>
       </c>
-      <c r="B111" t="s">
-        <v>50</v>
+      <c r="B111" s="2">
+        <v>15</v>
       </c>
       <c r="C111" t="s">
         <v>275</v>
@@ -4807,8 +4810,8 @@
       <c r="A112" t="s">
         <v>245</v>
       </c>
-      <c r="B112" t="s">
-        <v>53</v>
+      <c r="B112" s="2">
+        <v>16</v>
       </c>
       <c r="C112" t="s">
         <v>277</v>
@@ -4927,7 +4930,7 @@
       <c r="A118" t="s">
         <v>289</v>
       </c>
-      <c r="B118" s="2">
+      <c r="B118" s="3">
         <v>1</v>
       </c>
       <c r="C118" t="s">
@@ -4947,7 +4950,7 @@
       <c r="A119" t="s">
         <v>289</v>
       </c>
-      <c r="B119" s="2">
+      <c r="B119" s="3">
         <v>2</v>
       </c>
       <c r="C119" t="s">
@@ -4967,7 +4970,7 @@
       <c r="A120" t="s">
         <v>289</v>
       </c>
-      <c r="B120" s="2">
+      <c r="B120" s="3">
         <v>3</v>
       </c>
       <c r="C120" t="s">
@@ -4987,7 +4990,7 @@
       <c r="A121" t="s">
         <v>289</v>
       </c>
-      <c r="B121" s="2">
+      <c r="B121" s="3">
         <v>4</v>
       </c>
       <c r="C121" t="s">
@@ -5007,7 +5010,7 @@
       <c r="A122" t="s">
         <v>289</v>
       </c>
-      <c r="B122" s="2">
+      <c r="B122" s="3">
         <v>5</v>
       </c>
       <c r="C122" t="s">
@@ -5027,7 +5030,7 @@
       <c r="A123" t="s">
         <v>289</v>
       </c>
-      <c r="B123" s="2">
+      <c r="B123" s="3">
         <v>6</v>
       </c>
       <c r="C123" t="s">
@@ -5047,7 +5050,7 @@
       <c r="A124" t="s">
         <v>289</v>
       </c>
-      <c r="B124" s="2">
+      <c r="B124" s="3">
         <v>7</v>
       </c>
       <c r="C124" t="s">
@@ -5067,7 +5070,7 @@
       <c r="A125" t="s">
         <v>289</v>
       </c>
-      <c r="B125" s="2">
+      <c r="B125" s="3">
         <v>8</v>
       </c>
       <c r="C125" t="s">
@@ -5087,7 +5090,7 @@
       <c r="A126" t="s">
         <v>307</v>
       </c>
-      <c r="B126" s="2">
+      <c r="B126" s="3">
         <v>1</v>
       </c>
       <c r="C126" t="s">
@@ -5107,7 +5110,7 @@
       <c r="A127" t="s">
         <v>307</v>
       </c>
-      <c r="B127" s="2">
+      <c r="B127" s="3">
         <v>2</v>
       </c>
       <c r="C127" t="s">
@@ -5127,7 +5130,7 @@
       <c r="A128" t="s">
         <v>307</v>
       </c>
-      <c r="B128" s="2">
+      <c r="B128" s="3">
         <v>3</v>
       </c>
       <c r="C128" t="s">
@@ -5147,7 +5150,7 @@
       <c r="A129" t="s">
         <v>307</v>
       </c>
-      <c r="B129" s="2">
+      <c r="B129" s="3">
         <v>4</v>
       </c>
       <c r="C129" t="s">
@@ -5167,7 +5170,7 @@
       <c r="A130" t="s">
         <v>307</v>
       </c>
-      <c r="B130" s="2">
+      <c r="B130" s="3">
         <v>5</v>
       </c>
       <c r="C130" t="s">
@@ -5187,7 +5190,7 @@
       <c r="A131" t="s">
         <v>307</v>
       </c>
-      <c r="B131" s="2">
+      <c r="B131" s="3">
         <v>6</v>
       </c>
       <c r="C131" t="s">
@@ -5207,7 +5210,7 @@
       <c r="A132" t="s">
         <v>307</v>
       </c>
-      <c r="B132" s="2">
+      <c r="B132" s="3">
         <v>7</v>
       </c>
       <c r="C132" t="s">
@@ -5227,7 +5230,7 @@
       <c r="A133" t="s">
         <v>307</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B133" s="3">
         <v>8</v>
       </c>
       <c r="C133" t="s">
@@ -5247,7 +5250,7 @@
       <c r="A134" t="s">
         <v>307</v>
       </c>
-      <c r="B134" s="2">
+      <c r="B134" s="3">
         <v>9</v>
       </c>
       <c r="C134" t="s">
@@ -5267,7 +5270,7 @@
       <c r="A135" t="s">
         <v>307</v>
       </c>
-      <c r="B135" s="2">
+      <c r="B135" s="3">
         <v>10</v>
       </c>
       <c r="C135" t="s">
@@ -5287,7 +5290,7 @@
       <c r="A136" t="s">
         <v>307</v>
       </c>
-      <c r="B136" s="2">
+      <c r="B136" s="3">
         <v>11</v>
       </c>
       <c r="C136" t="s">
@@ -5313,7 +5316,7 @@
       <c r="C137" t="s">
         <v>331</v>
       </c>
-      <c r="D137" s="3" t="s">
+      <c r="D137" s="4" t="s">
         <v>332</v>
       </c>
       <c r="F137" t="s">
@@ -5684,7 +5687,7 @@
       <c r="A156" t="s">
         <v>369</v>
       </c>
-      <c r="B156" s="4">
+      <c r="B156" s="5">
         <v>1</v>
       </c>
       <c r="C156" t="s">
@@ -5704,7 +5707,7 @@
       <c r="A157" t="s">
         <v>369</v>
       </c>
-      <c r="B157" s="4">
+      <c r="B157" s="5">
         <v>2</v>
       </c>
       <c r="C157" t="s">
@@ -5724,7 +5727,7 @@
       <c r="A158" t="s">
         <v>369</v>
       </c>
-      <c r="B158" s="4">
+      <c r="B158" s="5">
         <v>3</v>
       </c>
       <c r="C158" t="s">
@@ -5744,7 +5747,7 @@
       <c r="A159" t="s">
         <v>369</v>
       </c>
-      <c r="B159" s="4">
+      <c r="B159" s="5">
         <v>4</v>
       </c>
       <c r="C159" t="s">
@@ -5764,7 +5767,7 @@
       <c r="A160" t="s">
         <v>369</v>
       </c>
-      <c r="B160" s="4">
+      <c r="B160" s="5">
         <v>5</v>
       </c>
       <c r="C160" t="s">
@@ -5784,7 +5787,7 @@
       <c r="A161" t="s">
         <v>369</v>
       </c>
-      <c r="B161" s="4">
+      <c r="B161" s="5">
         <v>6</v>
       </c>
       <c r="C161" t="s">
@@ -5804,7 +5807,7 @@
       <c r="A162" t="s">
         <v>369</v>
       </c>
-      <c r="B162" s="4">
+      <c r="B162" s="5">
         <v>7</v>
       </c>
       <c r="C162" t="s">
@@ -5824,7 +5827,7 @@
       <c r="A163" t="s">
         <v>369</v>
       </c>
-      <c r="B163" s="4">
+      <c r="B163" s="5">
         <v>8</v>
       </c>
       <c r="C163" t="s">
@@ -5844,7 +5847,7 @@
       <c r="A164" t="s">
         <v>369</v>
       </c>
-      <c r="B164" s="4">
+      <c r="B164" s="5">
         <v>9</v>
       </c>
       <c r="C164" t="s">
@@ -5864,7 +5867,7 @@
       <c r="A165" t="s">
         <v>369</v>
       </c>
-      <c r="B165" s="4">
+      <c r="B165" s="5">
         <v>10</v>
       </c>
       <c r="C165" t="s">
@@ -5884,7 +5887,7 @@
       <c r="A166" t="s">
         <v>369</v>
       </c>
-      <c r="B166" s="4">
+      <c r="B166" s="5">
         <v>11</v>
       </c>
       <c r="C166" t="s">
@@ -5904,7 +5907,7 @@
       <c r="A167" t="s">
         <v>369</v>
       </c>
-      <c r="B167" s="4">
+      <c r="B167" s="5">
         <v>12</v>
       </c>
       <c r="C167" t="s">
@@ -5924,7 +5927,7 @@
       <c r="A168" t="s">
         <v>369</v>
       </c>
-      <c r="B168" s="4">
+      <c r="B168" s="5">
         <v>13</v>
       </c>
       <c r="C168" t="s">
@@ -5944,7 +5947,7 @@
       <c r="A169" t="s">
         <v>369</v>
       </c>
-      <c r="B169" s="4">
+      <c r="B169" s="5">
         <v>14</v>
       </c>
       <c r="C169" t="s">
@@ -6144,10 +6147,10 @@
       <c r="A179" t="s">
         <v>398</v>
       </c>
-      <c r="B179" t="s">
-        <v>35</v>
-      </c>
-      <c r="C179" t="s">
+      <c r="B179" s="2">
+        <v>10</v>
+      </c>
+      <c r="C179" s="2" t="s">
         <v>426</v>
       </c>
       <c r="D179" t="s">
@@ -6164,10 +6167,10 @@
       <c r="A180" t="s">
         <v>398</v>
       </c>
-      <c r="B180" t="s">
-        <v>38</v>
-      </c>
-      <c r="C180" t="s">
+      <c r="B180" s="2">
+        <v>11</v>
+      </c>
+      <c r="C180" s="2" t="s">
         <v>429</v>
       </c>
       <c r="D180" t="s">
@@ -6184,10 +6187,10 @@
       <c r="A181" t="s">
         <v>398</v>
       </c>
-      <c r="B181" t="s">
-        <v>41</v>
-      </c>
-      <c r="C181" t="s">
+      <c r="B181" s="2">
+        <v>12</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>432</v>
       </c>
       <c r="D181" t="s">
@@ -6204,10 +6207,10 @@
       <c r="A182" t="s">
         <v>398</v>
       </c>
-      <c r="B182" t="s">
-        <v>44</v>
-      </c>
-      <c r="C182" t="s">
+      <c r="B182" s="2">
+        <v>13</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>435</v>
       </c>
       <c r="D182" t="s">
@@ -6225,7 +6228,7 @@
         <v>398</v>
       </c>
       <c r="B183" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C183" t="s">
         <v>438</v>

--- a/journal/journal_list.xlsx
+++ b/journal/journal_list.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="486">
   <si>
     <t>Category</t>
   </si>
@@ -1022,60 +1022,60 @@
     <t>Wiley/Taylor/WorldScientific</t>
   </si>
   <si>
+    <t>Expert Systems</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/14680394</t>
+  </si>
+  <si>
+    <t>International Transactions in Operational Research</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/14753995</t>
+  </si>
+  <si>
+    <t>Journal of Multi-Criteria Decision Analysis</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/10991360</t>
+  </si>
+  <si>
+    <t>Decision Sciences Journal</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/15405915</t>
+  </si>
+  <si>
+    <t>Risk Analysis</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/15396924</t>
+  </si>
+  <si>
+    <t>International Journal of Finance &amp; Economics</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/toc/10991158/0/0</t>
+  </si>
+  <si>
+    <t>Journal of Forecasting</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/toc/1099131x/0/0</t>
+  </si>
+  <si>
+    <t>Quality and Reliability Engineering International</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/toc/10991638/0/0</t>
+  </si>
+  <si>
     <t>International Journal of Intelligent Systems</t>
   </si>
   <si>
     <t>https://onlinelibrary.wiley.com/journal/1098111x</t>
   </si>
   <si>
-    <t>Expert Systems</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/journal/14680394</t>
-  </si>
-  <si>
-    <t>International Transactions in Operational Research</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/journal/14753995</t>
-  </si>
-  <si>
-    <t>Journal of Multi-Criteria Decision Analysis</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/journal/10991360</t>
-  </si>
-  <si>
-    <t>Decision Sciences Journal</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/journal/15405915</t>
-  </si>
-  <si>
-    <t>Risk Analysis</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/journal/15396924</t>
-  </si>
-  <si>
-    <t>International Journal of Finance &amp; Economics</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/toc/10991158/0/0</t>
-  </si>
-  <si>
-    <t>Journal of Forecasting</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/toc/1099131x/0/0</t>
-  </si>
-  <si>
-    <t>Quality and Reliability Engineering International</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/toc/10991638/0/0</t>
-  </si>
-  <si>
     <t>IISE Transactions</t>
   </si>
   <si>
@@ -1106,6 +1106,18 @@
     <t>http://www.tandfonline.com/action/showAxaArticles?journalCode=ggen20</t>
   </si>
   <si>
+    <t>Journal of Management Analytics</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/action/showAxaArticles?journalCode=tjma20</t>
+  </si>
+  <si>
+    <t>Economic Research</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/action/showAxaArticles?journalCode=rero20</t>
+  </si>
+  <si>
     <t>International Journal of Information Technology &amp; Decision Making</t>
   </si>
   <si>
@@ -1122,18 +1134,6 @@
   </si>
   <si>
     <t>http://www.worldscientific.com/toc/apjor/0/0</t>
-  </si>
-  <si>
-    <t>Economic Research</t>
-  </si>
-  <si>
-    <t>https://www.tandfonline.com/action/showAxaArticles?journalCode=rero20</t>
-  </si>
-  <si>
-    <t>Journal of Management Analytics</t>
-  </si>
-  <si>
-    <t>https://www.tandfonline.com/action/showAxaArticles?journalCode=tjma20</t>
   </si>
   <si>
     <t>Others</t>
@@ -2130,11 +2130,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -5306,18 +5306,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" ht="14.4" spans="1:6">
+    <row r="137" spans="1:6">
       <c r="A137" t="s">
         <v>330</v>
       </c>
-      <c r="B137" t="s">
-        <v>7</v>
+      <c r="B137" s="4">
+        <v>1</v>
       </c>
       <c r="C137" t="s">
         <v>331</v>
       </c>
-      <c r="D137" s="4" t="s">
+      <c r="D137" t="s">
         <v>332</v>
+      </c>
+      <c r="E137" t="s">
+        <v>10</v>
       </c>
       <c r="F137" t="s">
         <v>10</v>
@@ -5327,8 +5330,8 @@
       <c r="A138" t="s">
         <v>330</v>
       </c>
-      <c r="B138" t="s">
-        <v>11</v>
+      <c r="B138" s="4">
+        <v>2</v>
       </c>
       <c r="C138" t="s">
         <v>333</v>
@@ -5347,8 +5350,8 @@
       <c r="A139" t="s">
         <v>330</v>
       </c>
-      <c r="B139" t="s">
-        <v>14</v>
+      <c r="B139" s="4">
+        <v>3</v>
       </c>
       <c r="C139" t="s">
         <v>335</v>
@@ -5367,8 +5370,8 @@
       <c r="A140" t="s">
         <v>330</v>
       </c>
-      <c r="B140" t="s">
-        <v>17</v>
+      <c r="B140" s="4">
+        <v>4</v>
       </c>
       <c r="C140" t="s">
         <v>337</v>
@@ -5387,8 +5390,8 @@
       <c r="A141" t="s">
         <v>330</v>
       </c>
-      <c r="B141" t="s">
-        <v>20</v>
+      <c r="B141" s="4">
+        <v>5</v>
       </c>
       <c r="C141" t="s">
         <v>339</v>
@@ -5407,8 +5410,8 @@
       <c r="A142" t="s">
         <v>330</v>
       </c>
-      <c r="B142" t="s">
-        <v>23</v>
+      <c r="B142" s="4">
+        <v>6</v>
       </c>
       <c r="C142" t="s">
         <v>341</v>
@@ -5427,8 +5430,8 @@
       <c r="A143" t="s">
         <v>330</v>
       </c>
-      <c r="B143" t="s">
-        <v>26</v>
+      <c r="B143" s="4">
+        <v>7</v>
       </c>
       <c r="C143" t="s">
         <v>343</v>
@@ -5447,8 +5450,8 @@
       <c r="A144" t="s">
         <v>330</v>
       </c>
-      <c r="B144" t="s">
-        <v>29</v>
+      <c r="B144" s="4">
+        <v>8</v>
       </c>
       <c r="C144" t="s">
         <v>345</v>
@@ -5463,21 +5466,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" ht="14.4" spans="1:6">
       <c r="A145" t="s">
         <v>330</v>
       </c>
-      <c r="B145" t="s">
-        <v>32</v>
+      <c r="B145" s="4">
+        <v>9</v>
       </c>
       <c r="C145" t="s">
         <v>347</v>
       </c>
-      <c r="D145" t="s">
+      <c r="D145" s="5" t="s">
         <v>348</v>
-      </c>
-      <c r="E145" t="s">
-        <v>10</v>
       </c>
       <c r="F145" t="s">
         <v>10</v>
@@ -5487,8 +5487,8 @@
       <c r="A146" t="s">
         <v>330</v>
       </c>
-      <c r="B146" t="s">
-        <v>35</v>
+      <c r="B146" s="4">
+        <v>10</v>
       </c>
       <c r="C146" t="s">
         <v>349</v>
@@ -5507,8 +5507,8 @@
       <c r="A147" t="s">
         <v>330</v>
       </c>
-      <c r="B147" t="s">
-        <v>38</v>
+      <c r="B147" s="4">
+        <v>11</v>
       </c>
       <c r="C147" t="s">
         <v>351</v>
@@ -5527,8 +5527,8 @@
       <c r="A148" t="s">
         <v>330</v>
       </c>
-      <c r="B148" t="s">
-        <v>41</v>
+      <c r="B148" s="4">
+        <v>12</v>
       </c>
       <c r="C148" t="s">
         <v>353</v>
@@ -5547,8 +5547,8 @@
       <c r="A149" t="s">
         <v>330</v>
       </c>
-      <c r="B149" t="s">
-        <v>44</v>
+      <c r="B149" s="4">
+        <v>13</v>
       </c>
       <c r="C149" t="s">
         <v>355</v>
@@ -5567,8 +5567,8 @@
       <c r="A150" t="s">
         <v>330</v>
       </c>
-      <c r="B150" t="s">
-        <v>47</v>
+      <c r="B150" s="4">
+        <v>14</v>
       </c>
       <c r="C150" t="s">
         <v>357</v>
@@ -5587,8 +5587,8 @@
       <c r="A151" t="s">
         <v>330</v>
       </c>
-      <c r="B151" t="s">
-        <v>50</v>
+      <c r="B151" s="4">
+        <v>15</v>
       </c>
       <c r="C151" t="s">
         <v>359</v>
@@ -5607,8 +5607,8 @@
       <c r="A152" t="s">
         <v>330</v>
       </c>
-      <c r="B152" t="s">
-        <v>53</v>
+      <c r="B152" s="4">
+        <v>16</v>
       </c>
       <c r="C152" t="s">
         <v>361</v>
@@ -5627,8 +5627,8 @@
       <c r="A153" t="s">
         <v>330</v>
       </c>
-      <c r="B153" t="s">
-        <v>56</v>
+      <c r="B153" s="4">
+        <v>17</v>
       </c>
       <c r="C153" t="s">
         <v>363</v>
@@ -5647,8 +5647,8 @@
       <c r="A154" t="s">
         <v>330</v>
       </c>
-      <c r="B154" t="s">
-        <v>59</v>
+      <c r="B154" s="4">
+        <v>18</v>
       </c>
       <c r="C154" t="s">
         <v>365</v>
@@ -5667,8 +5667,8 @@
       <c r="A155" t="s">
         <v>330</v>
       </c>
-      <c r="B155" t="s">
-        <v>62</v>
+      <c r="B155" s="4">
+        <v>19</v>
       </c>
       <c r="C155" t="s">
         <v>367</v>
@@ -5687,7 +5687,7 @@
       <c r="A156" t="s">
         <v>369</v>
       </c>
-      <c r="B156" s="5">
+      <c r="B156" s="2">
         <v>1</v>
       </c>
       <c r="C156" t="s">
@@ -5707,7 +5707,7 @@
       <c r="A157" t="s">
         <v>369</v>
       </c>
-      <c r="B157" s="5">
+      <c r="B157" s="2">
         <v>2</v>
       </c>
       <c r="C157" t="s">
@@ -5727,7 +5727,7 @@
       <c r="A158" t="s">
         <v>369</v>
       </c>
-      <c r="B158" s="5">
+      <c r="B158" s="2">
         <v>3</v>
       </c>
       <c r="C158" t="s">
@@ -5747,7 +5747,7 @@
       <c r="A159" t="s">
         <v>369</v>
       </c>
-      <c r="B159" s="5">
+      <c r="B159" s="2">
         <v>4</v>
       </c>
       <c r="C159" t="s">
@@ -5767,7 +5767,7 @@
       <c r="A160" t="s">
         <v>369</v>
       </c>
-      <c r="B160" s="5">
+      <c r="B160" s="2">
         <v>5</v>
       </c>
       <c r="C160" t="s">
@@ -5787,7 +5787,7 @@
       <c r="A161" t="s">
         <v>369</v>
       </c>
-      <c r="B161" s="5">
+      <c r="B161" s="2">
         <v>6</v>
       </c>
       <c r="C161" t="s">
@@ -5807,7 +5807,7 @@
       <c r="A162" t="s">
         <v>369</v>
       </c>
-      <c r="B162" s="5">
+      <c r="B162" s="2">
         <v>7</v>
       </c>
       <c r="C162" t="s">
@@ -5827,7 +5827,7 @@
       <c r="A163" t="s">
         <v>369</v>
       </c>
-      <c r="B163" s="5">
+      <c r="B163" s="2">
         <v>8</v>
       </c>
       <c r="C163" t="s">
@@ -5847,7 +5847,7 @@
       <c r="A164" t="s">
         <v>369</v>
       </c>
-      <c r="B164" s="5">
+      <c r="B164" s="2">
         <v>9</v>
       </c>
       <c r="C164" t="s">
@@ -5867,7 +5867,7 @@
       <c r="A165" t="s">
         <v>369</v>
       </c>
-      <c r="B165" s="5">
+      <c r="B165" s="2">
         <v>10</v>
       </c>
       <c r="C165" t="s">
@@ -5887,7 +5887,7 @@
       <c r="A166" t="s">
         <v>369</v>
       </c>
-      <c r="B166" s="5">
+      <c r="B166" s="2">
         <v>11</v>
       </c>
       <c r="C166" t="s">
@@ -5907,7 +5907,7 @@
       <c r="A167" t="s">
         <v>369</v>
       </c>
-      <c r="B167" s="5">
+      <c r="B167" s="2">
         <v>12</v>
       </c>
       <c r="C167" t="s">
@@ -5927,7 +5927,7 @@
       <c r="A168" t="s">
         <v>369</v>
       </c>
-      <c r="B168" s="5">
+      <c r="B168" s="2">
         <v>13</v>
       </c>
       <c r="C168" t="s">
@@ -5947,7 +5947,7 @@
       <c r="A169" t="s">
         <v>369</v>
       </c>
-      <c r="B169" s="5">
+      <c r="B169" s="2">
         <v>14</v>
       </c>
       <c r="C169" t="s">

--- a/journal/journal_list.xlsx
+++ b/journal/journal_list.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\journal\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAE8D9A-52EA-47B2-98B5-AFFAD8CB23AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal List" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="514">
   <si>
     <t>Category</t>
   </si>
@@ -896,9 +902,6 @@
     <t>https://ieeexplore.ieee.org/xpl/tocresult.jsp?isnumber=4601496&amp;sortType=newest</t>
   </si>
   <si>
-    <t>UTD/INFORMS</t>
-  </si>
-  <si>
     <t>Management Science</t>
   </si>
   <si>
@@ -944,560 +947,673 @@
     <t>Production and Operations Management</t>
   </si>
   <si>
+    <t>Wiley|https://onlinelibrary.wiley.com/toc/19375956/0/0</t>
+  </si>
+  <si>
+    <t>ACM</t>
+  </si>
+  <si>
+    <t>ACM Computing Surveys</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/toc/csur/justaccepted</t>
+  </si>
+  <si>
+    <t>ACM Transactions on Intelligent Systems and Technology</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/toc/tist/justaccepted</t>
+  </si>
+  <si>
+    <t>ACM Transactions on Knowledge Discovery from Data</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/toc/tkdd/justaccepted</t>
+  </si>
+  <si>
+    <t>ACM Transactions on Management Information Systems</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/toc/tmis/justaccepted</t>
+  </si>
+  <si>
+    <t>ACM Transactions on Information Systems</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/toc/tois/justaccepted</t>
+  </si>
+  <si>
+    <t>ACM Transactions on the Web</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/toc/tweb/justaccepted</t>
+  </si>
+  <si>
+    <t>ACM Transactions on Recommender Systems</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/toc/tors/justaccepted</t>
+  </si>
+  <si>
+    <t>ACM Transactions on Internet Technology</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/toc/toit/justaccepted</t>
+  </si>
+  <si>
+    <t>ACM Transactions on Modeling and Computer Simulation</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/toc/tomacs/justaccepted</t>
+  </si>
+  <si>
+    <t>ACM Transactions on Social Computing</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/toc/tsc/justaccepted</t>
+  </si>
+  <si>
+    <t>ACM/IMS Transactions on Data Science</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/toc/tds/current</t>
+  </si>
+  <si>
+    <t>Wiley/Taylor/WorldScientific</t>
+  </si>
+  <si>
+    <t>Expert Systems</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/14680394</t>
+  </si>
+  <si>
+    <t>International Transactions in Operational Research</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/14753995</t>
+  </si>
+  <si>
+    <t>Journal of Multi-Criteria Decision Analysis</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/10991360</t>
+  </si>
+  <si>
+    <t>Decision Sciences Journal</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/15405915</t>
+  </si>
+  <si>
+    <t>Risk Analysis</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/15396924</t>
+  </si>
+  <si>
+    <t>International Journal of Finance &amp; Economics</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/toc/10991158/0/0</t>
+  </si>
+  <si>
+    <t>Journal of Forecasting</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/toc/1099131x/0/0</t>
+  </si>
+  <si>
+    <t>Quality and Reliability Engineering International</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/toc/10991638/0/0</t>
+  </si>
+  <si>
+    <t>IISE Transactions</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/toc/uiie21/0/ja</t>
+  </si>
+  <si>
+    <t>Journal of the Operational Research Society</t>
+  </si>
+  <si>
+    <t>http://www.tandfonline.com/action/showAxaArticles?journalCode=tjor20</t>
+  </si>
+  <si>
+    <t>International Journal of Production Research</t>
+  </si>
+  <si>
+    <t>http://www.tandfonline.com/action/showAxaArticles?journalCode=tprs20</t>
+  </si>
+  <si>
+    <t>International Journal of Systems Science</t>
+  </si>
+  <si>
+    <t>http://www.tandfonline.com/action/showAxaArticles?journalCode=tsys20</t>
+  </si>
+  <si>
+    <t>International Journal of General Systems</t>
+  </si>
+  <si>
+    <t>http://www.tandfonline.com/action/showAxaArticles?journalCode=ggen20</t>
+  </si>
+  <si>
+    <t>Journal of Management Analytics</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/action/showAxaArticles?journalCode=tjma20</t>
+  </si>
+  <si>
+    <t>Economic Research</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/action/showAxaArticles?journalCode=rero20</t>
+  </si>
+  <si>
+    <t>International Journal of Information Technology &amp; Decision Making</t>
+  </si>
+  <si>
+    <t>http://www.worldscientific.com/worldscinet/ijitdm</t>
+  </si>
+  <si>
+    <t>International Journal of Uncertainty, Fuzziness and Knowledge-Based Systems</t>
+  </si>
+  <si>
+    <t>http://www.worldscientific.com/worldscinet/ijufks</t>
+  </si>
+  <si>
+    <t>Asia-Pacific Journal of Operational Research</t>
+  </si>
+  <si>
+    <t>http://www.worldscientific.com/toc/apjor/0/0</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Technological and Economic Development of Economy</t>
+  </si>
+  <si>
+    <t>https://journals.vgtu.lt/index.php/TEDE</t>
+  </si>
+  <si>
+    <t>INFORMATICA</t>
+  </si>
+  <si>
+    <t>https://informatica.vu.lt/journal/INFORMATICA/to-appear</t>
+  </si>
+  <si>
+    <t>International Journal of Computers Communications &amp; Control</t>
+  </si>
+  <si>
+    <t>http://univagora.ro/jour/index.php/ijccc/</t>
+  </si>
+  <si>
+    <t>International Journal of Strategic Property Management</t>
+  </si>
+  <si>
+    <t>https://journals.vgtu.lt/index.php/IJSPM</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>https://journals.vgtu.lt/index.php/Transport</t>
+  </si>
+  <si>
+    <t>Transformations in Business &amp; Economics</t>
+  </si>
+  <si>
+    <t>http://www.transformations.knf.vu.lt/</t>
+  </si>
+  <si>
+    <t>Scientia Iranica</t>
+  </si>
+  <si>
+    <t>http://scientiairanica.sharif.edu/?_action=current&amp;_is=Current%20Issue</t>
+  </si>
+  <si>
+    <t>Iranian Journal of Fuzzy Systems</t>
+  </si>
+  <si>
+    <t>http://ijfs.usb.ac.ir/?_action=press&amp;issue=-1&amp;_is=Articles%20in%20Press</t>
+  </si>
+  <si>
+    <t>Kybernetes</t>
+  </si>
+  <si>
+    <t>https://www.emerald.com/insight/publication/issn/0368-492X</t>
+  </si>
+  <si>
+    <t>Intelligent Decision Technologies</t>
+  </si>
+  <si>
+    <t>http://content.iospress.com/journals/intelligent-decision-technologies</t>
+  </si>
+  <si>
+    <t>Fundamenta Informaticae</t>
+  </si>
+  <si>
+    <t>http://content.iospress.com/journals/fundamenta-informaticae</t>
+  </si>
+  <si>
+    <t>Intelligent Data Analysis</t>
+  </si>
+  <si>
+    <t>http://content.iospress.com/journals/intelligent-data-analysis</t>
+  </si>
+  <si>
+    <t>Journal of Smart Environments and Green Computing</t>
+  </si>
+  <si>
+    <t>https://segcjournal.com/journal/archives</t>
+  </si>
+  <si>
+    <t>Journal of Civil Engineering and Management</t>
+  </si>
+  <si>
+    <t>https://journals.vgtu.lt/index.php/JCEM/issue/current</t>
+  </si>
+  <si>
+    <t>中文期刊</t>
+  </si>
+  <si>
+    <t>管理科学学报</t>
+  </si>
+  <si>
+    <t>http://jmsc.tju.edu.cn/ch/index.aspx</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8LJ05z2WKBaal83R1aZsKHhDdcfMpx3UBz-GfhJW-s7MsP1nXNGVxV1DUmvt3bqyaob8lhOefEDtskNzOE_2EpC2gCrA_8RJXiGWDTI_iUNA==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>系统工程理论与实践</t>
+  </si>
+  <si>
+    <t>http://www.sysengi.com/</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=i3PX7_dq32X2Zk0vdxkR-ODkxN-nI3yF4njbEspRx73Nm7WAR7J-vcwM0_OoNx8FEvxGLJCXasn3KAcQ0RARebKAq4xD1pgviZ0U7vSuBvfNMhDxzEeSoA==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>管理世界</t>
+  </si>
+  <si>
+    <t>http://www.mwm.net.cn/web/</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9bPeMF52gorOhVMoCTm_bP4JUtgupb_E88sMy-gsXzFr1P8lBB8uHZukD4Te4RdLMKnj45i1j1MNnPQo45WRUOuqkrMgwUszODdbOWIRUqkg==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>中国管理科学</t>
+  </si>
+  <si>
+    <t>http://www.zgglkx.com</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-JU_du0-bK0lg27F1Oi8b1cNGusZwUOwac7P02Y1arLcSfkZu0L8ZB1IJhn7Fj80XDx2f9_sQ5r3G6IQgpyTe3Y_JDssEju9qAhMsGw3X0qw==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>系统工程学报</t>
+  </si>
+  <si>
+    <t>http://jse.tju.edu.cn</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-NWam7tarWG4WxmWSs2_tcqdiLEz4i3KVdQbtnKLITej4vXhwHRR3aDau0yw8d_IavznXlO9dN3zYuKL_de5S7p2u36GqLdzMfHA3Wg9Wx0w==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>系统管理学报</t>
+  </si>
+  <si>
+    <t>http://xtglxb.sjtu.edu.cn/</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9URZHjnjpZNx894uUc8hEV_8y-XaWbYy_QQKZwrmUaOuHU_Ulmiyfu5w84oSoQ8OSwjHPBK4vEcFxdVksfIHxNuv4CL8S5HTYziOHdCIpK2w==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>管理科学</t>
+  </si>
+  <si>
+    <t>http://glkx.hit.edu.cn/glkxcn/ch/index.aspx</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_ZE6E2FOt_BwppB5uBeXQErN0I5kVHOud5T_DbHM98apuHBLYdN4agXMpq5m9CZr4pnZE4hFnsyANk-8DWJ3fFUdWzB2oij7TzlVIKAxfF6A==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>管理评论</t>
+  </si>
+  <si>
+    <t>http://www.glplzz.com/</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-TCsOxvxdXdlSvw79gRfLC3Qs4Zx8pWINWUiL6dgoj_PFvNjjxeJ-IodjHg3dspx0OB_4yj_j_2YdtzhxiYvBKymQM3Mm052AZyEPIfen2cA==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>管理工程学报</t>
+  </si>
+  <si>
+    <t>http://glgcxb.zju.edu.cn/</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-of79BoeSNOewUhIo96ZMAjN8mFut9UoGSjZTP2iEpFABYwcruA3SHWcybncpeXPbpyxidSxZmHELrN_sWz_TwKPS7pW14Bd4_6sV_an3TIw==&amp;uniplatform=NZKPT; Wanfang|http://c.wanfangdata.com.cn/Periodical-glgcxb.aspx</t>
+  </si>
+  <si>
+    <t>科研管理</t>
+  </si>
+  <si>
+    <t>http://www.kygl.net.cn/CN/volumn/current.shtml</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-suj3LK5xOmewi2RL88KpHw_Y4IWQV_LOZn6OY_pKGmFH9FAohJfOJBLBXlxEnZMv4t3D9HHG9tzRAf1HsRr0LLg2WgmXzxmB0DsRcV4L4UA==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>情报学报</t>
+  </si>
+  <si>
+    <t>http://c.g.wanfangdata.com.cn/Periodical-qbxb.aspx</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8YKwcHxwZXR6_E831nWKL7VA3KAJM_62nvUu58_o090RvVqN70o6VSQkS3qUEV_VUpKVZXPuh6_MSWrBjvD009QGRHA63B8helTMTx8zKObw==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>工程管理科技前沿</t>
+  </si>
+  <si>
+    <t>https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-GAv0jPFKFXS8SEP2Ah0gRdsS1WKdacP65L7Jt8Llj4s_mjmxb0WQ1lZ8cjqzqp-aMY6vqJmqbd4XiZF25Ocq4q4DcD50p7qpvTJKltS_NFw==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-GAv0jPFKFXS8SEP2Ah0gRdsS1WKdacP65L7Jt8Llj4s_mjmxb0WQ1lZ8cjqzqp-aMY6vqJmqbd4XiZF25Ocq4q4DcD50p7qpvTJKltS_NFw==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>运筹与管理</t>
+  </si>
+  <si>
+    <t>http://www.jorms.net/CN/1007-3221/home.shtml</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-imVfP0-dYeXXBrc_IVJAxvFZOMzq3jmwCdvsMpISPOot7nrWj97vgMsjF53RRn6g8m1XptEIkO8hZpt33WgwzXUX2oAJdEwD1eWfkhpcbTQ==&amp;uniplatform=NZKPT; Wanfang|http://c.wanfangdata.com.cn/Periodical-ycygl.aspx</t>
+  </si>
+  <si>
+    <t>南开管理评论</t>
+  </si>
+  <si>
+    <t>http://www.nbronline.cn/ch/index.aspx</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9Ue16OTUg-5EwLDyLEfx1_wPrOxIGe2xH33y5mqsDNofkcaL-y2W7K3uP1LsvOBXr20eEhJFLOhUI4gKsH11k050omDbMZlN9CsaeGMhwMBA==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>管理学报</t>
+  </si>
+  <si>
+    <t>http://manu68.magtech.com.cn/Jwk_glxb/CN/volumn/current.shtml</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8PCnUrD8saRufeUaB7vvWh8ImJB4HeHNeLqW0ePwzGyEPNRCnQsHlbFXGOlO-wcTfqZgKY4hDwsLs-3Tn89zOBbGtw1AAMZyEw5PPM6laErQ==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>工业工程与管理</t>
+  </si>
+  <si>
+    <t>https://gygc.cbpt.cnki.net/WKB2/WebPublication/index.aspx?mid=gygc</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8br7MgEIcFYMQt_ZJBi4Gq5howJvAAN2q5Uw-jRJpkwA6seBfU1WclQ4xGDeYNZADI68ojMDuwRNLC-W9Dialui-wgcg5tuYIT8ESNZSpaSQ==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>系统工程</t>
+  </si>
+  <si>
+    <t>http://www.xitonggongcheng.cn/</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_WFCPnBSQTbCMipV7pzuUWmqJVRmNF8oX6Kjc45ATyApiwW7K32zXQ0P-6LMKJ521dERQpzlafVK7qGUOU45RpQBLI3a7dqVm6V_hSwqA5HQ==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>控制与决策</t>
+  </si>
+  <si>
+    <t>http://kzyjc.alljournals.cn/ch/index.aspx</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9VMm0YxN4tX5yL-EVnsT6PAjZVl9XwIKssVo1NvBga91FGUvekhWuNlMQI0JER059BEkpPkSf2yKf-gU-zpBPmAP0aZmcjFXxTBOO3l4T0hA==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>系统工程与电子技术</t>
+  </si>
+  <si>
+    <t>http://www.sys-ele.com/CN/1001-506X/home.shtml</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_WFCPnBSQTbCMipV7pzuUWmqJVRmNF8oX6Kjc45ATyApiwW7K32zXQ0P-6LMKJ522XKppJFMLpkDt0YeID7jzeew3YqHq1UltKzV8MACc98A==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>中国软科学</t>
+  </si>
+  <si>
+    <t>http://www.cssm.com.cn/ch/index.aspx</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8jySLJU_283KXns0m8yNk0Ce8rmtobTme-1MViCCKsbzSynAlfsvvxkGahZxy_URE-jKLwH5grOgRQ7kKV0KBnSC88LYojIfsOG5GxO7NKdg==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>系统科学与数学</t>
+  </si>
+  <si>
+    <t>http://sysmath.com/jweb_xtkxysx</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-E-p5hVM-T-2-bewhhYzlPKidJWYOorDi1B-PITMAbOL0S7cekgijFCS0nSXq4XQNKt1GbaW3S6VWjdbpFqoGY_EIIuekH5mr8rxzI_HrR7g==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>计量经济学报</t>
+  </si>
+  <si>
+    <t>http://www.cjoe.ac.cn/CN/2096-9732/home.shtml</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9O7KTOAqVcVsRDT7MmQLR8XCOwVreqgSqoJ_mGw8hFdrvny_-zVG3nRwmEQnA8E_SpxQeLOkYd7CxfbKQuxDeda_UEYUS14oC9RQJGSD6dYg==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>自动化学报</t>
+  </si>
+  <si>
+    <t>http://www.aas.net.cn/CN/volumn/current.shtml</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_KyFB5Et1OillJwmuopCWBj5pdqWDmDRaudYAq4j6C1SQ8RskmxnZJipOZnXxhDK_wNDwDjzo_dILEkzq7JyCDiG26p2JrBu__1dKfqF0Hug==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>计算机学报</t>
+  </si>
+  <si>
+    <t>http://cjc.ict.ac.cn/</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9_vxQO77UEmThRI7mhs7_u-tPwE_PVKzc0Y8BhMYBHTzr98uiHz_J7VQEcj0zQgQD69gziJmOh-Y7_MS0eWzVrjAi2cxJHj4AyA5FLhECB7Q==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>计算机研究与发展</t>
+  </si>
+  <si>
+    <t>http://crad.ict.ac.cn/</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8lGm60BT1S32qMmgQriP9uZ2ShOTZe4_8yW-QQYDij87AjrNp9M_13YGgNGlrNwq-vJCQhJ1KyL0VCjz5laN36JY4u-_EtYQc2NFnjQlP6wg==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>电子学报</t>
+  </si>
+  <si>
+    <t>http://www.ejournal.org.cn/CN/volumn/current.shtml</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/journals/DZXU/detail?uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>软件学报</t>
+  </si>
+  <si>
+    <t>http://www.jos.org.cn/</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-eSDBBKMj0vAeZF-smiUXPlDeISBrKFJZZ9arNvuLVDlcERM2YiZPI_j0aeLQpFlrUVoLG0JBQXMun-myIj8mt0fvZymwFzAizMqubrnbCDg==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>中国科学: 信息科学</t>
+  </si>
+  <si>
+    <t>https://www.sciengine.com/publisher/scp/journal/SSI?slug=firstpublish</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_wGZ_mUleWCYCON5LbBM4MWv3xigAWN4kttzDDJAGVBd7SeAnjCYVkCmhMZnWmK8p7oIeobAw_ntBHWA0d52ws1dPal6Yqvk_voRKDk5MihA==&amp;uniplatform=NZKPT</t>
+  </si>
+  <si>
+    <t>数据分析与知识发现</t>
+  </si>
+  <si>
+    <t>https://manu44.magtech.com.cn/Jwk_infotech_wk3/CN/2096-3467/home.shtml</t>
+  </si>
+  <si>
+    <t>CNKI|https://navi.cnki.net/knavi/journals/XDTQ/detail</t>
+  </si>
+  <si>
+    <t>EBSCO|https://search.ebscohost.com/direct.asp?db=bth&amp;jid=MGS&amp;scope=site</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBSCO|https://search.ebscohost.com/direct.asp?db=bth&amp;jid=OPR&amp;scope=site</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBSCO|https://search.ebscohost.com/direct.asp?db=bth&amp;jid=7EE&amp;scope=site</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBSCO|https://search.ebscohost.com/direct.asp?db=bth&amp;jid=RD0&amp;scope=site</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBSCO|https://search.ebscohost.com/direct.asp?db=bth&amp;jid=5YY&amp;scope=site</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBSCO|https://search.ebscohost.com/direct.asp?db=bth&amp;jid=1LD&amp;scope=site</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBSCO|https://search.ebscohost.com/direct.asp?db=bth&amp;jid=N81C&amp;scope=site</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Marketing Science</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBSCO|https://search.ebscohost.com/direct.asp?db=bth&amp;jid=MKS&amp;scope=site</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transportation Science</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://pubsonline.informs.org/journal/trsc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://pubsonline.informs.org/journal/mksc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBSCO|https://search.ebscohost.com/direct.asp?db=bth&amp;jid=2HN&amp;scope=site</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBSCO|https://search.ebscohost.com/direct.asp?db=bth&amp;jid=MIS&amp;scope=site</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Harvard Business Review</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://misq.umn.edu/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MIS Quarterly</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://search.ebscohost.com/direct.asp?db=bth&amp;jid=HBR&amp;scope=site</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTD/INFORMS/FT</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Journal of Management Information Systems</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Web|https://www.jmis-web.org/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://research.ebsco.com/c/ueifeu/search/advanced/publications/JOU?autocorrect=y&amp;selectedDb=bthjnh</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Journal of Marketing Research(JMR)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBSCO|https://search.ebscohost.com/direct.asp?db=bth&amp;jid=MKR&amp;scope=site</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>https://journals.sagepub.com/action/doSearch?AllField=Production+and+Operations+Management&amp;SeriesKey=paoa&amp;startPage=0&amp;sortBy=FullEpubDateField</t>
-  </si>
-  <si>
-    <t>Wiley|https://onlinelibrary.wiley.com/toc/19375956/0/0</t>
-  </si>
-  <si>
-    <t>ACM</t>
-  </si>
-  <si>
-    <t>ACM Computing Surveys</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/toc/csur/justaccepted</t>
-  </si>
-  <si>
-    <t>ACM Transactions on Intelligent Systems and Technology</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/toc/tist/justaccepted</t>
-  </si>
-  <si>
-    <t>ACM Transactions on Knowledge Discovery from Data</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/toc/tkdd/justaccepted</t>
-  </si>
-  <si>
-    <t>ACM Transactions on Management Information Systems</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/toc/tmis/justaccepted</t>
-  </si>
-  <si>
-    <t>ACM Transactions on Information Systems</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/toc/tois/justaccepted</t>
-  </si>
-  <si>
-    <t>ACM Transactions on the Web</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/toc/tweb/justaccepted</t>
-  </si>
-  <si>
-    <t>ACM Transactions on Recommender Systems</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/toc/tors/justaccepted</t>
-  </si>
-  <si>
-    <t>ACM Transactions on Internet Technology</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/toc/toit/justaccepted</t>
-  </si>
-  <si>
-    <t>ACM Transactions on Modeling and Computer Simulation</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/toc/tomacs/justaccepted</t>
-  </si>
-  <si>
-    <t>ACM Transactions on Social Computing</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/toc/tsc/justaccepted</t>
-  </si>
-  <si>
-    <t>ACM/IMS Transactions on Data Science</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/toc/tds/current</t>
-  </si>
-  <si>
-    <t>Wiley/Taylor/WorldScientific</t>
-  </si>
-  <si>
-    <t>Expert Systems</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/journal/14680394</t>
-  </si>
-  <si>
-    <t>International Transactions in Operational Research</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/journal/14753995</t>
-  </si>
-  <si>
-    <t>Journal of Multi-Criteria Decision Analysis</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/journal/10991360</t>
-  </si>
-  <si>
-    <t>Decision Sciences Journal</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/journal/15405915</t>
-  </si>
-  <si>
-    <t>Risk Analysis</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/journal/15396924</t>
-  </si>
-  <si>
-    <t>International Journal of Finance &amp; Economics</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/toc/10991158/0/0</t>
-  </si>
-  <si>
-    <t>Journal of Forecasting</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/toc/1099131x/0/0</t>
-  </si>
-  <si>
-    <t>Quality and Reliability Engineering International</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/toc/10991638/0/0</t>
-  </si>
-  <si>
-    <t>International Journal of Intelligent Systems</t>
-  </si>
-  <si>
-    <t>https://onlinelibrary.wiley.com/journal/1098111x</t>
-  </si>
-  <si>
-    <t>IISE Transactions</t>
-  </si>
-  <si>
-    <t>https://www.tandfonline.com/toc/uiie21/0/ja</t>
-  </si>
-  <si>
-    <t>Journal of the Operational Research Society</t>
-  </si>
-  <si>
-    <t>http://www.tandfonline.com/action/showAxaArticles?journalCode=tjor20</t>
-  </si>
-  <si>
-    <t>International Journal of Production Research</t>
-  </si>
-  <si>
-    <t>http://www.tandfonline.com/action/showAxaArticles?journalCode=tprs20</t>
-  </si>
-  <si>
-    <t>International Journal of Systems Science</t>
-  </si>
-  <si>
-    <t>http://www.tandfonline.com/action/showAxaArticles?journalCode=tsys20</t>
-  </si>
-  <si>
-    <t>International Journal of General Systems</t>
-  </si>
-  <si>
-    <t>http://www.tandfonline.com/action/showAxaArticles?journalCode=ggen20</t>
-  </si>
-  <si>
-    <t>Journal of Management Analytics</t>
-  </si>
-  <si>
-    <t>https://www.tandfonline.com/action/showAxaArticles?journalCode=tjma20</t>
-  </si>
-  <si>
-    <t>Economic Research</t>
-  </si>
-  <si>
-    <t>https://www.tandfonline.com/action/showAxaArticles?journalCode=rero20</t>
-  </si>
-  <si>
-    <t>International Journal of Information Technology &amp; Decision Making</t>
-  </si>
-  <si>
-    <t>http://www.worldscientific.com/worldscinet/ijitdm</t>
-  </si>
-  <si>
-    <t>International Journal of Uncertainty, Fuzziness and Knowledge-Based Systems</t>
-  </si>
-  <si>
-    <t>http://www.worldscientific.com/worldscinet/ijufks</t>
-  </si>
-  <si>
-    <t>Asia-Pacific Journal of Operational Research</t>
-  </si>
-  <si>
-    <t>http://www.worldscientific.com/toc/apjor/0/0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/action/doSearch?AllField=Journal+of+Marketing+Research&amp;startPage=0&amp;sortBy=FullEpubDateField</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Journal of Consumer Research</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBSCO|https://search.ebscohost.com/direct.asp?db=bth&amp;jid=JCR&amp;scope=site</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://academic.oup.com/jcr/issue</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Others</t>
-  </si>
-  <si>
-    <t>Technological and Economic Development of Economy</t>
-  </si>
-  <si>
-    <t>https://journals.vgtu.lt/index.php/TEDE</t>
-  </si>
-  <si>
-    <t>INFORMATICA</t>
-  </si>
-  <si>
-    <t>https://informatica.vu.lt/journal/INFORMATICA/to-appear</t>
-  </si>
-  <si>
-    <t>International Journal of Computers Communications &amp; Control</t>
-  </si>
-  <si>
-    <t>http://univagora.ro/jour/index.php/ijccc/</t>
-  </si>
-  <si>
-    <t>International Journal of Strategic Property Management</t>
-  </si>
-  <si>
-    <t>https://journals.vgtu.lt/index.php/IJSPM</t>
-  </si>
-  <si>
-    <t>Transport</t>
-  </si>
-  <si>
-    <t>https://journals.vgtu.lt/index.php/Transport</t>
-  </si>
-  <si>
-    <t>Transformations in Business &amp; Economics</t>
-  </si>
-  <si>
-    <t>http://www.transformations.knf.vu.lt/</t>
-  </si>
-  <si>
-    <t>Scientia Iranica</t>
-  </si>
-  <si>
-    <t>http://scientiairanica.sharif.edu/?_action=current&amp;_is=Current%20Issue</t>
-  </si>
-  <si>
-    <t>Iranian Journal of Fuzzy Systems</t>
-  </si>
-  <si>
-    <t>http://ijfs.usb.ac.ir/?_action=press&amp;issue=-1&amp;_is=Articles%20in%20Press</t>
-  </si>
-  <si>
-    <t>Kybernetes</t>
-  </si>
-  <si>
-    <t>https://www.emerald.com/insight/publication/issn/0368-492X</t>
-  </si>
-  <si>
-    <t>Intelligent Decision Technologies</t>
-  </si>
-  <si>
-    <t>http://content.iospress.com/journals/intelligent-decision-technologies</t>
-  </si>
-  <si>
-    <t>Fundamenta Informaticae</t>
-  </si>
-  <si>
-    <t>http://content.iospress.com/journals/fundamenta-informaticae</t>
-  </si>
-  <si>
-    <t>Intelligent Data Analysis</t>
-  </si>
-  <si>
-    <t>http://content.iospress.com/journals/intelligent-data-analysis</t>
-  </si>
-  <si>
-    <t>Journal of Smart Environments and Green Computing</t>
-  </si>
-  <si>
-    <t>https://segcjournal.com/journal/archives</t>
-  </si>
-  <si>
-    <t>Journal of Civil Engineering and Management</t>
-  </si>
-  <si>
-    <t>https://journals.vgtu.lt/index.php/JCEM/issue/current</t>
-  </si>
-  <si>
-    <t>中文期刊</t>
-  </si>
-  <si>
-    <t>管理科学学报</t>
-  </si>
-  <si>
-    <t>http://jmsc.tju.edu.cn/ch/index.aspx</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8LJ05z2WKBaal83R1aZsKHhDdcfMpx3UBz-GfhJW-s7MsP1nXNGVxV1DUmvt3bqyaob8lhOefEDtskNzOE_2EpC2gCrA_8RJXiGWDTI_iUNA==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>系统工程理论与实践</t>
-  </si>
-  <si>
-    <t>http://www.sysengi.com/</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=i3PX7_dq32X2Zk0vdxkR-ODkxN-nI3yF4njbEspRx73Nm7WAR7J-vcwM0_OoNx8FEvxGLJCXasn3KAcQ0RARebKAq4xD1pgviZ0U7vSuBvfNMhDxzEeSoA==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>管理世界</t>
-  </si>
-  <si>
-    <t>http://www.mwm.net.cn/web/</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9bPeMF52gorOhVMoCTm_bP4JUtgupb_E88sMy-gsXzFr1P8lBB8uHZukD4Te4RdLMKnj45i1j1MNnPQo45WRUOuqkrMgwUszODdbOWIRUqkg==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>中国管理科学</t>
-  </si>
-  <si>
-    <t>http://www.zgglkx.com</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-JU_du0-bK0lg27F1Oi8b1cNGusZwUOwac7P02Y1arLcSfkZu0L8ZB1IJhn7Fj80XDx2f9_sQ5r3G6IQgpyTe3Y_JDssEju9qAhMsGw3X0qw==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>系统工程学报</t>
-  </si>
-  <si>
-    <t>http://jse.tju.edu.cn</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-NWam7tarWG4WxmWSs2_tcqdiLEz4i3KVdQbtnKLITej4vXhwHRR3aDau0yw8d_IavznXlO9dN3zYuKL_de5S7p2u36GqLdzMfHA3Wg9Wx0w==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>系统管理学报</t>
-  </si>
-  <si>
-    <t>http://xtglxb.sjtu.edu.cn/</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9URZHjnjpZNx894uUc8hEV_8y-XaWbYy_QQKZwrmUaOuHU_Ulmiyfu5w84oSoQ8OSwjHPBK4vEcFxdVksfIHxNuv4CL8S5HTYziOHdCIpK2w==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>管理科学</t>
-  </si>
-  <si>
-    <t>http://glkx.hit.edu.cn/glkxcn/ch/index.aspx</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_ZE6E2FOt_BwppB5uBeXQErN0I5kVHOud5T_DbHM98apuHBLYdN4agXMpq5m9CZr4pnZE4hFnsyANk-8DWJ3fFUdWzB2oij7TzlVIKAxfF6A==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>管理评论</t>
-  </si>
-  <si>
-    <t>http://www.glplzz.com/</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-TCsOxvxdXdlSvw79gRfLC3Qs4Zx8pWINWUiL6dgoj_PFvNjjxeJ-IodjHg3dspx0OB_4yj_j_2YdtzhxiYvBKymQM3Mm052AZyEPIfen2cA==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>管理工程学报</t>
-  </si>
-  <si>
-    <t>http://glgcxb.zju.edu.cn/</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-of79BoeSNOewUhIo96ZMAjN8mFut9UoGSjZTP2iEpFABYwcruA3SHWcybncpeXPbpyxidSxZmHELrN_sWz_TwKPS7pW14Bd4_6sV_an3TIw==&amp;uniplatform=NZKPT; Wanfang|http://c.wanfangdata.com.cn/Periodical-glgcxb.aspx</t>
-  </si>
-  <si>
-    <t>科研管理</t>
-  </si>
-  <si>
-    <t>http://www.kygl.net.cn/CN/volumn/current.shtml</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-suj3LK5xOmewi2RL88KpHw_Y4IWQV_LOZn6OY_pKGmFH9FAohJfOJBLBXlxEnZMv4t3D9HHG9tzRAf1HsRr0LLg2WgmXzxmB0DsRcV4L4UA==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>情报学报</t>
-  </si>
-  <si>
-    <t>http://c.g.wanfangdata.com.cn/Periodical-qbxb.aspx</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8YKwcHxwZXR6_E831nWKL7VA3KAJM_62nvUu58_o090RvVqN70o6VSQkS3qUEV_VUpKVZXPuh6_MSWrBjvD009QGRHA63B8helTMTx8zKObw==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>工程管理科技前沿</t>
-  </si>
-  <si>
-    <t>https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-GAv0jPFKFXS8SEP2Ah0gRdsS1WKdacP65L7Jt8Llj4s_mjmxb0WQ1lZ8cjqzqp-aMY6vqJmqbd4XiZF25Ocq4q4DcD50p7qpvTJKltS_NFw==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-GAv0jPFKFXS8SEP2Ah0gRdsS1WKdacP65L7Jt8Llj4s_mjmxb0WQ1lZ8cjqzqp-aMY6vqJmqbd4XiZF25Ocq4q4DcD50p7qpvTJKltS_NFw==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>运筹与管理</t>
-  </si>
-  <si>
-    <t>http://www.jorms.net/CN/1007-3221/home.shtml</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-imVfP0-dYeXXBrc_IVJAxvFZOMzq3jmwCdvsMpISPOot7nrWj97vgMsjF53RRn6g8m1XptEIkO8hZpt33WgwzXUX2oAJdEwD1eWfkhpcbTQ==&amp;uniplatform=NZKPT; Wanfang|http://c.wanfangdata.com.cn/Periodical-ycygl.aspx</t>
-  </si>
-  <si>
-    <t>南开管理评论</t>
-  </si>
-  <si>
-    <t>http://www.nbronline.cn/ch/index.aspx</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9Ue16OTUg-5EwLDyLEfx1_wPrOxIGe2xH33y5mqsDNofkcaL-y2W7K3uP1LsvOBXr20eEhJFLOhUI4gKsH11k050omDbMZlN9CsaeGMhwMBA==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>管理学报</t>
-  </si>
-  <si>
-    <t>http://manu68.magtech.com.cn/Jwk_glxb/CN/volumn/current.shtml</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8PCnUrD8saRufeUaB7vvWh8ImJB4HeHNeLqW0ePwzGyEPNRCnQsHlbFXGOlO-wcTfqZgKY4hDwsLs-3Tn89zOBbGtw1AAMZyEw5PPM6laErQ==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>工业工程与管理</t>
-  </si>
-  <si>
-    <t>https://gygc.cbpt.cnki.net/WKB2/WebPublication/index.aspx?mid=gygc</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8br7MgEIcFYMQt_ZJBi4Gq5howJvAAN2q5Uw-jRJpkwA6seBfU1WclQ4xGDeYNZADI68ojMDuwRNLC-W9Dialui-wgcg5tuYIT8ESNZSpaSQ==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>系统工程</t>
-  </si>
-  <si>
-    <t>http://www.xitonggongcheng.cn/</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_WFCPnBSQTbCMipV7pzuUWmqJVRmNF8oX6Kjc45ATyApiwW7K32zXQ0P-6LMKJ521dERQpzlafVK7qGUOU45RpQBLI3a7dqVm6V_hSwqA5HQ==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>控制与决策</t>
-  </si>
-  <si>
-    <t>http://kzyjc.alljournals.cn/ch/index.aspx</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9VMm0YxN4tX5yL-EVnsT6PAjZVl9XwIKssVo1NvBga91FGUvekhWuNlMQI0JER059BEkpPkSf2yKf-gU-zpBPmAP0aZmcjFXxTBOO3l4T0hA==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>系统工程与电子技术</t>
-  </si>
-  <si>
-    <t>http://www.sys-ele.com/CN/1001-506X/home.shtml</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_WFCPnBSQTbCMipV7pzuUWmqJVRmNF8oX6Kjc45ATyApiwW7K32zXQ0P-6LMKJ522XKppJFMLpkDt0YeID7jzeew3YqHq1UltKzV8MACc98A==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>中国软科学</t>
-  </si>
-  <si>
-    <t>http://www.cssm.com.cn/ch/index.aspx</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8jySLJU_283KXns0m8yNk0Ce8rmtobTme-1MViCCKsbzSynAlfsvvxkGahZxy_URE-jKLwH5grOgRQ7kKV0KBnSC88LYojIfsOG5GxO7NKdg==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>系统科学与数学</t>
-  </si>
-  <si>
-    <t>http://sysmath.com/jweb_xtkxysx</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-E-p5hVM-T-2-bewhhYzlPKidJWYOorDi1B-PITMAbOL0S7cekgijFCS0nSXq4XQNKt1GbaW3S6VWjdbpFqoGY_EIIuekH5mr8rxzI_HrR7g==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>计量经济学报</t>
-  </si>
-  <si>
-    <t>http://www.cjoe.ac.cn/CN/2096-9732/home.shtml</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9O7KTOAqVcVsRDT7MmQLR8XCOwVreqgSqoJ_mGw8hFdrvny_-zVG3nRwmEQnA8E_SpxQeLOkYd7CxfbKQuxDeda_UEYUS14oC9RQJGSD6dYg==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>自动化学报</t>
-  </si>
-  <si>
-    <t>http://www.aas.net.cn/CN/volumn/current.shtml</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_KyFB5Et1OillJwmuopCWBj5pdqWDmDRaudYAq4j6C1SQ8RskmxnZJipOZnXxhDK_wNDwDjzo_dILEkzq7JyCDiG26p2JrBu__1dKfqF0Hug==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>计算机学报</t>
-  </si>
-  <si>
-    <t>http://cjc.ict.ac.cn/</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9_vxQO77UEmThRI7mhs7_u-tPwE_PVKzc0Y8BhMYBHTzr98uiHz_J7VQEcj0zQgQD69gziJmOh-Y7_MS0eWzVrjAi2cxJHj4AyA5FLhECB7Q==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>计算机研究与发展</t>
-  </si>
-  <si>
-    <t>http://crad.ict.ac.cn/</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh8lGm60BT1S32qMmgQriP9uZ2ShOTZe4_8yW-QQYDij87AjrNp9M_13YGgNGlrNwq-vJCQhJ1KyL0VCjz5laN36JY4u-_EtYQc2NFnjQlP6wg==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>电子学报</t>
-  </si>
-  <si>
-    <t>http://www.ejournal.org.cn/CN/volumn/current.shtml</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/journals/DZXU/detail?uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>软件学报</t>
-  </si>
-  <si>
-    <t>http://www.jos.org.cn/</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh-eSDBBKMj0vAeZF-smiUXPlDeISBrKFJZZ9arNvuLVDlcERM2YiZPI_j0aeLQpFlrUVoLG0JBQXMun-myIj8mt0fvZymwFzAizMqubrnbCDg==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>中国科学: 信息科学</t>
-  </si>
-  <si>
-    <t>https://www.sciengine.com/publisher/scp/journal/SSI?slug=firstpublish</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_wGZ_mUleWCYCON5LbBM4MWv3xigAWN4kttzDDJAGVBd7SeAnjCYVkCmhMZnWmK8p7oIeobAw_ntBHWA0d52ws1dPal6Yqvk_voRKDk5MihA==&amp;uniplatform=NZKPT</t>
-  </si>
-  <si>
-    <t>数据分析与知识发现</t>
-  </si>
-  <si>
-    <t>https://manu44.magtech.com.cn/Jwk_infotech_wk3/CN/2096-3467/home.shtml</t>
-  </si>
-  <si>
-    <t>CNKI|https://navi.cnki.net/knavi/journals/XDTQ/detail</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PNAS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.pnas.org/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1512,157 +1628,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Carlito"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="Carlito"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1675,194 +1650,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1870,357 +1659,187 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -2231,7 +1850,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2259,168 +1878,54 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="JournalListTable" displayName="JournalListTable" ref="A1:F198">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="JournalListTable" displayName="JournalListTable" ref="A1:F205">
   <tableColumns count="6">
-    <tableColumn id="1" name="Category"/>
-    <tableColumn id="2" name="Order"/>
-    <tableColumn id="3" name="Journal"/>
-    <tableColumn id="4" name="URL"/>
-    <tableColumn id="5" name="Extra Links"/>
-    <tableColumn id="6" name="Note"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Category"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Order"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Journal"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="URL"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Extra Links"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2569,14 +2074,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F198"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F205"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -4351,13 +3856,13 @@
         <v>170</v>
       </c>
       <c r="B89" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C89" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D89" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
@@ -4371,13 +3876,13 @@
         <v>170</v>
       </c>
       <c r="B90" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C90" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D90" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E90" t="s">
         <v>10</v>
@@ -4928,19 +4433,19 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>289</v>
+        <v>500</v>
       </c>
       <c r="B118" s="3">
         <v>1</v>
       </c>
       <c r="C118" t="s">
+        <v>289</v>
+      </c>
+      <c r="D118" t="s">
         <v>290</v>
       </c>
-      <c r="D118" t="s">
-        <v>291</v>
-      </c>
       <c r="E118" t="s">
-        <v>10</v>
+        <v>482</v>
       </c>
       <c r="F118" t="s">
         <v>10</v>
@@ -4948,19 +4453,19 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>289</v>
+        <v>500</v>
       </c>
       <c r="B119" s="3">
         <v>2</v>
       </c>
       <c r="C119" t="s">
+        <v>291</v>
+      </c>
+      <c r="D119" t="s">
         <v>292</v>
       </c>
-      <c r="D119" t="s">
-        <v>293</v>
-      </c>
       <c r="E119" t="s">
-        <v>10</v>
+        <v>483</v>
       </c>
       <c r="F119" t="s">
         <v>10</v>
@@ -4968,19 +4473,19 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>289</v>
+        <v>500</v>
       </c>
       <c r="B120" s="3">
         <v>3</v>
       </c>
       <c r="C120" t="s">
+        <v>293</v>
+      </c>
+      <c r="D120" t="s">
         <v>294</v>
       </c>
-      <c r="D120" t="s">
-        <v>295</v>
-      </c>
       <c r="E120" t="s">
-        <v>10</v>
+        <v>484</v>
       </c>
       <c r="F120" t="s">
         <v>10</v>
@@ -4988,19 +4493,19 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>289</v>
+        <v>500</v>
       </c>
       <c r="B121" s="3">
         <v>4</v>
       </c>
       <c r="C121" t="s">
+        <v>295</v>
+      </c>
+      <c r="D121" t="s">
         <v>296</v>
       </c>
-      <c r="D121" t="s">
-        <v>297</v>
-      </c>
       <c r="E121" t="s">
-        <v>10</v>
+        <v>487</v>
       </c>
       <c r="F121" t="s">
         <v>10</v>
@@ -5008,19 +4513,19 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>289</v>
+        <v>500</v>
       </c>
       <c r="B122" s="3">
         <v>5</v>
       </c>
       <c r="C122" t="s">
+        <v>297</v>
+      </c>
+      <c r="D122" t="s">
         <v>298</v>
       </c>
-      <c r="D122" t="s">
-        <v>299</v>
-      </c>
       <c r="E122" t="s">
-        <v>10</v>
+        <v>486</v>
       </c>
       <c r="F122" t="s">
         <v>10</v>
@@ -5028,19 +4533,19 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>289</v>
+        <v>500</v>
       </c>
       <c r="B123" s="3">
         <v>6</v>
       </c>
       <c r="C123" t="s">
+        <v>299</v>
+      </c>
+      <c r="D123" t="s">
         <v>300</v>
       </c>
-      <c r="D123" t="s">
-        <v>301</v>
-      </c>
       <c r="E123" t="s">
-        <v>10</v>
+        <v>485</v>
       </c>
       <c r="F123" t="s">
         <v>10</v>
@@ -5048,19 +4553,19 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>289</v>
+        <v>500</v>
       </c>
       <c r="B124" s="3">
         <v>7</v>
       </c>
       <c r="C124" t="s">
+        <v>301</v>
+      </c>
+      <c r="D124" t="s">
         <v>302</v>
       </c>
-      <c r="D124" t="s">
-        <v>303</v>
-      </c>
       <c r="E124" t="s">
-        <v>10</v>
+        <v>488</v>
       </c>
       <c r="F124" t="s">
         <v>10</v>
@@ -5068,19 +4573,19 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>289</v>
+        <v>500</v>
       </c>
       <c r="B125" s="3">
         <v>8</v>
       </c>
       <c r="C125" t="s">
+        <v>303</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E125" t="s">
         <v>304</v>
-      </c>
-      <c r="D125" t="s">
-        <v>305</v>
-      </c>
-      <c r="E125" t="s">
-        <v>306</v>
       </c>
       <c r="F125" t="s">
         <v>10</v>
@@ -5088,156 +4593,132 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>307</v>
+        <v>500</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C126" t="s">
-        <v>308</v>
-      </c>
-      <c r="D126" t="s">
-        <v>309</v>
+        <v>489</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>493</v>
       </c>
       <c r="E126" t="s">
-        <v>10</v>
-      </c>
-      <c r="F126" t="s">
-        <v>10</v>
+        <v>490</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>307</v>
+        <v>500</v>
       </c>
       <c r="B127" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C127" t="s">
-        <v>310</v>
-      </c>
-      <c r="D127" t="s">
-        <v>311</v>
+        <v>491</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>492</v>
       </c>
       <c r="E127" t="s">
-        <v>10</v>
-      </c>
-      <c r="F127" t="s">
-        <v>10</v>
+        <v>494</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>307</v>
+        <v>500</v>
       </c>
       <c r="B128" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C128" t="s">
-        <v>312</v>
-      </c>
-      <c r="D128" t="s">
-        <v>313</v>
+        <v>498</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>497</v>
       </c>
       <c r="E128" t="s">
-        <v>10</v>
-      </c>
-      <c r="F128" t="s">
-        <v>10</v>
+        <v>495</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>307</v>
+        <v>500</v>
       </c>
       <c r="B129" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C129" t="s">
-        <v>314</v>
-      </c>
-      <c r="D129" t="s">
-        <v>315</v>
+        <v>504</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>507</v>
       </c>
       <c r="E129" t="s">
-        <v>10</v>
-      </c>
-      <c r="F129" t="s">
-        <v>10</v>
+        <v>505</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>307</v>
+        <v>500</v>
       </c>
       <c r="B130" s="3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C130" t="s">
-        <v>316</v>
-      </c>
-      <c r="D130" t="s">
-        <v>317</v>
+        <v>508</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>510</v>
       </c>
       <c r="E130" t="s">
-        <v>10</v>
-      </c>
-      <c r="F130" t="s">
-        <v>10</v>
+        <v>509</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>307</v>
+        <v>500</v>
       </c>
       <c r="B131" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C131" t="s">
-        <v>318</v>
-      </c>
-      <c r="D131" t="s">
-        <v>319</v>
-      </c>
-      <c r="E131" t="s">
-        <v>10</v>
-      </c>
-      <c r="F131" t="s">
-        <v>10</v>
+        <v>496</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>307</v>
+        <v>500</v>
       </c>
       <c r="B132" s="3">
-        <v>7</v>
-      </c>
-      <c r="C132" t="s">
-        <v>320</v>
-      </c>
-      <c r="D132" t="s">
-        <v>321</v>
+        <v>15</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>503</v>
       </c>
       <c r="E132" t="s">
-        <v>10</v>
-      </c>
-      <c r="F132" t="s">
-        <v>10</v>
+        <v>502</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
+        <v>305</v>
+      </c>
+      <c r="B133" s="3">
+        <v>1</v>
+      </c>
+      <c r="C133" t="s">
+        <v>306</v>
+      </c>
+      <c r="D133" t="s">
         <v>307</v>
-      </c>
-      <c r="B133" s="3">
-        <v>8</v>
-      </c>
-      <c r="C133" t="s">
-        <v>322</v>
-      </c>
-      <c r="D133" t="s">
-        <v>323</v>
       </c>
       <c r="E133" t="s">
         <v>10</v>
@@ -5248,16 +4729,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B134" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C134" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="D134" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="E134" t="s">
         <v>10</v>
@@ -5268,16 +4749,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B135" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C135" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="D135" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="E135" t="s">
         <v>10</v>
@@ -5288,16 +4769,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B136" s="3">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C136" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="D136" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="E136" t="s">
         <v>10</v>
@@ -5308,16 +4789,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>330</v>
-      </c>
-      <c r="B137" s="4">
-        <v>1</v>
+        <v>305</v>
+      </c>
+      <c r="B137" s="3">
+        <v>5</v>
       </c>
       <c r="C137" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="D137" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="E137" t="s">
         <v>10</v>
@@ -5328,16 +4809,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>330</v>
-      </c>
-      <c r="B138" s="4">
-        <v>2</v>
+        <v>305</v>
+      </c>
+      <c r="B138" s="3">
+        <v>6</v>
       </c>
       <c r="C138" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="D138" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="E138" t="s">
         <v>10</v>
@@ -5348,16 +4829,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>330</v>
-      </c>
-      <c r="B139" s="4">
-        <v>3</v>
+        <v>305</v>
+      </c>
+      <c r="B139" s="3">
+        <v>7</v>
       </c>
       <c r="C139" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="D139" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="E139" t="s">
         <v>10</v>
@@ -5368,16 +4849,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>330</v>
-      </c>
-      <c r="B140" s="4">
-        <v>4</v>
+        <v>305</v>
+      </c>
+      <c r="B140" s="3">
+        <v>8</v>
       </c>
       <c r="C140" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="D140" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="E140" t="s">
         <v>10</v>
@@ -5388,16 +4869,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>330</v>
-      </c>
-      <c r="B141" s="4">
-        <v>5</v>
+        <v>305</v>
+      </c>
+      <c r="B141" s="3">
+        <v>9</v>
       </c>
       <c r="C141" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="D141" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="E141" t="s">
         <v>10</v>
@@ -5408,16 +4889,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>330</v>
-      </c>
-      <c r="B142" s="4">
-        <v>6</v>
+        <v>305</v>
+      </c>
+      <c r="B142" s="3">
+        <v>10</v>
       </c>
       <c r="C142" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="D142" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
@@ -5428,16 +4909,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>330</v>
-      </c>
-      <c r="B143" s="4">
-        <v>7</v>
+        <v>305</v>
+      </c>
+      <c r="B143" s="3">
+        <v>11</v>
       </c>
       <c r="C143" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="D143" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="E143" t="s">
         <v>10</v>
@@ -5448,17 +4929,17 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
+        <v>328</v>
+      </c>
+      <c r="B144" s="4">
+        <v>1</v>
+      </c>
+      <c r="C144" t="s">
+        <v>329</v>
+      </c>
+      <c r="D144" t="s">
         <v>330</v>
       </c>
-      <c r="B144" s="4">
-        <v>8</v>
-      </c>
-      <c r="C144" t="s">
-        <v>345</v>
-      </c>
-      <c r="D144" t="s">
-        <v>346</v>
-      </c>
       <c r="E144" t="s">
         <v>10</v>
       </c>
@@ -5466,18 +4947,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" ht="14.4" spans="1:6">
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B145" s="4">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C145" t="s">
-        <v>347</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>348</v>
+        <v>331</v>
+      </c>
+      <c r="D145" t="s">
+        <v>332</v>
+      </c>
+      <c r="E145" t="s">
+        <v>10</v>
       </c>
       <c r="F145" t="s">
         <v>10</v>
@@ -5485,16 +4969,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B146" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C146" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="D146" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="E146" t="s">
         <v>10</v>
@@ -5505,16 +4989,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B147" s="4">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C147" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="D147" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="E147" t="s">
         <v>10</v>
@@ -5525,16 +5009,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B148" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C148" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="D148" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="E148" t="s">
         <v>10</v>
@@ -5545,16 +5029,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B149" s="4">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C149" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="D149" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="E149" t="s">
         <v>10</v>
@@ -5565,16 +5049,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B150" s="4">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C150" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="D150" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="E150" t="s">
         <v>10</v>
@@ -5585,16 +5069,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B151" s="4">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C151" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="D151" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="E151" t="s">
         <v>10</v>
@@ -5605,16 +5089,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B152" s="4">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C152" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="D152" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="E152" t="s">
         <v>10</v>
@@ -5625,16 +5109,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B153" s="4">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C153" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="D153" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="E153" t="s">
         <v>10</v>
@@ -5645,16 +5129,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B154" s="4">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C154" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="D154" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="E154" t="s">
         <v>10</v>
@@ -5665,16 +5149,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B155" s="4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C155" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="D155" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="E155" t="s">
         <v>10</v>
@@ -5685,16 +5169,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>369</v>
-      </c>
-      <c r="B156" s="2">
-        <v>1</v>
+        <v>328</v>
+      </c>
+      <c r="B156" s="4">
+        <v>14</v>
       </c>
       <c r="C156" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="D156" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="E156" t="s">
         <v>10</v>
@@ -5705,16 +5189,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>369</v>
-      </c>
-      <c r="B157" s="2">
-        <v>2</v>
+        <v>328</v>
+      </c>
+      <c r="B157" s="4">
+        <v>15</v>
       </c>
       <c r="C157" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="D157" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="E157" t="s">
         <v>10</v>
@@ -5725,16 +5209,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>369</v>
-      </c>
-      <c r="B158" s="2">
-        <v>3</v>
+        <v>328</v>
+      </c>
+      <c r="B158" s="4">
+        <v>16</v>
       </c>
       <c r="C158" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="D158" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="E158" t="s">
         <v>10</v>
@@ -5745,16 +5229,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>369</v>
-      </c>
-      <c r="B159" s="2">
-        <v>4</v>
+        <v>328</v>
+      </c>
+      <c r="B159" s="4">
+        <v>17</v>
       </c>
       <c r="C159" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="D159" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="E159" t="s">
         <v>10</v>
@@ -5765,16 +5249,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>369</v>
-      </c>
-      <c r="B160" s="2">
-        <v>5</v>
+        <v>328</v>
+      </c>
+      <c r="B160" s="4">
+        <v>18</v>
       </c>
       <c r="C160" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="D160" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="E160" t="s">
         <v>10</v>
@@ -5785,16 +5269,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>369</v>
-      </c>
-      <c r="B161" s="2">
-        <v>6</v>
+        <v>328</v>
+      </c>
+      <c r="B161" s="4">
+        <v>19</v>
       </c>
       <c r="C161" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="D161" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
@@ -5805,36 +5289,30 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>369</v>
+        <v>511</v>
       </c>
       <c r="B162" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C162" t="s">
-        <v>382</v>
-      </c>
-      <c r="D162" t="s">
-        <v>383</v>
-      </c>
-      <c r="E162" t="s">
-        <v>10</v>
-      </c>
-      <c r="F162" t="s">
-        <v>10</v>
+        <v>512</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B163" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C163" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="D163" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="E163" t="s">
         <v>10</v>
@@ -5845,16 +5323,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
+        <v>365</v>
+      </c>
+      <c r="B164" s="2">
+        <v>3</v>
+      </c>
+      <c r="C164" t="s">
+        <v>368</v>
+      </c>
+      <c r="D164" t="s">
         <v>369</v>
-      </c>
-      <c r="B164" s="2">
-        <v>9</v>
-      </c>
-      <c r="C164" t="s">
-        <v>386</v>
-      </c>
-      <c r="D164" t="s">
-        <v>387</v>
       </c>
       <c r="E164" t="s">
         <v>10</v>
@@ -5865,16 +5343,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B165" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C165" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="D165" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="E165" t="s">
         <v>10</v>
@@ -5885,16 +5363,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B166" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C166" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="D166" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="E166" t="s">
         <v>10</v>
@@ -5905,16 +5383,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B167" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C167" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="D167" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="E167" t="s">
         <v>10</v>
@@ -5925,16 +5403,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B168" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="D168" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="E168" t="s">
         <v>10</v>
@@ -5945,16 +5423,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B169" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="D169" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="E169" t="s">
         <v>10</v>
@@ -5965,19 +5443,19 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>398</v>
-      </c>
-      <c r="B170" t="s">
-        <v>7</v>
+        <v>365</v>
+      </c>
+      <c r="B170" s="2">
+        <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="D170" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="E170" t="s">
-        <v>401</v>
+        <v>10</v>
       </c>
       <c r="F170" t="s">
         <v>10</v>
@@ -5985,19 +5463,19 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>398</v>
-      </c>
-      <c r="B171" t="s">
-        <v>11</v>
+        <v>365</v>
+      </c>
+      <c r="B171" s="2">
+        <v>10</v>
       </c>
       <c r="C171" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="D171" t="s">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="E171" t="s">
-        <v>404</v>
+        <v>10</v>
       </c>
       <c r="F171" t="s">
         <v>10</v>
@@ -6005,19 +5483,19 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>398</v>
-      </c>
-      <c r="B172" t="s">
-        <v>14</v>
+        <v>365</v>
+      </c>
+      <c r="B172" s="2">
+        <v>11</v>
       </c>
       <c r="C172" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="D172" t="s">
-        <v>406</v>
+        <v>385</v>
       </c>
       <c r="E172" t="s">
-        <v>407</v>
+        <v>10</v>
       </c>
       <c r="F172" t="s">
         <v>10</v>
@@ -6025,19 +5503,19 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>398</v>
-      </c>
-      <c r="B173" t="s">
-        <v>17</v>
+        <v>365</v>
+      </c>
+      <c r="B173" s="2">
+        <v>12</v>
       </c>
       <c r="C173" t="s">
-        <v>408</v>
+        <v>386</v>
       </c>
       <c r="D173" t="s">
-        <v>409</v>
+        <v>387</v>
       </c>
       <c r="E173" t="s">
-        <v>410</v>
+        <v>10</v>
       </c>
       <c r="F173" t="s">
         <v>10</v>
@@ -6045,19 +5523,19 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>398</v>
-      </c>
-      <c r="B174" t="s">
-        <v>20</v>
+        <v>365</v>
+      </c>
+      <c r="B174" s="2">
+        <v>13</v>
       </c>
       <c r="C174" t="s">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="D174" t="s">
-        <v>412</v>
+        <v>389</v>
       </c>
       <c r="E174" t="s">
-        <v>413</v>
+        <v>10</v>
       </c>
       <c r="F174" t="s">
         <v>10</v>
@@ -6065,19 +5543,19 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>398</v>
-      </c>
-      <c r="B175" t="s">
-        <v>23</v>
+        <v>365</v>
+      </c>
+      <c r="B175" s="2">
+        <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="D175" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="E175" t="s">
-        <v>416</v>
+        <v>10</v>
       </c>
       <c r="F175" t="s">
         <v>10</v>
@@ -6085,19 +5563,19 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>398</v>
-      </c>
-      <c r="B176" t="s">
-        <v>26</v>
+        <v>365</v>
+      </c>
+      <c r="B176" s="4">
+        <v>15</v>
       </c>
       <c r="C176" t="s">
-        <v>417</v>
+        <v>392</v>
       </c>
       <c r="D176" t="s">
-        <v>418</v>
+        <v>393</v>
       </c>
       <c r="E176" t="s">
-        <v>419</v>
+        <v>10</v>
       </c>
       <c r="F176" t="s">
         <v>10</v>
@@ -6105,19 +5583,19 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B177" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C177" t="s">
-        <v>420</v>
+        <v>395</v>
       </c>
       <c r="D177" t="s">
-        <v>421</v>
+        <v>396</v>
       </c>
       <c r="E177" t="s">
-        <v>422</v>
+        <v>397</v>
       </c>
       <c r="F177" t="s">
         <v>10</v>
@@ -6125,19 +5603,19 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
+        <v>394</v>
+      </c>
+      <c r="B178" t="s">
+        <v>11</v>
+      </c>
+      <c r="C178" t="s">
         <v>398</v>
       </c>
-      <c r="B178" t="s">
-        <v>32</v>
-      </c>
-      <c r="C178" t="s">
-        <v>423</v>
-      </c>
       <c r="D178" t="s">
-        <v>424</v>
+        <v>399</v>
       </c>
       <c r="E178" t="s">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="F178" t="s">
         <v>10</v>
@@ -6145,19 +5623,19 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>398</v>
-      </c>
-      <c r="B179" s="2">
-        <v>10</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>426</v>
+        <v>394</v>
+      </c>
+      <c r="B179" t="s">
+        <v>14</v>
+      </c>
+      <c r="C179" t="s">
+        <v>401</v>
       </c>
       <c r="D179" t="s">
-        <v>427</v>
+        <v>402</v>
       </c>
       <c r="E179" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="F179" t="s">
         <v>10</v>
@@ -6165,19 +5643,19 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>398</v>
-      </c>
-      <c r="B180" s="2">
-        <v>11</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>429</v>
+        <v>394</v>
+      </c>
+      <c r="B180" t="s">
+        <v>17</v>
+      </c>
+      <c r="C180" t="s">
+        <v>404</v>
       </c>
       <c r="D180" t="s">
-        <v>430</v>
+        <v>405</v>
       </c>
       <c r="E180" t="s">
-        <v>431</v>
+        <v>406</v>
       </c>
       <c r="F180" t="s">
         <v>10</v>
@@ -6185,19 +5663,19 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>398</v>
-      </c>
-      <c r="B181" s="2">
-        <v>12</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>432</v>
+        <v>394</v>
+      </c>
+      <c r="B181" t="s">
+        <v>20</v>
+      </c>
+      <c r="C181" t="s">
+        <v>407</v>
       </c>
       <c r="D181" t="s">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="E181" t="s">
-        <v>434</v>
+        <v>409</v>
       </c>
       <c r="F181" t="s">
         <v>10</v>
@@ -6205,19 +5683,19 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>398</v>
-      </c>
-      <c r="B182" s="2">
-        <v>13</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>435</v>
+        <v>394</v>
+      </c>
+      <c r="B182" t="s">
+        <v>23</v>
+      </c>
+      <c r="C182" t="s">
+        <v>410</v>
       </c>
       <c r="D182" t="s">
-        <v>436</v>
+        <v>411</v>
       </c>
       <c r="E182" t="s">
-        <v>437</v>
+        <v>412</v>
       </c>
       <c r="F182" t="s">
         <v>10</v>
@@ -6225,19 +5703,19 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B183" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C183" t="s">
-        <v>438</v>
+        <v>413</v>
       </c>
       <c r="D183" t="s">
-        <v>439</v>
+        <v>414</v>
       </c>
       <c r="E183" t="s">
-        <v>440</v>
+        <v>415</v>
       </c>
       <c r="F183" t="s">
         <v>10</v>
@@ -6245,19 +5723,19 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B184" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C184" t="s">
-        <v>441</v>
+        <v>416</v>
       </c>
       <c r="D184" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="E184" t="s">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="F184" t="s">
         <v>10</v>
@@ -6265,19 +5743,19 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B185" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C185" t="s">
-        <v>444</v>
+        <v>419</v>
       </c>
       <c r="D185" t="s">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="E185" t="s">
-        <v>446</v>
+        <v>421</v>
       </c>
       <c r="F185" t="s">
         <v>10</v>
@@ -6285,19 +5763,19 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>398</v>
-      </c>
-      <c r="B186" t="s">
-        <v>56</v>
-      </c>
-      <c r="C186" t="s">
-        <v>447</v>
+        <v>394</v>
+      </c>
+      <c r="B186" s="2">
+        <v>10</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>422</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>423</v>
       </c>
       <c r="E186" t="s">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="F186" t="s">
         <v>10</v>
@@ -6305,19 +5783,19 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>398</v>
-      </c>
-      <c r="B187" t="s">
-        <v>59</v>
-      </c>
-      <c r="C187" t="s">
-        <v>450</v>
+        <v>394</v>
+      </c>
+      <c r="B187" s="2">
+        <v>11</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>425</v>
       </c>
       <c r="D187" t="s">
-        <v>451</v>
+        <v>426</v>
       </c>
       <c r="E187" t="s">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="F187" t="s">
         <v>10</v>
@@ -6325,19 +5803,19 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>398</v>
-      </c>
-      <c r="B188" t="s">
-        <v>62</v>
-      </c>
-      <c r="C188" t="s">
-        <v>453</v>
+        <v>394</v>
+      </c>
+      <c r="B188" s="2">
+        <v>12</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>428</v>
       </c>
       <c r="D188" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="E188" t="s">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="F188" t="s">
         <v>10</v>
@@ -6345,19 +5823,19 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>398</v>
-      </c>
-      <c r="B189" t="s">
-        <v>65</v>
-      </c>
-      <c r="C189" t="s">
-        <v>456</v>
+        <v>394</v>
+      </c>
+      <c r="B189" s="2">
+        <v>13</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>431</v>
       </c>
       <c r="D189" t="s">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="E189" t="s">
-        <v>458</v>
+        <v>433</v>
       </c>
       <c r="F189" t="s">
         <v>10</v>
@@ -6365,19 +5843,19 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B190" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="C190" t="s">
-        <v>459</v>
+        <v>434</v>
       </c>
       <c r="D190" t="s">
-        <v>460</v>
+        <v>435</v>
       </c>
       <c r="E190" t="s">
-        <v>461</v>
+        <v>436</v>
       </c>
       <c r="F190" t="s">
         <v>10</v>
@@ -6385,19 +5863,19 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B191" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C191" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="D191" t="s">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="E191" t="s">
-        <v>464</v>
+        <v>439</v>
       </c>
       <c r="F191" t="s">
         <v>10</v>
@@ -6405,19 +5883,19 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B192" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C192" t="s">
-        <v>465</v>
+        <v>440</v>
       </c>
       <c r="D192" t="s">
-        <v>466</v>
+        <v>441</v>
       </c>
       <c r="E192" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="F192" t="s">
         <v>10</v>
@@ -6425,19 +5903,19 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B193" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C193" t="s">
-        <v>468</v>
+        <v>443</v>
       </c>
       <c r="D193" t="s">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="E193" t="s">
-        <v>470</v>
+        <v>445</v>
       </c>
       <c r="F193" t="s">
         <v>10</v>
@@ -6445,19 +5923,19 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B194" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="C194" t="s">
-        <v>471</v>
+        <v>446</v>
       </c>
       <c r="D194" t="s">
-        <v>472</v>
+        <v>447</v>
       </c>
       <c r="E194" t="s">
-        <v>473</v>
+        <v>448</v>
       </c>
       <c r="F194" t="s">
         <v>10</v>
@@ -6465,19 +5943,19 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B195" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C195" t="s">
-        <v>474</v>
+        <v>449</v>
       </c>
       <c r="D195" t="s">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="E195" t="s">
-        <v>476</v>
+        <v>451</v>
       </c>
       <c r="F195" t="s">
         <v>10</v>
@@ -6485,19 +5963,19 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B196" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C196" t="s">
-        <v>477</v>
+        <v>452</v>
       </c>
       <c r="D196" t="s">
-        <v>478</v>
+        <v>453</v>
       </c>
       <c r="E196" t="s">
-        <v>479</v>
+        <v>454</v>
       </c>
       <c r="F196" t="s">
         <v>10</v>
@@ -6505,19 +5983,19 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B197" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="C197" t="s">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="D197" t="s">
-        <v>481</v>
+        <v>456</v>
       </c>
       <c r="E197" t="s">
-        <v>482</v>
+        <v>457</v>
       </c>
       <c r="F197" t="s">
         <v>10</v>
@@ -6525,27 +6003,167 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B198" t="s">
+        <v>71</v>
+      </c>
+      <c r="C198" t="s">
+        <v>458</v>
+      </c>
+      <c r="D198" t="s">
+        <v>459</v>
+      </c>
+      <c r="E198" t="s">
+        <v>460</v>
+      </c>
+      <c r="F198" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" t="s">
+        <v>394</v>
+      </c>
+      <c r="B199" t="s">
+        <v>74</v>
+      </c>
+      <c r="C199" t="s">
+        <v>461</v>
+      </c>
+      <c r="D199" t="s">
+        <v>462</v>
+      </c>
+      <c r="E199" t="s">
+        <v>463</v>
+      </c>
+      <c r="F199" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" t="s">
+        <v>394</v>
+      </c>
+      <c r="B200" t="s">
+        <v>77</v>
+      </c>
+      <c r="C200" t="s">
+        <v>464</v>
+      </c>
+      <c r="D200" t="s">
+        <v>465</v>
+      </c>
+      <c r="E200" t="s">
+        <v>466</v>
+      </c>
+      <c r="F200" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" t="s">
+        <v>394</v>
+      </c>
+      <c r="B201" t="s">
+        <v>80</v>
+      </c>
+      <c r="C201" t="s">
+        <v>467</v>
+      </c>
+      <c r="D201" t="s">
+        <v>468</v>
+      </c>
+      <c r="E201" t="s">
+        <v>469</v>
+      </c>
+      <c r="F201" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" t="s">
+        <v>394</v>
+      </c>
+      <c r="B202" t="s">
+        <v>83</v>
+      </c>
+      <c r="C202" t="s">
+        <v>470</v>
+      </c>
+      <c r="D202" t="s">
+        <v>471</v>
+      </c>
+      <c r="E202" t="s">
+        <v>472</v>
+      </c>
+      <c r="F202" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" t="s">
+        <v>394</v>
+      </c>
+      <c r="B203" t="s">
+        <v>86</v>
+      </c>
+      <c r="C203" t="s">
+        <v>473</v>
+      </c>
+      <c r="D203" t="s">
+        <v>474</v>
+      </c>
+      <c r="E203" t="s">
+        <v>475</v>
+      </c>
+      <c r="F203" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" t="s">
+        <v>394</v>
+      </c>
+      <c r="B204" t="s">
+        <v>89</v>
+      </c>
+      <c r="C204" t="s">
+        <v>476</v>
+      </c>
+      <c r="D204" t="s">
+        <v>477</v>
+      </c>
+      <c r="E204" t="s">
+        <v>478</v>
+      </c>
+      <c r="F204" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" t="s">
+        <v>394</v>
+      </c>
+      <c r="B205" t="s">
         <v>92</v>
       </c>
-      <c r="C198" t="s">
-        <v>483</v>
-      </c>
-      <c r="D198" t="s">
-        <v>484</v>
-      </c>
-      <c r="E198" t="s">
-        <v>485</v>
-      </c>
-      <c r="F198" t="s">
+      <c r="C205" t="s">
+        <v>479</v>
+      </c>
+      <c r="D205" t="s">
+        <v>480</v>
+      </c>
+      <c r="E205" t="s">
+        <v>481</v>
+      </c>
+      <c r="F205" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/journal/journal_list.xlsx
+++ b/journal/journal_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAE8D9A-52EA-47B2-98B5-AFFAD8CB23AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A22F053C-70B1-4A16-96E0-C734AC6EFCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="514">
   <si>
     <t>Category</t>
   </si>
@@ -1277,9 +1277,6 @@
     <t>管理科学</t>
   </si>
   <si>
-    <t>http://glkx.hit.edu.cn/glkxcn/ch/index.aspx</t>
-  </si>
-  <si>
     <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh_ZE6E2FOt_BwppB5uBeXQErN0I5kVHOud5T_DbHM98apuHBLYdN4agXMpq5m9CZr4pnZE4hFnsyANk-8DWJ3fFUdWzB2oij7TzlVIKAxfF6A==&amp;uniplatform=NZKPT</t>
   </si>
   <si>
@@ -1338,9 +1335,6 @@
   </si>
   <si>
     <t>南开管理评论</t>
-  </si>
-  <si>
-    <t>http://www.nbronline.cn/ch/index.aspx</t>
   </si>
   <si>
     <t>CNKI|https://navi.cnki.net/knavi/detail?p=lKTCeAGFZh9Ue16OTUg-5EwLDyLEfx1_wPrOxIGe2xH33y5mqsDNofkcaL-y2W7K3uP1LsvOBXr20eEhJFLOhUI4gKsH11k050omDbMZlN9CsaeGMhwMBA==&amp;uniplatform=NZKPT</t>
@@ -1606,6 +1600,14 @@
   </si>
   <si>
     <t>https://www.pnas.org/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://nbr.nankai.edu.cn/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://glkx.hit.edu.cn</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -4433,7 +4435,7 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B118" s="3">
         <v>1</v>
@@ -4445,7 +4447,7 @@
         <v>290</v>
       </c>
       <c r="E118" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F118" t="s">
         <v>10</v>
@@ -4453,7 +4455,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B119" s="3">
         <v>2</v>
@@ -4465,7 +4467,7 @@
         <v>292</v>
       </c>
       <c r="E119" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F119" t="s">
         <v>10</v>
@@ -4473,7 +4475,7 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B120" s="3">
         <v>3</v>
@@ -4485,7 +4487,7 @@
         <v>294</v>
       </c>
       <c r="E120" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F120" t="s">
         <v>10</v>
@@ -4493,7 +4495,7 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B121" s="3">
         <v>4</v>
@@ -4505,7 +4507,7 @@
         <v>296</v>
       </c>
       <c r="E121" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F121" t="s">
         <v>10</v>
@@ -4513,7 +4515,7 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B122" s="3">
         <v>5</v>
@@ -4525,7 +4527,7 @@
         <v>298</v>
       </c>
       <c r="E122" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F122" t="s">
         <v>10</v>
@@ -4533,7 +4535,7 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B123" s="3">
         <v>6</v>
@@ -4545,7 +4547,7 @@
         <v>300</v>
       </c>
       <c r="E123" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F123" t="s">
         <v>10</v>
@@ -4553,7 +4555,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B124" s="3">
         <v>7</v>
@@ -4565,7 +4567,7 @@
         <v>302</v>
       </c>
       <c r="E124" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F124" t="s">
         <v>10</v>
@@ -4573,7 +4575,7 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B125" s="3">
         <v>8</v>
@@ -4582,7 +4584,7 @@
         <v>303</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E125" t="s">
         <v>304</v>
@@ -4593,118 +4595,118 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B126" s="3">
         <v>9</v>
       </c>
       <c r="C126" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E126" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B127" s="3">
         <v>10</v>
       </c>
       <c r="C127" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D127" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="E127" t="s">
         <v>492</v>
-      </c>
-      <c r="E127" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B128" s="3">
         <v>11</v>
       </c>
       <c r="C128" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E128" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B129" s="3">
         <v>12</v>
       </c>
       <c r="C129" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E129" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B130" s="3">
         <v>13</v>
       </c>
       <c r="C130" t="s">
+        <v>506</v>
+      </c>
+      <c r="D130" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="D130" s="5" t="s">
-        <v>510</v>
-      </c>
       <c r="E130" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B131" s="3">
         <v>14</v>
       </c>
       <c r="C131" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B132" s="3">
         <v>15</v>
       </c>
       <c r="C132" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="D132" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="D132" s="5" t="s">
-        <v>503</v>
-      </c>
       <c r="E132" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -5289,16 +5291,16 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B162" s="2">
         <v>1</v>
       </c>
       <c r="C162" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -5711,11 +5713,11 @@
       <c r="C183" t="s">
         <v>413</v>
       </c>
-      <c r="D183" t="s">
+      <c r="D183" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="E183" t="s">
         <v>414</v>
-      </c>
-      <c r="E183" t="s">
-        <v>415</v>
       </c>
       <c r="F183" t="s">
         <v>10</v>
@@ -5729,13 +5731,13 @@
         <v>29</v>
       </c>
       <c r="C184" t="s">
+        <v>415</v>
+      </c>
+      <c r="D184" t="s">
         <v>416</v>
       </c>
-      <c r="D184" t="s">
+      <c r="E184" t="s">
         <v>417</v>
-      </c>
-      <c r="E184" t="s">
-        <v>418</v>
       </c>
       <c r="F184" t="s">
         <v>10</v>
@@ -5749,13 +5751,13 @@
         <v>32</v>
       </c>
       <c r="C185" t="s">
+        <v>418</v>
+      </c>
+      <c r="D185" t="s">
         <v>419</v>
       </c>
-      <c r="D185" t="s">
+      <c r="E185" t="s">
         <v>420</v>
-      </c>
-      <c r="E185" t="s">
-        <v>421</v>
       </c>
       <c r="F185" t="s">
         <v>10</v>
@@ -5769,13 +5771,13 @@
         <v>10</v>
       </c>
       <c r="C186" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D186" t="s">
         <v>422</v>
       </c>
-      <c r="D186" t="s">
+      <c r="E186" t="s">
         <v>423</v>
-      </c>
-      <c r="E186" t="s">
-        <v>424</v>
       </c>
       <c r="F186" t="s">
         <v>10</v>
@@ -5789,13 +5791,13 @@
         <v>11</v>
       </c>
       <c r="C187" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D187" t="s">
         <v>425</v>
       </c>
-      <c r="D187" t="s">
+      <c r="E187" t="s">
         <v>426</v>
-      </c>
-      <c r="E187" t="s">
-        <v>427</v>
       </c>
       <c r="F187" t="s">
         <v>10</v>
@@ -5809,13 +5811,13 @@
         <v>12</v>
       </c>
       <c r="C188" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D188" t="s">
         <v>428</v>
       </c>
-      <c r="D188" t="s">
+      <c r="E188" t="s">
         <v>429</v>
-      </c>
-      <c r="E188" t="s">
-        <v>430</v>
       </c>
       <c r="F188" t="s">
         <v>10</v>
@@ -5829,13 +5831,13 @@
         <v>13</v>
       </c>
       <c r="C189" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D189" t="s">
         <v>431</v>
       </c>
-      <c r="D189" t="s">
+      <c r="E189" t="s">
         <v>432</v>
-      </c>
-      <c r="E189" t="s">
-        <v>433</v>
       </c>
       <c r="F189" t="s">
         <v>10</v>
@@ -5849,13 +5851,13 @@
         <v>35</v>
       </c>
       <c r="C190" t="s">
+        <v>433</v>
+      </c>
+      <c r="D190" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="E190" t="s">
         <v>434</v>
-      </c>
-      <c r="D190" t="s">
-        <v>435</v>
-      </c>
-      <c r="E190" t="s">
-        <v>436</v>
       </c>
       <c r="F190" t="s">
         <v>10</v>
@@ -5869,13 +5871,13 @@
         <v>50</v>
       </c>
       <c r="C191" t="s">
+        <v>435</v>
+      </c>
+      <c r="D191" t="s">
+        <v>436</v>
+      </c>
+      <c r="E191" t="s">
         <v>437</v>
-      </c>
-      <c r="D191" t="s">
-        <v>438</v>
-      </c>
-      <c r="E191" t="s">
-        <v>439</v>
       </c>
       <c r="F191" t="s">
         <v>10</v>
@@ -5889,13 +5891,13 @@
         <v>53</v>
       </c>
       <c r="C192" t="s">
+        <v>438</v>
+      </c>
+      <c r="D192" t="s">
+        <v>439</v>
+      </c>
+      <c r="E192" t="s">
         <v>440</v>
-      </c>
-      <c r="D192" t="s">
-        <v>441</v>
-      </c>
-      <c r="E192" t="s">
-        <v>442</v>
       </c>
       <c r="F192" t="s">
         <v>10</v>
@@ -5909,13 +5911,13 @@
         <v>56</v>
       </c>
       <c r="C193" t="s">
+        <v>441</v>
+      </c>
+      <c r="D193" t="s">
+        <v>442</v>
+      </c>
+      <c r="E193" t="s">
         <v>443</v>
-      </c>
-      <c r="D193" t="s">
-        <v>444</v>
-      </c>
-      <c r="E193" t="s">
-        <v>445</v>
       </c>
       <c r="F193" t="s">
         <v>10</v>
@@ -5929,13 +5931,13 @@
         <v>59</v>
       </c>
       <c r="C194" t="s">
+        <v>444</v>
+      </c>
+      <c r="D194" t="s">
+        <v>445</v>
+      </c>
+      <c r="E194" t="s">
         <v>446</v>
-      </c>
-      <c r="D194" t="s">
-        <v>447</v>
-      </c>
-      <c r="E194" t="s">
-        <v>448</v>
       </c>
       <c r="F194" t="s">
         <v>10</v>
@@ -5949,13 +5951,13 @@
         <v>62</v>
       </c>
       <c r="C195" t="s">
+        <v>447</v>
+      </c>
+      <c r="D195" t="s">
+        <v>448</v>
+      </c>
+      <c r="E195" t="s">
         <v>449</v>
-      </c>
-      <c r="D195" t="s">
-        <v>450</v>
-      </c>
-      <c r="E195" t="s">
-        <v>451</v>
       </c>
       <c r="F195" t="s">
         <v>10</v>
@@ -5969,13 +5971,13 @@
         <v>65</v>
       </c>
       <c r="C196" t="s">
+        <v>450</v>
+      </c>
+      <c r="D196" t="s">
+        <v>451</v>
+      </c>
+      <c r="E196" t="s">
         <v>452</v>
-      </c>
-      <c r="D196" t="s">
-        <v>453</v>
-      </c>
-      <c r="E196" t="s">
-        <v>454</v>
       </c>
       <c r="F196" t="s">
         <v>10</v>
@@ -5989,13 +5991,13 @@
         <v>68</v>
       </c>
       <c r="C197" t="s">
+        <v>453</v>
+      </c>
+      <c r="D197" t="s">
+        <v>454</v>
+      </c>
+      <c r="E197" t="s">
         <v>455</v>
-      </c>
-      <c r="D197" t="s">
-        <v>456</v>
-      </c>
-      <c r="E197" t="s">
-        <v>457</v>
       </c>
       <c r="F197" t="s">
         <v>10</v>
@@ -6009,13 +6011,13 @@
         <v>71</v>
       </c>
       <c r="C198" t="s">
+        <v>456</v>
+      </c>
+      <c r="D198" t="s">
+        <v>457</v>
+      </c>
+      <c r="E198" t="s">
         <v>458</v>
-      </c>
-      <c r="D198" t="s">
-        <v>459</v>
-      </c>
-      <c r="E198" t="s">
-        <v>460</v>
       </c>
       <c r="F198" t="s">
         <v>10</v>
@@ -6029,13 +6031,13 @@
         <v>74</v>
       </c>
       <c r="C199" t="s">
+        <v>459</v>
+      </c>
+      <c r="D199" t="s">
+        <v>460</v>
+      </c>
+      <c r="E199" t="s">
         <v>461</v>
-      </c>
-      <c r="D199" t="s">
-        <v>462</v>
-      </c>
-      <c r="E199" t="s">
-        <v>463</v>
       </c>
       <c r="F199" t="s">
         <v>10</v>
@@ -6049,13 +6051,13 @@
         <v>77</v>
       </c>
       <c r="C200" t="s">
+        <v>462</v>
+      </c>
+      <c r="D200" t="s">
+        <v>463</v>
+      </c>
+      <c r="E200" t="s">
         <v>464</v>
-      </c>
-      <c r="D200" t="s">
-        <v>465</v>
-      </c>
-      <c r="E200" t="s">
-        <v>466</v>
       </c>
       <c r="F200" t="s">
         <v>10</v>
@@ -6069,13 +6071,13 @@
         <v>80</v>
       </c>
       <c r="C201" t="s">
+        <v>465</v>
+      </c>
+      <c r="D201" t="s">
+        <v>466</v>
+      </c>
+      <c r="E201" t="s">
         <v>467</v>
-      </c>
-      <c r="D201" t="s">
-        <v>468</v>
-      </c>
-      <c r="E201" t="s">
-        <v>469</v>
       </c>
       <c r="F201" t="s">
         <v>10</v>
@@ -6089,13 +6091,13 @@
         <v>83</v>
       </c>
       <c r="C202" t="s">
+        <v>468</v>
+      </c>
+      <c r="D202" t="s">
+        <v>469</v>
+      </c>
+      <c r="E202" t="s">
         <v>470</v>
-      </c>
-      <c r="D202" t="s">
-        <v>471</v>
-      </c>
-      <c r="E202" t="s">
-        <v>472</v>
       </c>
       <c r="F202" t="s">
         <v>10</v>
@@ -6109,13 +6111,13 @@
         <v>86</v>
       </c>
       <c r="C203" t="s">
+        <v>471</v>
+      </c>
+      <c r="D203" t="s">
+        <v>472</v>
+      </c>
+      <c r="E203" t="s">
         <v>473</v>
-      </c>
-      <c r="D203" t="s">
-        <v>474</v>
-      </c>
-      <c r="E203" t="s">
-        <v>475</v>
       </c>
       <c r="F203" t="s">
         <v>10</v>
@@ -6129,13 +6131,13 @@
         <v>89</v>
       </c>
       <c r="C204" t="s">
+        <v>474</v>
+      </c>
+      <c r="D204" t="s">
+        <v>475</v>
+      </c>
+      <c r="E204" t="s">
         <v>476</v>
-      </c>
-      <c r="D204" t="s">
-        <v>477</v>
-      </c>
-      <c r="E204" t="s">
-        <v>478</v>
       </c>
       <c r="F204" t="s">
         <v>10</v>
@@ -6149,13 +6151,13 @@
         <v>92</v>
       </c>
       <c r="C205" t="s">
+        <v>477</v>
+      </c>
+      <c r="D205" t="s">
+        <v>478</v>
+      </c>
+      <c r="E205" t="s">
         <v>479</v>
-      </c>
-      <c r="D205" t="s">
-        <v>480</v>
-      </c>
-      <c r="E205" t="s">
-        <v>481</v>
       </c>
       <c r="F205" t="s">
         <v>10</v>

--- a/journal/journal_list.xlsx
+++ b/journal/journal_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A22F053C-70B1-4A16-96E0-C734AC6EFCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CFFC13-1631-4BAA-BC03-1B4953E819A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -494,9 +494,6 @@
     <t>International Journal of Contemporary Hospitality Management</t>
   </si>
   <si>
-    <t>https://www.emerald.com/insight/publication/issn/0959-6119#earlycite</t>
-  </si>
-  <si>
     <t>Information Technology &amp; Tourism</t>
   </si>
   <si>
@@ -1608,6 +1605,10 @@
   </si>
   <si>
     <t>http://glkx.hit.edu.cn</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.emerald.com/ijchm/earlycite</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1615,7 +1616,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1635,6 +1636,13 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Carlito"/>
       <charset val="134"/>
     </font>
@@ -1662,13 +1670,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1688,10 +1699,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -3123,8 +3136,8 @@
       <c r="C52" t="s">
         <v>152</v>
       </c>
-      <c r="D52" t="s">
-        <v>153</v>
+      <c r="D52" s="7" t="s">
+        <v>513</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
@@ -3141,10 +3154,10 @@
         <v>32</v>
       </c>
       <c r="C53" t="s">
+        <v>153</v>
+      </c>
+      <c r="D53" t="s">
         <v>154</v>
-      </c>
-      <c r="D53" t="s">
-        <v>155</v>
       </c>
       <c r="E53" t="s">
         <v>10</v>
@@ -3161,10 +3174,10 @@
         <v>35</v>
       </c>
       <c r="C54" t="s">
+        <v>155</v>
+      </c>
+      <c r="D54" t="s">
         <v>156</v>
-      </c>
-      <c r="D54" t="s">
-        <v>157</v>
       </c>
       <c r="E54" t="s">
         <v>10</v>
@@ -3181,10 +3194,10 @@
         <v>38</v>
       </c>
       <c r="C55" t="s">
+        <v>157</v>
+      </c>
+      <c r="D55" t="s">
         <v>158</v>
-      </c>
-      <c r="D55" t="s">
-        <v>159</v>
       </c>
       <c r="E55" t="s">
         <v>10</v>
@@ -3201,10 +3214,10 @@
         <v>41</v>
       </c>
       <c r="C56" t="s">
+        <v>159</v>
+      </c>
+      <c r="D56" t="s">
         <v>160</v>
-      </c>
-      <c r="D56" t="s">
-        <v>161</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
@@ -3221,10 +3234,10 @@
         <v>44</v>
       </c>
       <c r="C57" t="s">
+        <v>161</v>
+      </c>
+      <c r="D57" t="s">
         <v>162</v>
-      </c>
-      <c r="D57" t="s">
-        <v>163</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
@@ -3241,10 +3254,10 @@
         <v>47</v>
       </c>
       <c r="C58" t="s">
+        <v>163</v>
+      </c>
+      <c r="D58" t="s">
         <v>164</v>
-      </c>
-      <c r="D58" t="s">
-        <v>165</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
@@ -3261,10 +3274,10 @@
         <v>50</v>
       </c>
       <c r="C59" t="s">
+        <v>165</v>
+      </c>
+      <c r="D59" t="s">
         <v>166</v>
-      </c>
-      <c r="D59" t="s">
-        <v>167</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
@@ -3281,10 +3294,10 @@
         <v>53</v>
       </c>
       <c r="C60" t="s">
+        <v>167</v>
+      </c>
+      <c r="D60" t="s">
         <v>168</v>
-      </c>
-      <c r="D60" t="s">
-        <v>169</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
@@ -3295,16 +3308,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B61" t="s">
         <v>7</v>
       </c>
       <c r="C61" t="s">
+        <v>170</v>
+      </c>
+      <c r="D61" t="s">
         <v>171</v>
-      </c>
-      <c r="D61" t="s">
-        <v>172</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
@@ -3315,16 +3328,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B62" t="s">
         <v>11</v>
       </c>
       <c r="C62" t="s">
+        <v>172</v>
+      </c>
+      <c r="D62" t="s">
         <v>173</v>
-      </c>
-      <c r="D62" t="s">
-        <v>174</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
@@ -3335,16 +3348,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
       </c>
       <c r="C63" t="s">
+        <v>174</v>
+      </c>
+      <c r="D63" t="s">
         <v>175</v>
-      </c>
-      <c r="D63" t="s">
-        <v>176</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
@@ -3355,16 +3368,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B64" t="s">
         <v>17</v>
       </c>
       <c r="C64" t="s">
+        <v>176</v>
+      </c>
+      <c r="D64" t="s">
         <v>177</v>
-      </c>
-      <c r="D64" t="s">
-        <v>178</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
@@ -3375,16 +3388,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B65" t="s">
         <v>20</v>
       </c>
       <c r="C65" t="s">
+        <v>178</v>
+      </c>
+      <c r="D65" t="s">
         <v>179</v>
-      </c>
-      <c r="D65" t="s">
-        <v>180</v>
       </c>
       <c r="E65" t="s">
         <v>10</v>
@@ -3395,16 +3408,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B66" t="s">
         <v>23</v>
       </c>
       <c r="C66" t="s">
+        <v>180</v>
+      </c>
+      <c r="D66" t="s">
         <v>181</v>
-      </c>
-      <c r="D66" t="s">
-        <v>182</v>
       </c>
       <c r="E66" t="s">
         <v>10</v>
@@ -3415,16 +3428,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B67" t="s">
         <v>26</v>
       </c>
       <c r="C67" t="s">
+        <v>182</v>
+      </c>
+      <c r="D67" t="s">
         <v>183</v>
-      </c>
-      <c r="D67" t="s">
-        <v>184</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
@@ -3435,16 +3448,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B68" t="s">
         <v>29</v>
       </c>
       <c r="C68" t="s">
+        <v>184</v>
+      </c>
+      <c r="D68" t="s">
         <v>185</v>
-      </c>
-      <c r="D68" t="s">
-        <v>186</v>
       </c>
       <c r="E68" t="s">
         <v>10</v>
@@ -3455,16 +3468,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B69" t="s">
         <v>32</v>
       </c>
       <c r="C69" t="s">
+        <v>186</v>
+      </c>
+      <c r="D69" t="s">
         <v>187</v>
-      </c>
-      <c r="D69" t="s">
-        <v>188</v>
       </c>
       <c r="E69" t="s">
         <v>10</v>
@@ -3475,16 +3488,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B70" t="s">
         <v>35</v>
       </c>
       <c r="C70" t="s">
+        <v>188</v>
+      </c>
+      <c r="D70" t="s">
         <v>189</v>
-      </c>
-      <c r="D70" t="s">
-        <v>190</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
@@ -3495,16 +3508,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B71" t="s">
         <v>38</v>
       </c>
       <c r="C71" t="s">
+        <v>190</v>
+      </c>
+      <c r="D71" t="s">
         <v>191</v>
-      </c>
-      <c r="D71" t="s">
-        <v>192</v>
       </c>
       <c r="E71" t="s">
         <v>10</v>
@@ -3515,16 +3528,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B72" t="s">
         <v>41</v>
       </c>
       <c r="C72" t="s">
+        <v>192</v>
+      </c>
+      <c r="D72" t="s">
         <v>193</v>
-      </c>
-      <c r="D72" t="s">
-        <v>194</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
@@ -3535,16 +3548,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B73" t="s">
         <v>44</v>
       </c>
       <c r="C73" t="s">
+        <v>194</v>
+      </c>
+      <c r="D73" t="s">
         <v>195</v>
-      </c>
-      <c r="D73" t="s">
-        <v>196</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
@@ -3555,19 +3568,19 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B74" t="s">
         <v>47</v>
       </c>
       <c r="C74" t="s">
+        <v>196</v>
+      </c>
+      <c r="D74" t="s">
         <v>197</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>198</v>
-      </c>
-      <c r="E74" t="s">
-        <v>199</v>
       </c>
       <c r="F74" t="s">
         <v>10</v>
@@ -3575,16 +3588,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B75" t="s">
         <v>50</v>
       </c>
       <c r="C75" t="s">
+        <v>199</v>
+      </c>
+      <c r="D75" t="s">
         <v>200</v>
-      </c>
-      <c r="D75" t="s">
-        <v>201</v>
       </c>
       <c r="E75" t="s">
         <v>10</v>
@@ -3595,19 +3608,19 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B76" t="s">
         <v>53</v>
       </c>
       <c r="C76" t="s">
+        <v>201</v>
+      </c>
+      <c r="D76" t="s">
         <v>202</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>203</v>
-      </c>
-      <c r="E76" t="s">
-        <v>204</v>
       </c>
       <c r="F76" t="s">
         <v>10</v>
@@ -3615,16 +3628,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B77" t="s">
         <v>56</v>
       </c>
       <c r="C77" t="s">
+        <v>204</v>
+      </c>
+      <c r="D77" t="s">
         <v>205</v>
-      </c>
-      <c r="D77" t="s">
-        <v>206</v>
       </c>
       <c r="E77" t="s">
         <v>10</v>
@@ -3635,16 +3648,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B78" t="s">
         <v>59</v>
       </c>
       <c r="C78" t="s">
+        <v>206</v>
+      </c>
+      <c r="D78" t="s">
         <v>207</v>
-      </c>
-      <c r="D78" t="s">
-        <v>208</v>
       </c>
       <c r="E78" t="s">
         <v>10</v>
@@ -3655,16 +3668,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B79" t="s">
         <v>62</v>
       </c>
       <c r="C79" t="s">
+        <v>208</v>
+      </c>
+      <c r="D79" t="s">
         <v>209</v>
-      </c>
-      <c r="D79" t="s">
-        <v>210</v>
       </c>
       <c r="E79" t="s">
         <v>10</v>
@@ -3675,16 +3688,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B80" t="s">
         <v>65</v>
       </c>
       <c r="C80" t="s">
+        <v>210</v>
+      </c>
+      <c r="D80" t="s">
         <v>211</v>
-      </c>
-      <c r="D80" t="s">
-        <v>212</v>
       </c>
       <c r="E80" t="s">
         <v>10</v>
@@ -3695,16 +3708,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B81" t="s">
         <v>68</v>
       </c>
       <c r="C81" t="s">
+        <v>212</v>
+      </c>
+      <c r="D81" t="s">
         <v>213</v>
-      </c>
-      <c r="D81" t="s">
-        <v>214</v>
       </c>
       <c r="E81" t="s">
         <v>10</v>
@@ -3715,16 +3728,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B82" t="s">
         <v>71</v>
       </c>
       <c r="C82" t="s">
+        <v>214</v>
+      </c>
+      <c r="D82" t="s">
         <v>215</v>
-      </c>
-      <c r="D82" t="s">
-        <v>216</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
@@ -3735,16 +3748,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B83" t="s">
         <v>74</v>
       </c>
       <c r="C83" t="s">
+        <v>216</v>
+      </c>
+      <c r="D83" t="s">
         <v>217</v>
-      </c>
-      <c r="D83" t="s">
-        <v>218</v>
       </c>
       <c r="E83" t="s">
         <v>10</v>
@@ -3755,16 +3768,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B84" t="s">
         <v>77</v>
       </c>
       <c r="C84" t="s">
+        <v>218</v>
+      </c>
+      <c r="D84" t="s">
         <v>219</v>
-      </c>
-      <c r="D84" t="s">
-        <v>220</v>
       </c>
       <c r="E84" t="s">
         <v>10</v>
@@ -3775,16 +3788,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B85" t="s">
         <v>80</v>
       </c>
       <c r="C85" t="s">
+        <v>220</v>
+      </c>
+      <c r="D85" t="s">
         <v>221</v>
-      </c>
-      <c r="D85" t="s">
-        <v>222</v>
       </c>
       <c r="E85" t="s">
         <v>10</v>
@@ -3795,16 +3808,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B86" t="s">
         <v>83</v>
       </c>
       <c r="C86" t="s">
+        <v>222</v>
+      </c>
+      <c r="D86" t="s">
         <v>223</v>
-      </c>
-      <c r="D86" t="s">
-        <v>224</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
@@ -3815,16 +3828,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B87" t="s">
         <v>86</v>
       </c>
       <c r="C87" t="s">
+        <v>224</v>
+      </c>
+      <c r="D87" t="s">
         <v>225</v>
-      </c>
-      <c r="D87" t="s">
-        <v>226</v>
       </c>
       <c r="E87" t="s">
         <v>10</v>
@@ -3835,16 +3848,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B88" t="s">
         <v>89</v>
       </c>
       <c r="C88" t="s">
+        <v>226</v>
+      </c>
+      <c r="D88" t="s">
         <v>227</v>
-      </c>
-      <c r="D88" t="s">
-        <v>228</v>
       </c>
       <c r="E88" t="s">
         <v>10</v>
@@ -3855,16 +3868,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B89" t="s">
         <v>95</v>
       </c>
       <c r="C89" t="s">
+        <v>230</v>
+      </c>
+      <c r="D89" t="s">
         <v>231</v>
-      </c>
-      <c r="D89" t="s">
-        <v>232</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
@@ -3875,16 +3888,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B90" t="s">
         <v>92</v>
       </c>
       <c r="C90" t="s">
+        <v>228</v>
+      </c>
+      <c r="D90" t="s">
         <v>229</v>
-      </c>
-      <c r="D90" t="s">
-        <v>230</v>
       </c>
       <c r="E90" t="s">
         <v>10</v>
@@ -3895,16 +3908,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B91" t="s">
         <v>98</v>
       </c>
       <c r="C91" t="s">
+        <v>232</v>
+      </c>
+      <c r="D91" t="s">
         <v>233</v>
-      </c>
-      <c r="D91" t="s">
-        <v>234</v>
       </c>
       <c r="E91" t="s">
         <v>10</v>
@@ -3915,16 +3928,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B92" t="s">
         <v>101</v>
       </c>
       <c r="C92" t="s">
+        <v>234</v>
+      </c>
+      <c r="D92" t="s">
         <v>235</v>
-      </c>
-      <c r="D92" t="s">
-        <v>236</v>
       </c>
       <c r="E92" t="s">
         <v>10</v>
@@ -3935,16 +3948,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B93" t="s">
         <v>104</v>
       </c>
       <c r="C93" t="s">
+        <v>236</v>
+      </c>
+      <c r="D93" t="s">
         <v>237</v>
-      </c>
-      <c r="D93" t="s">
-        <v>238</v>
       </c>
       <c r="E93" t="s">
         <v>10</v>
@@ -3955,16 +3968,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B94" t="s">
         <v>107</v>
       </c>
       <c r="C94" t="s">
+        <v>238</v>
+      </c>
+      <c r="D94" t="s">
         <v>239</v>
-      </c>
-      <c r="D94" t="s">
-        <v>240</v>
       </c>
       <c r="E94" t="s">
         <v>10</v>
@@ -3975,16 +3988,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B95" t="s">
         <v>110</v>
       </c>
       <c r="C95" t="s">
+        <v>240</v>
+      </c>
+      <c r="D95" t="s">
         <v>241</v>
-      </c>
-      <c r="D95" t="s">
-        <v>242</v>
       </c>
       <c r="E95" t="s">
         <v>10</v>
@@ -3995,16 +4008,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B96" t="s">
         <v>113</v>
       </c>
       <c r="C96" t="s">
+        <v>242</v>
+      </c>
+      <c r="D96" t="s">
         <v>243</v>
-      </c>
-      <c r="D96" t="s">
-        <v>244</v>
       </c>
       <c r="E96" t="s">
         <v>10</v>
@@ -4015,16 +4028,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B97" t="s">
         <v>7</v>
       </c>
       <c r="C97" t="s">
+        <v>245</v>
+      </c>
+      <c r="D97" t="s">
         <v>246</v>
-      </c>
-      <c r="D97" t="s">
-        <v>247</v>
       </c>
       <c r="E97" t="s">
         <v>10</v>
@@ -4035,16 +4048,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B98" t="s">
         <v>11</v>
       </c>
       <c r="C98" t="s">
+        <v>247</v>
+      </c>
+      <c r="D98" t="s">
         <v>248</v>
-      </c>
-      <c r="D98" t="s">
-        <v>249</v>
       </c>
       <c r="E98" t="s">
         <v>10</v>
@@ -4055,16 +4068,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B99" t="s">
         <v>14</v>
       </c>
       <c r="C99" t="s">
+        <v>249</v>
+      </c>
+      <c r="D99" t="s">
         <v>250</v>
-      </c>
-      <c r="D99" t="s">
-        <v>251</v>
       </c>
       <c r="E99" t="s">
         <v>10</v>
@@ -4075,16 +4088,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B100" t="s">
         <v>17</v>
       </c>
       <c r="C100" t="s">
+        <v>251</v>
+      </c>
+      <c r="D100" t="s">
         <v>252</v>
-      </c>
-      <c r="D100" t="s">
-        <v>253</v>
       </c>
       <c r="E100" t="s">
         <v>10</v>
@@ -4095,16 +4108,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B101" t="s">
         <v>20</v>
       </c>
       <c r="C101" t="s">
+        <v>253</v>
+      </c>
+      <c r="D101" t="s">
         <v>254</v>
-      </c>
-      <c r="D101" t="s">
-        <v>255</v>
       </c>
       <c r="E101" t="s">
         <v>10</v>
@@ -4115,16 +4128,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B102" t="s">
         <v>23</v>
       </c>
       <c r="C102" t="s">
+        <v>255</v>
+      </c>
+      <c r="D102" t="s">
         <v>256</v>
-      </c>
-      <c r="D102" t="s">
-        <v>257</v>
       </c>
       <c r="E102" t="s">
         <v>10</v>
@@ -4135,16 +4148,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B103" t="s">
         <v>26</v>
       </c>
       <c r="C103" t="s">
+        <v>257</v>
+      </c>
+      <c r="D103" t="s">
         <v>258</v>
-      </c>
-      <c r="D103" t="s">
-        <v>259</v>
       </c>
       <c r="E103" t="s">
         <v>10</v>
@@ -4155,16 +4168,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B104" t="s">
         <v>29</v>
       </c>
       <c r="C104" t="s">
+        <v>259</v>
+      </c>
+      <c r="D104" t="s">
         <v>260</v>
-      </c>
-      <c r="D104" t="s">
-        <v>261</v>
       </c>
       <c r="E104" t="s">
         <v>10</v>
@@ -4175,16 +4188,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B105" t="s">
         <v>32</v>
       </c>
       <c r="C105" t="s">
+        <v>261</v>
+      </c>
+      <c r="D105" t="s">
         <v>262</v>
-      </c>
-      <c r="D105" t="s">
-        <v>263</v>
       </c>
       <c r="E105" t="s">
         <v>10</v>
@@ -4195,16 +4208,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B106" t="s">
         <v>35</v>
       </c>
       <c r="C106" t="s">
+        <v>263</v>
+      </c>
+      <c r="D106" t="s">
         <v>264</v>
-      </c>
-      <c r="D106" t="s">
-        <v>265</v>
       </c>
       <c r="E106" t="s">
         <v>10</v>
@@ -4215,16 +4228,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B107" t="s">
         <v>38</v>
       </c>
       <c r="C107" t="s">
+        <v>265</v>
+      </c>
+      <c r="D107" t="s">
         <v>266</v>
-      </c>
-      <c r="D107" t="s">
-        <v>267</v>
       </c>
       <c r="E107" t="s">
         <v>10</v>
@@ -4235,16 +4248,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B108" t="s">
         <v>41</v>
       </c>
       <c r="C108" t="s">
+        <v>267</v>
+      </c>
+      <c r="D108" t="s">
         <v>268</v>
-      </c>
-      <c r="D108" t="s">
-        <v>269</v>
       </c>
       <c r="E108" t="s">
         <v>10</v>
@@ -4255,16 +4268,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B109" t="s">
         <v>44</v>
       </c>
       <c r="C109" t="s">
+        <v>269</v>
+      </c>
+      <c r="D109" t="s">
         <v>270</v>
-      </c>
-      <c r="D109" t="s">
-        <v>271</v>
       </c>
       <c r="E109" t="s">
         <v>10</v>
@@ -4275,19 +4288,19 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B110" t="s">
         <v>47</v>
       </c>
       <c r="C110" t="s">
+        <v>271</v>
+      </c>
+      <c r="D110" t="s">
         <v>272</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>273</v>
-      </c>
-      <c r="E110" t="s">
-        <v>274</v>
       </c>
       <c r="F110" t="s">
         <v>10</v>
@@ -4295,16 +4308,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B111" s="2">
         <v>15</v>
       </c>
       <c r="C111" t="s">
+        <v>274</v>
+      </c>
+      <c r="D111" t="s">
         <v>275</v>
-      </c>
-      <c r="D111" t="s">
-        <v>276</v>
       </c>
       <c r="E111" t="s">
         <v>10</v>
@@ -4315,16 +4328,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B112" s="2">
         <v>16</v>
       </c>
       <c r="C112" t="s">
+        <v>276</v>
+      </c>
+      <c r="D112" t="s">
         <v>277</v>
-      </c>
-      <c r="D112" t="s">
-        <v>278</v>
       </c>
       <c r="E112" t="s">
         <v>10</v>
@@ -4335,16 +4348,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B113" t="s">
         <v>56</v>
       </c>
       <c r="C113" t="s">
+        <v>278</v>
+      </c>
+      <c r="D113" t="s">
         <v>279</v>
-      </c>
-      <c r="D113" t="s">
-        <v>280</v>
       </c>
       <c r="E113" t="s">
         <v>10</v>
@@ -4355,16 +4368,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B114" t="s">
         <v>59</v>
       </c>
       <c r="C114" t="s">
+        <v>280</v>
+      </c>
+      <c r="D114" t="s">
         <v>281</v>
-      </c>
-      <c r="D114" t="s">
-        <v>282</v>
       </c>
       <c r="E114" t="s">
         <v>10</v>
@@ -4375,16 +4388,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B115" t="s">
         <v>62</v>
       </c>
       <c r="C115" t="s">
+        <v>282</v>
+      </c>
+      <c r="D115" t="s">
         <v>283</v>
-      </c>
-      <c r="D115" t="s">
-        <v>284</v>
       </c>
       <c r="E115" t="s">
         <v>10</v>
@@ -4395,16 +4408,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B116" t="s">
         <v>65</v>
       </c>
       <c r="C116" t="s">
+        <v>284</v>
+      </c>
+      <c r="D116" t="s">
         <v>285</v>
-      </c>
-      <c r="D116" t="s">
-        <v>286</v>
       </c>
       <c r="E116" t="s">
         <v>10</v>
@@ -4415,16 +4428,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B117" t="s">
         <v>68</v>
       </c>
       <c r="C117" t="s">
+        <v>286</v>
+      </c>
+      <c r="D117" t="s">
         <v>287</v>
-      </c>
-      <c r="D117" t="s">
-        <v>288</v>
       </c>
       <c r="E117" t="s">
         <v>10</v>
@@ -4435,19 +4448,19 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B118" s="3">
         <v>1</v>
       </c>
       <c r="C118" t="s">
+        <v>288</v>
+      </c>
+      <c r="D118" t="s">
         <v>289</v>
       </c>
-      <c r="D118" t="s">
-        <v>290</v>
-      </c>
       <c r="E118" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F118" t="s">
         <v>10</v>
@@ -4455,19 +4468,19 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B119" s="3">
         <v>2</v>
       </c>
       <c r="C119" t="s">
+        <v>290</v>
+      </c>
+      <c r="D119" t="s">
         <v>291</v>
       </c>
-      <c r="D119" t="s">
-        <v>292</v>
-      </c>
       <c r="E119" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F119" t="s">
         <v>10</v>
@@ -4475,19 +4488,19 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B120" s="3">
         <v>3</v>
       </c>
       <c r="C120" t="s">
+        <v>292</v>
+      </c>
+      <c r="D120" t="s">
         <v>293</v>
       </c>
-      <c r="D120" t="s">
-        <v>294</v>
-      </c>
       <c r="E120" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F120" t="s">
         <v>10</v>
@@ -4495,19 +4508,19 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B121" s="3">
         <v>4</v>
       </c>
       <c r="C121" t="s">
+        <v>294</v>
+      </c>
+      <c r="D121" t="s">
         <v>295</v>
       </c>
-      <c r="D121" t="s">
-        <v>296</v>
-      </c>
       <c r="E121" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F121" t="s">
         <v>10</v>
@@ -4515,19 +4528,19 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B122" s="3">
         <v>5</v>
       </c>
       <c r="C122" t="s">
+        <v>296</v>
+      </c>
+      <c r="D122" t="s">
         <v>297</v>
       </c>
-      <c r="D122" t="s">
-        <v>298</v>
-      </c>
       <c r="E122" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F122" t="s">
         <v>10</v>
@@ -4535,19 +4548,19 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B123" s="3">
         <v>6</v>
       </c>
       <c r="C123" t="s">
+        <v>298</v>
+      </c>
+      <c r="D123" t="s">
         <v>299</v>
       </c>
-      <c r="D123" t="s">
-        <v>300</v>
-      </c>
       <c r="E123" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F123" t="s">
         <v>10</v>
@@ -4555,19 +4568,19 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B124" s="3">
         <v>7</v>
       </c>
       <c r="C124" t="s">
+        <v>300</v>
+      </c>
+      <c r="D124" t="s">
         <v>301</v>
       </c>
-      <c r="D124" t="s">
-        <v>302</v>
-      </c>
       <c r="E124" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F124" t="s">
         <v>10</v>
@@ -4575,19 +4588,19 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B125" s="3">
         <v>8</v>
       </c>
       <c r="C125" t="s">
+        <v>302</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="E125" t="s">
         <v>303</v>
-      </c>
-      <c r="D125" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="E125" t="s">
-        <v>304</v>
       </c>
       <c r="F125" t="s">
         <v>10</v>
@@ -4595,132 +4608,132 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B126" s="3">
         <v>9</v>
       </c>
       <c r="C126" t="s">
+        <v>486</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="E126" t="s">
         <v>487</v>
-      </c>
-      <c r="D126" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="E126" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B127" s="3">
         <v>10</v>
       </c>
       <c r="C127" t="s">
+        <v>488</v>
+      </c>
+      <c r="D127" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="D127" s="5" t="s">
-        <v>490</v>
-      </c>
       <c r="E127" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B128" s="3">
         <v>11</v>
       </c>
       <c r="C128" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E128" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B129" s="3">
         <v>12</v>
       </c>
       <c r="C129" t="s">
+        <v>501</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="E129" t="s">
         <v>502</v>
-      </c>
-      <c r="D129" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="E129" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B130" s="3">
         <v>13</v>
       </c>
       <c r="C130" t="s">
+        <v>505</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="E130" t="s">
         <v>506</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>508</v>
-      </c>
-      <c r="E130" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B131" s="3">
         <v>14</v>
       </c>
       <c r="C131" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B132" s="3">
         <v>15</v>
       </c>
       <c r="C132" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="E132" t="s">
         <v>499</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="E132" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B133" s="3">
         <v>1</v>
       </c>
       <c r="C133" t="s">
+        <v>305</v>
+      </c>
+      <c r="D133" t="s">
         <v>306</v>
-      </c>
-      <c r="D133" t="s">
-        <v>307</v>
       </c>
       <c r="E133" t="s">
         <v>10</v>
@@ -4731,16 +4744,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B134" s="3">
         <v>2</v>
       </c>
       <c r="C134" t="s">
+        <v>307</v>
+      </c>
+      <c r="D134" t="s">
         <v>308</v>
-      </c>
-      <c r="D134" t="s">
-        <v>309</v>
       </c>
       <c r="E134" t="s">
         <v>10</v>
@@ -4751,16 +4764,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B135" s="3">
         <v>3</v>
       </c>
       <c r="C135" t="s">
+        <v>309</v>
+      </c>
+      <c r="D135" t="s">
         <v>310</v>
-      </c>
-      <c r="D135" t="s">
-        <v>311</v>
       </c>
       <c r="E135" t="s">
         <v>10</v>
@@ -4771,16 +4784,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B136" s="3">
         <v>4</v>
       </c>
       <c r="C136" t="s">
+        <v>311</v>
+      </c>
+      <c r="D136" t="s">
         <v>312</v>
-      </c>
-      <c r="D136" t="s">
-        <v>313</v>
       </c>
       <c r="E136" t="s">
         <v>10</v>
@@ -4791,16 +4804,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B137" s="3">
         <v>5</v>
       </c>
       <c r="C137" t="s">
+        <v>313</v>
+      </c>
+      <c r="D137" t="s">
         <v>314</v>
-      </c>
-      <c r="D137" t="s">
-        <v>315</v>
       </c>
       <c r="E137" t="s">
         <v>10</v>
@@ -4811,16 +4824,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B138" s="3">
         <v>6</v>
       </c>
       <c r="C138" t="s">
+        <v>315</v>
+      </c>
+      <c r="D138" t="s">
         <v>316</v>
-      </c>
-      <c r="D138" t="s">
-        <v>317</v>
       </c>
       <c r="E138" t="s">
         <v>10</v>
@@ -4831,16 +4844,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B139" s="3">
         <v>7</v>
       </c>
       <c r="C139" t="s">
+        <v>317</v>
+      </c>
+      <c r="D139" t="s">
         <v>318</v>
-      </c>
-      <c r="D139" t="s">
-        <v>319</v>
       </c>
       <c r="E139" t="s">
         <v>10</v>
@@ -4851,16 +4864,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B140" s="3">
         <v>8</v>
       </c>
       <c r="C140" t="s">
+        <v>319</v>
+      </c>
+      <c r="D140" t="s">
         <v>320</v>
-      </c>
-      <c r="D140" t="s">
-        <v>321</v>
       </c>
       <c r="E140" t="s">
         <v>10</v>
@@ -4871,16 +4884,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B141" s="3">
         <v>9</v>
       </c>
       <c r="C141" t="s">
+        <v>321</v>
+      </c>
+      <c r="D141" t="s">
         <v>322</v>
-      </c>
-      <c r="D141" t="s">
-        <v>323</v>
       </c>
       <c r="E141" t="s">
         <v>10</v>
@@ -4891,16 +4904,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B142" s="3">
         <v>10</v>
       </c>
       <c r="C142" t="s">
+        <v>323</v>
+      </c>
+      <c r="D142" t="s">
         <v>324</v>
-      </c>
-      <c r="D142" t="s">
-        <v>325</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
@@ -4911,16 +4924,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B143" s="3">
         <v>11</v>
       </c>
       <c r="C143" t="s">
+        <v>325</v>
+      </c>
+      <c r="D143" t="s">
         <v>326</v>
-      </c>
-      <c r="D143" t="s">
-        <v>327</v>
       </c>
       <c r="E143" t="s">
         <v>10</v>
@@ -4931,16 +4944,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B144" s="4">
         <v>1</v>
       </c>
       <c r="C144" t="s">
+        <v>328</v>
+      </c>
+      <c r="D144" t="s">
         <v>329</v>
-      </c>
-      <c r="D144" t="s">
-        <v>330</v>
       </c>
       <c r="E144" t="s">
         <v>10</v>
@@ -4951,16 +4964,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B145" s="4">
         <v>2</v>
       </c>
       <c r="C145" t="s">
+        <v>330</v>
+      </c>
+      <c r="D145" t="s">
         <v>331</v>
-      </c>
-      <c r="D145" t="s">
-        <v>332</v>
       </c>
       <c r="E145" t="s">
         <v>10</v>
@@ -4971,16 +4984,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B146" s="4">
         <v>3</v>
       </c>
       <c r="C146" t="s">
+        <v>332</v>
+      </c>
+      <c r="D146" t="s">
         <v>333</v>
-      </c>
-      <c r="D146" t="s">
-        <v>334</v>
       </c>
       <c r="E146" t="s">
         <v>10</v>
@@ -4991,16 +5004,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B147" s="4">
         <v>4</v>
       </c>
       <c r="C147" t="s">
+        <v>334</v>
+      </c>
+      <c r="D147" t="s">
         <v>335</v>
-      </c>
-      <c r="D147" t="s">
-        <v>336</v>
       </c>
       <c r="E147" t="s">
         <v>10</v>
@@ -5011,16 +5024,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B148" s="4">
         <v>5</v>
       </c>
       <c r="C148" t="s">
+        <v>336</v>
+      </c>
+      <c r="D148" t="s">
         <v>337</v>
-      </c>
-      <c r="D148" t="s">
-        <v>338</v>
       </c>
       <c r="E148" t="s">
         <v>10</v>
@@ -5031,16 +5044,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B149" s="4">
         <v>6</v>
       </c>
       <c r="C149" t="s">
+        <v>338</v>
+      </c>
+      <c r="D149" t="s">
         <v>339</v>
-      </c>
-      <c r="D149" t="s">
-        <v>340</v>
       </c>
       <c r="E149" t="s">
         <v>10</v>
@@ -5051,16 +5064,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B150" s="4">
         <v>7</v>
       </c>
       <c r="C150" t="s">
+        <v>340</v>
+      </c>
+      <c r="D150" t="s">
         <v>341</v>
-      </c>
-      <c r="D150" t="s">
-        <v>342</v>
       </c>
       <c r="E150" t="s">
         <v>10</v>
@@ -5071,16 +5084,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B151" s="4">
         <v>8</v>
       </c>
       <c r="C151" t="s">
+        <v>342</v>
+      </c>
+      <c r="D151" t="s">
         <v>343</v>
-      </c>
-      <c r="D151" t="s">
-        <v>344</v>
       </c>
       <c r="E151" t="s">
         <v>10</v>
@@ -5091,16 +5104,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B152" s="4">
         <v>10</v>
       </c>
       <c r="C152" t="s">
+        <v>344</v>
+      </c>
+      <c r="D152" t="s">
         <v>345</v>
-      </c>
-      <c r="D152" t="s">
-        <v>346</v>
       </c>
       <c r="E152" t="s">
         <v>10</v>
@@ -5111,16 +5124,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B153" s="4">
         <v>11</v>
       </c>
       <c r="C153" t="s">
+        <v>346</v>
+      </c>
+      <c r="D153" t="s">
         <v>347</v>
-      </c>
-      <c r="D153" t="s">
-        <v>348</v>
       </c>
       <c r="E153" t="s">
         <v>10</v>
@@ -5131,16 +5144,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B154" s="4">
         <v>12</v>
       </c>
       <c r="C154" t="s">
+        <v>348</v>
+      </c>
+      <c r="D154" t="s">
         <v>349</v>
-      </c>
-      <c r="D154" t="s">
-        <v>350</v>
       </c>
       <c r="E154" t="s">
         <v>10</v>
@@ -5151,16 +5164,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B155" s="4">
         <v>13</v>
       </c>
       <c r="C155" t="s">
+        <v>350</v>
+      </c>
+      <c r="D155" t="s">
         <v>351</v>
-      </c>
-      <c r="D155" t="s">
-        <v>352</v>
       </c>
       <c r="E155" t="s">
         <v>10</v>
@@ -5171,16 +5184,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B156" s="4">
         <v>14</v>
       </c>
       <c r="C156" t="s">
+        <v>352</v>
+      </c>
+      <c r="D156" t="s">
         <v>353</v>
-      </c>
-      <c r="D156" t="s">
-        <v>354</v>
       </c>
       <c r="E156" t="s">
         <v>10</v>
@@ -5191,16 +5204,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B157" s="4">
         <v>15</v>
       </c>
       <c r="C157" t="s">
+        <v>354</v>
+      </c>
+      <c r="D157" t="s">
         <v>355</v>
-      </c>
-      <c r="D157" t="s">
-        <v>356</v>
       </c>
       <c r="E157" t="s">
         <v>10</v>
@@ -5211,16 +5224,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B158" s="4">
         <v>16</v>
       </c>
       <c r="C158" t="s">
+        <v>356</v>
+      </c>
+      <c r="D158" t="s">
         <v>357</v>
-      </c>
-      <c r="D158" t="s">
-        <v>358</v>
       </c>
       <c r="E158" t="s">
         <v>10</v>
@@ -5231,16 +5244,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B159" s="4">
         <v>17</v>
       </c>
       <c r="C159" t="s">
+        <v>358</v>
+      </c>
+      <c r="D159" t="s">
         <v>359</v>
-      </c>
-      <c r="D159" t="s">
-        <v>360</v>
       </c>
       <c r="E159" t="s">
         <v>10</v>
@@ -5251,16 +5264,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B160" s="4">
         <v>18</v>
       </c>
       <c r="C160" t="s">
+        <v>360</v>
+      </c>
+      <c r="D160" t="s">
         <v>361</v>
-      </c>
-      <c r="D160" t="s">
-        <v>362</v>
       </c>
       <c r="E160" t="s">
         <v>10</v>
@@ -5271,16 +5284,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B161" s="4">
         <v>19</v>
       </c>
       <c r="C161" t="s">
+        <v>362</v>
+      </c>
+      <c r="D161" t="s">
         <v>363</v>
-      </c>
-      <c r="D161" t="s">
-        <v>364</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
@@ -5291,30 +5304,30 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B162" s="2">
         <v>1</v>
       </c>
       <c r="C162" t="s">
+        <v>509</v>
+      </c>
+      <c r="D162" s="5" t="s">
         <v>510</v>
-      </c>
-      <c r="D162" s="5" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B163" s="2">
         <v>2</v>
       </c>
       <c r="C163" t="s">
+        <v>365</v>
+      </c>
+      <c r="D163" t="s">
         <v>366</v>
-      </c>
-      <c r="D163" t="s">
-        <v>367</v>
       </c>
       <c r="E163" t="s">
         <v>10</v>
@@ -5325,16 +5338,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B164" s="2">
         <v>3</v>
       </c>
       <c r="C164" t="s">
+        <v>367</v>
+      </c>
+      <c r="D164" t="s">
         <v>368</v>
-      </c>
-      <c r="D164" t="s">
-        <v>369</v>
       </c>
       <c r="E164" t="s">
         <v>10</v>
@@ -5345,16 +5358,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B165" s="2">
         <v>4</v>
       </c>
       <c r="C165" t="s">
+        <v>369</v>
+      </c>
+      <c r="D165" t="s">
         <v>370</v>
-      </c>
-      <c r="D165" t="s">
-        <v>371</v>
       </c>
       <c r="E165" t="s">
         <v>10</v>
@@ -5365,16 +5378,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B166" s="2">
         <v>5</v>
       </c>
       <c r="C166" t="s">
+        <v>371</v>
+      </c>
+      <c r="D166" t="s">
         <v>372</v>
-      </c>
-      <c r="D166" t="s">
-        <v>373</v>
       </c>
       <c r="E166" t="s">
         <v>10</v>
@@ -5385,16 +5398,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B167" s="2">
         <v>6</v>
       </c>
       <c r="C167" t="s">
+        <v>373</v>
+      </c>
+      <c r="D167" t="s">
         <v>374</v>
-      </c>
-      <c r="D167" t="s">
-        <v>375</v>
       </c>
       <c r="E167" t="s">
         <v>10</v>
@@ -5405,16 +5418,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B168" s="2">
         <v>7</v>
       </c>
       <c r="C168" t="s">
+        <v>375</v>
+      </c>
+      <c r="D168" t="s">
         <v>376</v>
-      </c>
-      <c r="D168" t="s">
-        <v>377</v>
       </c>
       <c r="E168" t="s">
         <v>10</v>
@@ -5425,16 +5438,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B169" s="2">
         <v>8</v>
       </c>
       <c r="C169" t="s">
+        <v>377</v>
+      </c>
+      <c r="D169" t="s">
         <v>378</v>
-      </c>
-      <c r="D169" t="s">
-        <v>379</v>
       </c>
       <c r="E169" t="s">
         <v>10</v>
@@ -5445,16 +5458,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B170" s="2">
         <v>9</v>
       </c>
       <c r="C170" t="s">
+        <v>379</v>
+      </c>
+      <c r="D170" t="s">
         <v>380</v>
-      </c>
-      <c r="D170" t="s">
-        <v>381</v>
       </c>
       <c r="E170" t="s">
         <v>10</v>
@@ -5465,16 +5478,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B171" s="2">
         <v>10</v>
       </c>
       <c r="C171" t="s">
+        <v>381</v>
+      </c>
+      <c r="D171" t="s">
         <v>382</v>
-      </c>
-      <c r="D171" t="s">
-        <v>383</v>
       </c>
       <c r="E171" t="s">
         <v>10</v>
@@ -5485,16 +5498,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B172" s="2">
         <v>11</v>
       </c>
       <c r="C172" t="s">
+        <v>383</v>
+      </c>
+      <c r="D172" t="s">
         <v>384</v>
-      </c>
-      <c r="D172" t="s">
-        <v>385</v>
       </c>
       <c r="E172" t="s">
         <v>10</v>
@@ -5505,16 +5518,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B173" s="2">
         <v>12</v>
       </c>
       <c r="C173" t="s">
+        <v>385</v>
+      </c>
+      <c r="D173" t="s">
         <v>386</v>
-      </c>
-      <c r="D173" t="s">
-        <v>387</v>
       </c>
       <c r="E173" t="s">
         <v>10</v>
@@ -5525,16 +5538,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B174" s="2">
         <v>13</v>
       </c>
       <c r="C174" t="s">
+        <v>387</v>
+      </c>
+      <c r="D174" t="s">
         <v>388</v>
-      </c>
-      <c r="D174" t="s">
-        <v>389</v>
       </c>
       <c r="E174" t="s">
         <v>10</v>
@@ -5545,16 +5558,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B175" s="2">
         <v>14</v>
       </c>
       <c r="C175" t="s">
+        <v>389</v>
+      </c>
+      <c r="D175" t="s">
         <v>390</v>
-      </c>
-      <c r="D175" t="s">
-        <v>391</v>
       </c>
       <c r="E175" t="s">
         <v>10</v>
@@ -5565,16 +5578,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B176" s="4">
         <v>15</v>
       </c>
       <c r="C176" t="s">
+        <v>391</v>
+      </c>
+      <c r="D176" t="s">
         <v>392</v>
-      </c>
-      <c r="D176" t="s">
-        <v>393</v>
       </c>
       <c r="E176" t="s">
         <v>10</v>
@@ -5585,19 +5598,19 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B177" t="s">
         <v>7</v>
       </c>
       <c r="C177" t="s">
+        <v>394</v>
+      </c>
+      <c r="D177" t="s">
         <v>395</v>
       </c>
-      <c r="D177" t="s">
+      <c r="E177" t="s">
         <v>396</v>
-      </c>
-      <c r="E177" t="s">
-        <v>397</v>
       </c>
       <c r="F177" t="s">
         <v>10</v>
@@ -5605,19 +5618,19 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B178" t="s">
         <v>11</v>
       </c>
       <c r="C178" t="s">
+        <v>397</v>
+      </c>
+      <c r="D178" t="s">
         <v>398</v>
       </c>
-      <c r="D178" t="s">
+      <c r="E178" t="s">
         <v>399</v>
-      </c>
-      <c r="E178" t="s">
-        <v>400</v>
       </c>
       <c r="F178" t="s">
         <v>10</v>
@@ -5625,19 +5638,19 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B179" t="s">
         <v>14</v>
       </c>
       <c r="C179" t="s">
+        <v>400</v>
+      </c>
+      <c r="D179" t="s">
         <v>401</v>
       </c>
-      <c r="D179" t="s">
+      <c r="E179" t="s">
         <v>402</v>
-      </c>
-      <c r="E179" t="s">
-        <v>403</v>
       </c>
       <c r="F179" t="s">
         <v>10</v>
@@ -5645,19 +5658,19 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B180" t="s">
         <v>17</v>
       </c>
       <c r="C180" t="s">
+        <v>403</v>
+      </c>
+      <c r="D180" t="s">
         <v>404</v>
       </c>
-      <c r="D180" t="s">
+      <c r="E180" t="s">
         <v>405</v>
-      </c>
-      <c r="E180" t="s">
-        <v>406</v>
       </c>
       <c r="F180" t="s">
         <v>10</v>
@@ -5665,19 +5678,19 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B181" t="s">
         <v>20</v>
       </c>
       <c r="C181" t="s">
+        <v>406</v>
+      </c>
+      <c r="D181" t="s">
         <v>407</v>
       </c>
-      <c r="D181" t="s">
+      <c r="E181" t="s">
         <v>408</v>
-      </c>
-      <c r="E181" t="s">
-        <v>409</v>
       </c>
       <c r="F181" t="s">
         <v>10</v>
@@ -5685,19 +5698,19 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B182" t="s">
         <v>23</v>
       </c>
       <c r="C182" t="s">
+        <v>409</v>
+      </c>
+      <c r="D182" t="s">
         <v>410</v>
       </c>
-      <c r="D182" t="s">
+      <c r="E182" t="s">
         <v>411</v>
-      </c>
-      <c r="E182" t="s">
-        <v>412</v>
       </c>
       <c r="F182" t="s">
         <v>10</v>
@@ -5705,19 +5718,19 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B183" t="s">
         <v>26</v>
       </c>
       <c r="C183" t="s">
+        <v>412</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="E183" t="s">
         <v>413</v>
-      </c>
-      <c r="D183" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="E183" t="s">
-        <v>414</v>
       </c>
       <c r="F183" t="s">
         <v>10</v>
@@ -5725,19 +5738,19 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B184" t="s">
         <v>29</v>
       </c>
       <c r="C184" t="s">
+        <v>414</v>
+      </c>
+      <c r="D184" t="s">
         <v>415</v>
       </c>
-      <c r="D184" t="s">
+      <c r="E184" t="s">
         <v>416</v>
-      </c>
-      <c r="E184" t="s">
-        <v>417</v>
       </c>
       <c r="F184" t="s">
         <v>10</v>
@@ -5745,19 +5758,19 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B185" t="s">
         <v>32</v>
       </c>
       <c r="C185" t="s">
+        <v>417</v>
+      </c>
+      <c r="D185" t="s">
         <v>418</v>
       </c>
-      <c r="D185" t="s">
+      <c r="E185" t="s">
         <v>419</v>
-      </c>
-      <c r="E185" t="s">
-        <v>420</v>
       </c>
       <c r="F185" t="s">
         <v>10</v>
@@ -5765,19 +5778,19 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B186" s="2">
         <v>10</v>
       </c>
       <c r="C186" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D186" t="s">
         <v>421</v>
       </c>
-      <c r="D186" t="s">
+      <c r="E186" t="s">
         <v>422</v>
-      </c>
-      <c r="E186" t="s">
-        <v>423</v>
       </c>
       <c r="F186" t="s">
         <v>10</v>
@@ -5785,19 +5798,19 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B187" s="2">
         <v>11</v>
       </c>
       <c r="C187" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D187" t="s">
         <v>424</v>
       </c>
-      <c r="D187" t="s">
+      <c r="E187" t="s">
         <v>425</v>
-      </c>
-      <c r="E187" t="s">
-        <v>426</v>
       </c>
       <c r="F187" t="s">
         <v>10</v>
@@ -5805,19 +5818,19 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B188" s="2">
         <v>12</v>
       </c>
       <c r="C188" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D188" t="s">
         <v>427</v>
       </c>
-      <c r="D188" t="s">
+      <c r="E188" t="s">
         <v>428</v>
-      </c>
-      <c r="E188" t="s">
-        <v>429</v>
       </c>
       <c r="F188" t="s">
         <v>10</v>
@@ -5825,19 +5838,19 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B189" s="2">
         <v>13</v>
       </c>
       <c r="C189" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D189" t="s">
         <v>430</v>
       </c>
-      <c r="D189" t="s">
+      <c r="E189" t="s">
         <v>431</v>
-      </c>
-      <c r="E189" t="s">
-        <v>432</v>
       </c>
       <c r="F189" t="s">
         <v>10</v>
@@ -5845,19 +5858,19 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B190" t="s">
         <v>35</v>
       </c>
       <c r="C190" t="s">
+        <v>432</v>
+      </c>
+      <c r="D190" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="E190" t="s">
         <v>433</v>
-      </c>
-      <c r="D190" s="5" t="s">
-        <v>512</v>
-      </c>
-      <c r="E190" t="s">
-        <v>434</v>
       </c>
       <c r="F190" t="s">
         <v>10</v>
@@ -5865,19 +5878,19 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B191" t="s">
         <v>50</v>
       </c>
       <c r="C191" t="s">
+        <v>434</v>
+      </c>
+      <c r="D191" t="s">
         <v>435</v>
       </c>
-      <c r="D191" t="s">
+      <c r="E191" t="s">
         <v>436</v>
-      </c>
-      <c r="E191" t="s">
-        <v>437</v>
       </c>
       <c r="F191" t="s">
         <v>10</v>
@@ -5885,19 +5898,19 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B192" t="s">
         <v>53</v>
       </c>
       <c r="C192" t="s">
+        <v>437</v>
+      </c>
+      <c r="D192" t="s">
         <v>438</v>
       </c>
-      <c r="D192" t="s">
+      <c r="E192" t="s">
         <v>439</v>
-      </c>
-      <c r="E192" t="s">
-        <v>440</v>
       </c>
       <c r="F192" t="s">
         <v>10</v>
@@ -5905,19 +5918,19 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B193" t="s">
         <v>56</v>
       </c>
       <c r="C193" t="s">
+        <v>440</v>
+      </c>
+      <c r="D193" t="s">
         <v>441</v>
       </c>
-      <c r="D193" t="s">
+      <c r="E193" t="s">
         <v>442</v>
-      </c>
-      <c r="E193" t="s">
-        <v>443</v>
       </c>
       <c r="F193" t="s">
         <v>10</v>
@@ -5925,19 +5938,19 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B194" t="s">
         <v>59</v>
       </c>
       <c r="C194" t="s">
+        <v>443</v>
+      </c>
+      <c r="D194" t="s">
         <v>444</v>
       </c>
-      <c r="D194" t="s">
+      <c r="E194" t="s">
         <v>445</v>
-      </c>
-      <c r="E194" t="s">
-        <v>446</v>
       </c>
       <c r="F194" t="s">
         <v>10</v>
@@ -5945,19 +5958,19 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B195" t="s">
         <v>62</v>
       </c>
       <c r="C195" t="s">
+        <v>446</v>
+      </c>
+      <c r="D195" t="s">
         <v>447</v>
       </c>
-      <c r="D195" t="s">
+      <c r="E195" t="s">
         <v>448</v>
-      </c>
-      <c r="E195" t="s">
-        <v>449</v>
       </c>
       <c r="F195" t="s">
         <v>10</v>
@@ -5965,19 +5978,19 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B196" t="s">
         <v>65</v>
       </c>
       <c r="C196" t="s">
+        <v>449</v>
+      </c>
+      <c r="D196" t="s">
         <v>450</v>
       </c>
-      <c r="D196" t="s">
+      <c r="E196" t="s">
         <v>451</v>
-      </c>
-      <c r="E196" t="s">
-        <v>452</v>
       </c>
       <c r="F196" t="s">
         <v>10</v>
@@ -5985,19 +5998,19 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B197" t="s">
         <v>68</v>
       </c>
       <c r="C197" t="s">
+        <v>452</v>
+      </c>
+      <c r="D197" t="s">
         <v>453</v>
       </c>
-      <c r="D197" t="s">
+      <c r="E197" t="s">
         <v>454</v>
-      </c>
-      <c r="E197" t="s">
-        <v>455</v>
       </c>
       <c r="F197" t="s">
         <v>10</v>
@@ -6005,19 +6018,19 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B198" t="s">
         <v>71</v>
       </c>
       <c r="C198" t="s">
+        <v>455</v>
+      </c>
+      <c r="D198" t="s">
         <v>456</v>
       </c>
-      <c r="D198" t="s">
+      <c r="E198" t="s">
         <v>457</v>
-      </c>
-      <c r="E198" t="s">
-        <v>458</v>
       </c>
       <c r="F198" t="s">
         <v>10</v>
@@ -6025,19 +6038,19 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B199" t="s">
         <v>74</v>
       </c>
       <c r="C199" t="s">
+        <v>458</v>
+      </c>
+      <c r="D199" t="s">
         <v>459</v>
       </c>
-      <c r="D199" t="s">
+      <c r="E199" t="s">
         <v>460</v>
-      </c>
-      <c r="E199" t="s">
-        <v>461</v>
       </c>
       <c r="F199" t="s">
         <v>10</v>
@@ -6045,19 +6058,19 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B200" t="s">
         <v>77</v>
       </c>
       <c r="C200" t="s">
+        <v>461</v>
+      </c>
+      <c r="D200" t="s">
         <v>462</v>
       </c>
-      <c r="D200" t="s">
+      <c r="E200" t="s">
         <v>463</v>
-      </c>
-      <c r="E200" t="s">
-        <v>464</v>
       </c>
       <c r="F200" t="s">
         <v>10</v>
@@ -6065,19 +6078,19 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B201" t="s">
         <v>80</v>
       </c>
       <c r="C201" t="s">
+        <v>464</v>
+      </c>
+      <c r="D201" t="s">
         <v>465</v>
       </c>
-      <c r="D201" t="s">
+      <c r="E201" t="s">
         <v>466</v>
-      </c>
-      <c r="E201" t="s">
-        <v>467</v>
       </c>
       <c r="F201" t="s">
         <v>10</v>
@@ -6085,19 +6098,19 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B202" t="s">
         <v>83</v>
       </c>
       <c r="C202" t="s">
+        <v>467</v>
+      </c>
+      <c r="D202" t="s">
         <v>468</v>
       </c>
-      <c r="D202" t="s">
+      <c r="E202" t="s">
         <v>469</v>
-      </c>
-      <c r="E202" t="s">
-        <v>470</v>
       </c>
       <c r="F202" t="s">
         <v>10</v>
@@ -6105,19 +6118,19 @@
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B203" t="s">
         <v>86</v>
       </c>
       <c r="C203" t="s">
+        <v>470</v>
+      </c>
+      <c r="D203" t="s">
         <v>471</v>
       </c>
-      <c r="D203" t="s">
+      <c r="E203" t="s">
         <v>472</v>
-      </c>
-      <c r="E203" t="s">
-        <v>473</v>
       </c>
       <c r="F203" t="s">
         <v>10</v>
@@ -6125,19 +6138,19 @@
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B204" t="s">
         <v>89</v>
       </c>
       <c r="C204" t="s">
+        <v>473</v>
+      </c>
+      <c r="D204" t="s">
         <v>474</v>
       </c>
-      <c r="D204" t="s">
+      <c r="E204" t="s">
         <v>475</v>
-      </c>
-      <c r="E204" t="s">
-        <v>476</v>
       </c>
       <c r="F204" t="s">
         <v>10</v>
@@ -6145,19 +6158,19 @@
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B205" t="s">
         <v>92</v>
       </c>
       <c r="C205" t="s">
+        <v>476</v>
+      </c>
+      <c r="D205" t="s">
         <v>477</v>
       </c>
-      <c r="D205" t="s">
+      <c r="E205" t="s">
         <v>478</v>
-      </c>
-      <c r="E205" t="s">
-        <v>479</v>
       </c>
       <c r="F205" t="s">
         <v>10</v>
@@ -6165,9 +6178,12 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D52" r:id="rId1" xr:uid="{05653E1F-7B16-4257-AB0C-7800B47E2144}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/journal/journal_list.xlsx
+++ b/journal/journal_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BD140E-BDB9-4705-9447-F5A4B11703E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C155514-2676-4D65-9A8C-67546DC53BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal List" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="535">
   <si>
     <t>Category</t>
   </si>
@@ -356,9 +356,6 @@
     <t>International Journal of Tourism Research</t>
   </si>
   <si>
-    <t>https://onlinelibrary.wiley.com/toc/15221970/0/0</t>
-  </si>
-  <si>
     <t>Tourism Planning and Development</t>
   </si>
   <si>
@@ -506,12 +503,6 @@
     <t>Journal of Ambient Intelligence and Humanized Computing</t>
   </si>
   <si>
-    <t>Progress in Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>Granular Computing</t>
-  </si>
-  <si>
     <t>IEEE</t>
   </si>
   <si>
@@ -848,12 +839,6 @@
     <t>https://www.tandfonline.com/action/showAxaArticles?journalCode=tjma20</t>
   </si>
   <si>
-    <t>Economic Research</t>
-  </si>
-  <si>
-    <t>https://www.tandfonline.com/action/showAxaArticles?journalCode=rero20</t>
-  </si>
-  <si>
     <t>International Journal of Information Technology &amp; Decision Making</t>
   </si>
   <si>
@@ -1317,10 +1302,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>https://journals.sagepub.com/action/doSearch?AllField=Journal+of+Marketing+Research&amp;startPage=0&amp;sortBy=FullEpubDateField</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Journal of Consumer Research</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1357,180 +1338,26 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.sciencedirect.com/search?docId=1568-4946&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0360-8352&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0305-0548&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0167-9236&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0377-2217&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0957-4174&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0165-0114&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=1566-2535&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0020-0255&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0888-613X&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0925-5273&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0950-7051&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0305-0483&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0952-1976&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=2096-2320&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=1567-4223&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0169-2070&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0378-7206&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0306-4379&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0004-3702&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0031-3203&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0167-8655&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0925-2312&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0378-4371&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0951-8320&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=1532-0464&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=2666-6510&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0893-6080&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=1474-0346&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0166-3615&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0040-1625&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0969-6989&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=1873-2887&amp;sortBy=date&amp;show=50</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Safety Science</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.sciencedirect.com/search?docId=0925-7535&amp;sortBy=date&amp;show=50</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0191-2615&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=1361-9209&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=1366-5545&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=2193-9446&amp;sortBy=date&amp;show=51</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Information Processing &amp; Management</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.sciencedirect.com/search?docId=0306-4573&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=1367-5788&amp;sortBy=date&amp;show=51</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Journal of Cleaner Production</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.sciencedirect.com/search?docId=1879-1786&amp;sortBy=date&amp;show=52</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Energy</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.sciencedirect.com/search?docId=0360-5442&amp;sortBy=date&amp;show=53</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Journal of Environmental Economics and Management</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.sciencedirect.com/search?docId=0095-0696&amp;sortBy=date&amp;show=54</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0261-5177&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0160-7383&amp;sortBy=date&amp;show=50</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=2211-9736&amp;sortBy=date&amp;show=50</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=1447-6770&amp;sortBy=date&amp;show=51</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/search?docId=0278-4319&amp;sortBy=date&amp;show=50</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>https://link.springer.com/search?facet-journal-id=10479&amp;query=*&amp;content-type=Article&amp;dateFrom=&amp;dateTo=&amp;sortBy=newestFirst</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1647,14 +1474,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>https://link.springer.com/search?facet-journal-id=13748&amp;query=*&amp;content-type=Article&amp;dateFrom=&amp;dateTo=&amp;sortBy=newestFirst</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://link.springer.com/search?facet-journal-id=41066&amp;query=*&amp;content-type=Article&amp;dateFrom=&amp;dateTo=&amp;sortBy=newestFirst</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Web|http://journal.hep.com.cn/fem/EN/article/showAsap.do</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1767,19 +1586,165 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Web|http://link.springer.com/journal/13748/articles</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Web|http://link.springer.com/journal/41066/articles</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>https://www.sciencedirect.com/search?docId=0952-1976&amp;sortBy=date&amp;show=25</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=0306-4573&amp;sortBy=date&amp;show=25</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=1474-0346&amp;sortBy=date&amp;show=25</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=0166-3615&amp;sortBy=date&amp;show=25</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=1873-2887&amp;sortBy=date&amp;show=25</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=0925-7535&amp;sortBy=date&amp;show=25</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=0040-1625&amp;sortBy=date&amp;show=25</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=0969-6989&amp;sortBy=date&amp;show=25</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=0191-2615&amp;sortBy=date&amp;show=25</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=1361-9209&amp;sortBy=date&amp;show=25</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=1366-5545&amp;sortBy=date&amp;show=25</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=0261-5177&amp;sortBy=date&amp;show=25</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=0160-7383&amp;sortBy=date&amp;show=25</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=0278-4319&amp;sortBy=date&amp;show=25</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=2211-9736&amp;sortBy=date&amp;show=25</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/applied-soft-computing/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/computers-and-industrial-engineering/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/computers-and-operations-research/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/decision-support-systems/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/european-journal-of-operational-research/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/expert-systems-with-applications/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/fuzzy-sets-and-systems/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/information-fusion/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/information-sciences/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/international-journal-of-approximate-reasoning/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/international-journal-of-production-economics/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/knowledge-based-systems/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/omega/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/journal-of-management-science-and-engineering/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/electronic-commerce-research-and-applications/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/international-journal-of-forecasting/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/information-and-management/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/information-systems/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/artificial-intelligence/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/pattern-recognition/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/pattern-recognition-letters/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/neurocomputing/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/physica-a-statistical-mechanics-and-its-applications/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/reliability-engineering-and-system-safety/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/journal-of-biomedical-informatics/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/ai-open/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/neural-networks/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/energy/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/journal-of-environmental-economics-and-management/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=1367-5788&amp;sortBy=date&amp;show=25</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=1879-1786&amp;sortBy=date&amp;show=25</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/journal/euro-journal-on-decision-processes/articles-in-press</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=1447-6770&amp;sortBy=date&amp;show=25</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/action/doSearch?field1=AllField&amp;text1=&amp;publication%5B%5D=mrja&amp;publication=&amp;Ppub=&amp;access=&amp;startPage=0&amp;sortBy=FullEpubDateField</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/15221970?af=R</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1799,6 +1764,13 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Carlito"/>
       <charset val="134"/>
     </font>
@@ -1826,13 +1798,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1855,10 +1830,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -2087,7 +2069,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="JournalListTable" displayName="JournalListTable" ref="A1:F205">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="JournalListTable" displayName="JournalListTable" ref="A1:F202">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Category"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Order"/>
@@ -2249,14 +2231,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F205"/>
+  <dimension ref="A1:F202"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="48" customWidth="1"/>
+    <col min="4" max="4" width="64.5546875" customWidth="1"/>
+    <col min="5" max="5" width="118.21875" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2273,14 +2255,14 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="28.8">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2290,17 +2272,14 @@
       <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+      <c r="D2" t="s">
+        <v>500</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="28.8">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -2310,17 +2289,14 @@
       <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
+      <c r="D3" t="s">
+        <v>501</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="28.8">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2330,17 +2306,14 @@
       <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
+      <c r="D4" t="s">
+        <v>502</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="28.8">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2350,17 +2323,14 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
+      <c r="D5" t="s">
+        <v>503</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="28.8">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -2370,17 +2340,14 @@
       <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
+      <c r="D6" t="s">
+        <v>504</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="28.8">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2390,17 +2357,14 @@
       <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
+      <c r="D7" t="s">
+        <v>505</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="28.8">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -2410,17 +2374,14 @@
       <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
+      <c r="D8" t="s">
+        <v>506</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="28.8">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -2430,17 +2391,14 @@
       <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
+      <c r="D9" t="s">
+        <v>507</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="28.8">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -2450,17 +2408,14 @@
       <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
+      <c r="D10" t="s">
+        <v>508</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="28.8">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -2470,17 +2425,14 @@
       <c r="C11" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
+      <c r="D11" t="s">
+        <v>509</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="28.8">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -2490,17 +2442,14 @@
       <c r="C12" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
+      <c r="D12" t="s">
+        <v>510</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="28.8">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -2510,17 +2459,14 @@
       <c r="C13" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
+      <c r="D13" t="s">
+        <v>511</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="28.8">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -2530,11 +2476,8 @@
       <c r="C14" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
+      <c r="D14" t="s">
+        <v>512</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
@@ -2551,16 +2494,13 @@
         <v>35</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
+        <v>485</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="28.8">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -2570,17 +2510,14 @@
       <c r="C16" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
+      <c r="D16" t="s">
+        <v>513</v>
       </c>
       <c r="F16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="28.8">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -2590,17 +2527,14 @@
       <c r="C17" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
+      <c r="D17" t="s">
+        <v>514</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="28.8">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -2610,17 +2544,14 @@
       <c r="C18" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
+      <c r="D18" t="s">
+        <v>515</v>
       </c>
       <c r="F18" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="28.8">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -2630,17 +2561,14 @@
       <c r="C19" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
+      <c r="D19" t="s">
+        <v>516</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="28.8">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -2650,17 +2578,14 @@
       <c r="C20" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
+      <c r="D20" t="s">
+        <v>517</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="28.8">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -2670,17 +2595,14 @@
       <c r="C21" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
+      <c r="D21" t="s">
+        <v>518</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="28.8">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -2690,17 +2612,14 @@
       <c r="C22" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
+      <c r="D22" t="s">
+        <v>519</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="28.8">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -2710,17 +2629,14 @@
       <c r="C23" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
+      <c r="D23" t="s">
+        <v>520</v>
       </c>
       <c r="F23" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="28.8">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -2730,17 +2646,14 @@
       <c r="C24" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
+      <c r="D24" t="s">
+        <v>521</v>
       </c>
       <c r="F24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="28.8">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -2750,17 +2663,14 @@
       <c r="C25" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
+      <c r="D25" t="s">
+        <v>522</v>
       </c>
       <c r="F25" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="28.8">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -2770,17 +2680,14 @@
       <c r="C26" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
+      <c r="D26" t="s">
+        <v>523</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="28.8">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -2790,17 +2697,14 @@
       <c r="C27" t="s">
         <v>59</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
+      <c r="D27" t="s">
+        <v>524</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="28.8">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -2810,17 +2714,14 @@
       <c r="C28" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
+      <c r="D28" t="s">
+        <v>525</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="28.8">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -2830,11 +2731,8 @@
       <c r="C29" t="s">
         <v>63</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
+      <c r="D29" t="s">
+        <v>526</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
@@ -2848,10 +2746,10 @@
         <v>64</v>
       </c>
       <c r="C30" t="s">
-        <v>468</v>
+        <v>424</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="28.8">
@@ -2865,10 +2763,7 @@
         <v>65</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>457</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
+        <v>487</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
@@ -2885,10 +2780,7 @@
         <v>67</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
+        <v>488</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
@@ -2905,10 +2797,7 @@
         <v>69</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
+        <v>489</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
@@ -2922,13 +2811,10 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>462</v>
+        <v>423</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
+        <v>490</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
@@ -2945,10 +2831,7 @@
         <v>72</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
+        <v>491</v>
       </c>
       <c r="F35" t="s">
         <v>9</v>
@@ -2965,10 +2848,7 @@
         <v>75</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
+        <v>529</v>
       </c>
       <c r="F36" t="s">
         <v>9</v>
@@ -2982,13 +2862,10 @@
         <v>76</v>
       </c>
       <c r="C37" t="s">
-        <v>471</v>
+        <v>425</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
+        <v>530</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
@@ -3002,13 +2879,10 @@
         <v>77</v>
       </c>
       <c r="C38" t="s">
-        <v>473</v>
+        <v>426</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
+        <v>527</v>
       </c>
       <c r="F38" t="s">
         <v>9</v>
@@ -3022,13 +2896,10 @@
         <v>78</v>
       </c>
       <c r="C39" t="s">
-        <v>475</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
+        <v>427</v>
+      </c>
+      <c r="D39" t="s">
+        <v>528</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
@@ -3045,10 +2916,7 @@
         <v>80</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
+        <v>492</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
@@ -3065,10 +2933,7 @@
         <v>82</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>464</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
+        <v>493</v>
       </c>
       <c r="F41" t="s">
         <v>9</v>
@@ -3085,10 +2950,7 @@
         <v>84</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
+        <v>494</v>
       </c>
       <c r="F42" t="s">
         <v>9</v>
@@ -3105,10 +2967,7 @@
         <v>86</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
+        <v>495</v>
       </c>
       <c r="F43" t="s">
         <v>9</v>
@@ -3124,11 +2983,8 @@
       <c r="C44" t="s">
         <v>88</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
+      <c r="D44" t="s">
+        <v>531</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>
@@ -3145,10 +3001,7 @@
         <v>90</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
+        <v>496</v>
       </c>
       <c r="F45" t="s">
         <v>9</v>
@@ -3165,10 +3018,7 @@
         <v>91</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
+        <v>497</v>
       </c>
       <c r="F46" t="s">
         <v>9</v>
@@ -3185,10 +3035,7 @@
         <v>96</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
+        <v>498</v>
       </c>
       <c r="F47" t="s">
         <v>9</v>
@@ -3205,10 +3052,7 @@
         <v>97</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="E48" t="s">
-        <v>9</v>
+        <v>532</v>
       </c>
       <c r="F48" t="s">
         <v>9</v>
@@ -3225,10 +3069,7 @@
         <v>105</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="E49" t="s">
-        <v>9</v>
+        <v>499</v>
       </c>
       <c r="F49" t="s">
         <v>9</v>
@@ -3282,10 +3123,10 @@
         <v>22</v>
       </c>
       <c r="C52" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" t="s">
         <v>110</v>
-      </c>
-      <c r="D52" t="s">
-        <v>111</v>
       </c>
       <c r="E52" t="s">
         <v>9</v>
@@ -3302,10 +3143,10 @@
         <v>24</v>
       </c>
       <c r="C53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D53" t="s">
         <v>112</v>
-      </c>
-      <c r="D53" t="s">
-        <v>113</v>
       </c>
       <c r="E53" t="s">
         <v>9</v>
@@ -3322,10 +3163,10 @@
         <v>26</v>
       </c>
       <c r="C54" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" t="s">
         <v>114</v>
-      </c>
-      <c r="D54" t="s">
-        <v>115</v>
       </c>
       <c r="E54" t="s">
         <v>9</v>
@@ -3365,7 +3206,7 @@
         <v>100</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="E56" t="s">
         <v>9</v>
@@ -3385,7 +3226,7 @@
         <v>106</v>
       </c>
       <c r="D57" t="s">
-        <v>107</v>
+        <v>534</v>
       </c>
       <c r="E57" t="s">
         <v>9</v>
@@ -3442,10 +3283,10 @@
         <v>38</v>
       </c>
       <c r="C60" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60" t="s">
         <v>108</v>
-      </c>
-      <c r="D60" t="s">
-        <v>109</v>
       </c>
       <c r="E60" t="s">
         <v>9</v>
@@ -3456,19 +3297,19 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B61" t="s">
         <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>482</v>
+        <v>428</v>
       </c>
       <c r="E61" t="s">
-        <v>514</v>
+        <v>458</v>
       </c>
       <c r="F61" t="s">
         <v>9</v>
@@ -3476,19 +3317,19 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B62" t="s">
         <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>483</v>
+        <v>429</v>
       </c>
       <c r="E62" t="s">
-        <v>515</v>
+        <v>459</v>
       </c>
       <c r="F62" t="s">
         <v>9</v>
@@ -3496,19 +3337,19 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>484</v>
+        <v>430</v>
       </c>
       <c r="E63" t="s">
-        <v>516</v>
+        <v>460</v>
       </c>
       <c r="F63" t="s">
         <v>9</v>
@@ -3516,19 +3357,19 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
       </c>
       <c r="C64" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>485</v>
+        <v>431</v>
       </c>
       <c r="E64" t="s">
-        <v>517</v>
+        <v>461</v>
       </c>
       <c r="F64" t="s">
         <v>9</v>
@@ -3536,19 +3377,19 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B65" t="s">
         <v>16</v>
       </c>
       <c r="C65" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>486</v>
+        <v>432</v>
       </c>
       <c r="E65" t="s">
-        <v>518</v>
+        <v>462</v>
       </c>
       <c r="F65" t="s">
         <v>9</v>
@@ -3556,19 +3397,19 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B66" t="s">
         <v>18</v>
       </c>
       <c r="C66" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>487</v>
+        <v>433</v>
       </c>
       <c r="E66" t="s">
-        <v>519</v>
+        <v>463</v>
       </c>
       <c r="F66" t="s">
         <v>9</v>
@@ -3576,19 +3417,19 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B67" t="s">
         <v>20</v>
       </c>
       <c r="C67" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>488</v>
+        <v>434</v>
       </c>
       <c r="E67" t="s">
-        <v>520</v>
+        <v>464</v>
       </c>
       <c r="F67" t="s">
         <v>9</v>
@@ -3596,19 +3437,19 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B68" t="s">
         <v>22</v>
       </c>
       <c r="C68" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>489</v>
+        <v>435</v>
       </c>
       <c r="E68" t="s">
-        <v>521</v>
+        <v>465</v>
       </c>
       <c r="F68" t="s">
         <v>9</v>
@@ -3616,19 +3457,19 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B69" t="s">
         <v>24</v>
       </c>
       <c r="C69" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>490</v>
+        <v>436</v>
       </c>
       <c r="E69" t="s">
-        <v>522</v>
+        <v>466</v>
       </c>
       <c r="F69" t="s">
         <v>9</v>
@@ -3636,19 +3477,19 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B70" t="s">
         <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>491</v>
+        <v>437</v>
       </c>
       <c r="E70" t="s">
-        <v>523</v>
+        <v>467</v>
       </c>
       <c r="F70" t="s">
         <v>9</v>
@@ -3656,19 +3497,19 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B71" t="s">
         <v>28</v>
       </c>
       <c r="C71" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>492</v>
+        <v>438</v>
       </c>
       <c r="E71" t="s">
-        <v>524</v>
+        <v>468</v>
       </c>
       <c r="F71" t="s">
         <v>9</v>
@@ -3676,19 +3517,19 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B72" t="s">
         <v>30</v>
       </c>
       <c r="C72" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>493</v>
+        <v>439</v>
       </c>
       <c r="E72" t="s">
-        <v>525</v>
+        <v>469</v>
       </c>
       <c r="F72" t="s">
         <v>9</v>
@@ -3696,19 +3537,19 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B73" t="s">
         <v>32</v>
       </c>
       <c r="C73" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>494</v>
+        <v>440</v>
       </c>
       <c r="E73" t="s">
-        <v>526</v>
+        <v>470</v>
       </c>
       <c r="F73" t="s">
         <v>9</v>
@@ -3716,19 +3557,19 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B74" t="s">
         <v>34</v>
       </c>
       <c r="C74" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>495</v>
+        <v>441</v>
       </c>
       <c r="E74" t="s">
-        <v>513</v>
+        <v>457</v>
       </c>
       <c r="F74" t="s">
         <v>9</v>
@@ -3736,19 +3577,19 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B75" t="s">
         <v>36</v>
       </c>
       <c r="C75" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>496</v>
+        <v>442</v>
       </c>
       <c r="E75" t="s">
-        <v>527</v>
+        <v>471</v>
       </c>
       <c r="F75" t="s">
         <v>9</v>
@@ -3756,19 +3597,19 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B76" t="s">
         <v>38</v>
       </c>
       <c r="C76" t="s">
+        <v>131</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="E76" t="s">
         <v>132</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="E76" t="s">
-        <v>133</v>
       </c>
       <c r="F76" t="s">
         <v>9</v>
@@ -3776,19 +3617,19 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B77" t="s">
         <v>40</v>
       </c>
       <c r="C77" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>498</v>
+        <v>444</v>
       </c>
       <c r="E77" t="s">
-        <v>528</v>
+        <v>472</v>
       </c>
       <c r="F77" t="s">
         <v>9</v>
@@ -3796,19 +3637,19 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B78" t="s">
         <v>42</v>
       </c>
       <c r="C78" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>499</v>
+        <v>445</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>529</v>
+        <v>473</v>
       </c>
       <c r="F78" t="s">
         <v>9</v>
@@ -3816,19 +3657,19 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B79" t="s">
         <v>44</v>
       </c>
       <c r="C79" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>500</v>
+        <v>446</v>
       </c>
       <c r="E79" t="s">
-        <v>530</v>
+        <v>474</v>
       </c>
       <c r="F79" t="s">
         <v>9</v>
@@ -3836,19 +3677,19 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B80" t="s">
         <v>46</v>
       </c>
       <c r="C80" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>501</v>
+        <v>447</v>
       </c>
       <c r="E80" t="s">
-        <v>531</v>
+        <v>475</v>
       </c>
       <c r="F80" t="s">
         <v>9</v>
@@ -3856,19 +3697,19 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B81" t="s">
         <v>48</v>
       </c>
       <c r="C81" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>502</v>
+        <v>448</v>
       </c>
       <c r="E81" t="s">
-        <v>532</v>
+        <v>476</v>
       </c>
       <c r="F81" t="s">
         <v>9</v>
@@ -3876,19 +3717,19 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B82" t="s">
         <v>50</v>
       </c>
       <c r="C82" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>503</v>
+        <v>449</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>533</v>
+        <v>477</v>
       </c>
       <c r="F82" t="s">
         <v>9</v>
@@ -3896,19 +3737,19 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B83" t="s">
         <v>52</v>
       </c>
       <c r="C83" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>504</v>
+        <v>450</v>
       </c>
       <c r="E83" t="s">
-        <v>534</v>
+        <v>478</v>
       </c>
       <c r="F83" t="s">
         <v>9</v>
@@ -3916,19 +3757,19 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B84" t="s">
         <v>54</v>
       </c>
       <c r="C84" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>505</v>
+        <v>451</v>
       </c>
       <c r="E84" t="s">
-        <v>535</v>
+        <v>479</v>
       </c>
       <c r="F84" t="s">
         <v>9</v>
@@ -3936,19 +3777,19 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B85" t="s">
         <v>56</v>
       </c>
       <c r="C85" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>506</v>
+        <v>452</v>
       </c>
       <c r="E85" t="s">
-        <v>536</v>
+        <v>480</v>
       </c>
       <c r="F85" t="s">
         <v>9</v>
@@ -3956,16 +3797,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B86" t="s">
         <v>58</v>
       </c>
       <c r="C86" t="s">
+        <v>142</v>
+      </c>
+      <c r="D86" t="s">
         <v>143</v>
-      </c>
-      <c r="D86" t="s">
-        <v>144</v>
       </c>
       <c r="E86" t="s">
         <v>9</v>
@@ -3976,16 +3817,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B87" t="s">
         <v>60</v>
       </c>
       <c r="C87" t="s">
+        <v>144</v>
+      </c>
+      <c r="D87" t="s">
         <v>145</v>
-      </c>
-      <c r="D87" t="s">
-        <v>146</v>
       </c>
       <c r="E87" t="s">
         <v>9</v>
@@ -3996,16 +3837,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B88" t="s">
         <v>62</v>
       </c>
       <c r="C88" t="s">
+        <v>146</v>
+      </c>
+      <c r="D88" t="s">
         <v>147</v>
-      </c>
-      <c r="D88" t="s">
-        <v>148</v>
       </c>
       <c r="E88" t="s">
         <v>9</v>
@@ -4016,16 +3857,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B89" t="s">
         <v>66</v>
       </c>
       <c r="C89" t="s">
+        <v>150</v>
+      </c>
+      <c r="D89" t="s">
         <v>151</v>
-      </c>
-      <c r="D89" t="s">
-        <v>152</v>
       </c>
       <c r="E89" t="s">
         <v>9</v>
@@ -4036,16 +3877,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B90" t="s">
         <v>64</v>
       </c>
       <c r="C90" t="s">
+        <v>148</v>
+      </c>
+      <c r="D90" t="s">
         <v>149</v>
-      </c>
-      <c r="D90" t="s">
-        <v>150</v>
       </c>
       <c r="E90" t="s">
         <v>9</v>
@@ -4056,19 +3897,19 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B91" t="s">
         <v>68</v>
       </c>
       <c r="C91" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>507</v>
+        <v>453</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>537</v>
+        <v>481</v>
       </c>
       <c r="F91" t="s">
         <v>9</v>
@@ -4076,19 +3917,19 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B92" t="s">
         <v>70</v>
       </c>
       <c r="C92" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>508</v>
+        <v>454</v>
       </c>
       <c r="E92" t="s">
-        <v>538</v>
+        <v>482</v>
       </c>
       <c r="F92" t="s">
         <v>9</v>
@@ -4096,19 +3937,19 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B93" t="s">
         <v>71</v>
       </c>
       <c r="C93" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>509</v>
+        <v>455</v>
       </c>
       <c r="E93" t="s">
-        <v>539</v>
+        <v>483</v>
       </c>
       <c r="F93" t="s">
         <v>9</v>
@@ -4116,19 +3957,19 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B94" t="s">
         <v>73</v>
       </c>
       <c r="C94" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>510</v>
+        <v>456</v>
       </c>
       <c r="E94" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
       <c r="F94" t="s">
         <v>9</v>
@@ -4136,19 +3977,19 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="B95" t="s">
-        <v>74</v>
+        <v>7</v>
       </c>
       <c r="C95" t="s">
         <v>157</v>
       </c>
-      <c r="D95" s="5" t="s">
-        <v>511</v>
+      <c r="D95" t="s">
+        <v>158</v>
       </c>
       <c r="E95" t="s">
-        <v>541</v>
+        <v>9</v>
       </c>
       <c r="F95" t="s">
         <v>9</v>
@@ -4156,19 +3997,19 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="B96" t="s">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="C96" t="s">
-        <v>158</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>512</v>
+        <v>159</v>
+      </c>
+      <c r="D96" t="s">
+        <v>160</v>
       </c>
       <c r="E96" t="s">
-        <v>542</v>
+        <v>9</v>
       </c>
       <c r="F96" t="s">
         <v>9</v>
@@ -4176,16 +4017,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B97" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C97" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D97" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E97" t="s">
         <v>9</v>
@@ -4196,16 +4037,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B98" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C98" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D98" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E98" t="s">
         <v>9</v>
@@ -4216,16 +4057,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B99" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C99" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D99" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E99" t="s">
         <v>9</v>
@@ -4236,16 +4077,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B100" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C100" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D100" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E100" t="s">
         <v>9</v>
@@ -4256,16 +4097,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B101" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C101" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D101" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E101" t="s">
         <v>9</v>
@@ -4276,16 +4117,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B102" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C102" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D102" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E102" t="s">
         <v>9</v>
@@ -4296,16 +4137,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B103" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C103" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D103" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E103" t="s">
         <v>9</v>
@@ -4316,16 +4157,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B104" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C104" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D104" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E104" t="s">
         <v>9</v>
@@ -4336,16 +4177,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B105" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C105" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D105" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E105" t="s">
         <v>9</v>
@@ -4356,16 +4197,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B106" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C106" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D106" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E106" t="s">
         <v>9</v>
@@ -4376,16 +4217,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B107" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C107" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D107" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E107" t="s">
         <v>9</v>
@@ -4396,19 +4237,19 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B108" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C108" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D108" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E108" t="s">
-        <v>9</v>
+        <v>185</v>
       </c>
       <c r="F108" t="s">
         <v>9</v>
@@ -4416,16 +4257,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>159</v>
-      </c>
-      <c r="B109" t="s">
-        <v>32</v>
+        <v>156</v>
+      </c>
+      <c r="B109" s="2">
+        <v>15</v>
       </c>
       <c r="C109" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D109" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E109" t="s">
         <v>9</v>
@@ -4436,19 +4277,19 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>159</v>
-      </c>
-      <c r="B110" t="s">
-        <v>34</v>
+        <v>156</v>
+      </c>
+      <c r="B110" s="2">
+        <v>16</v>
       </c>
       <c r="C110" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D110" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E110" t="s">
-        <v>188</v>
+        <v>9</v>
       </c>
       <c r="F110" t="s">
         <v>9</v>
@@ -4456,16 +4297,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>159</v>
-      </c>
-      <c r="B111" s="2">
-        <v>15</v>
+        <v>156</v>
+      </c>
+      <c r="B111" t="s">
+        <v>40</v>
       </c>
       <c r="C111" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D111" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E111" t="s">
         <v>9</v>
@@ -4476,16 +4317,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>159</v>
-      </c>
-      <c r="B112" s="2">
-        <v>16</v>
+        <v>156</v>
+      </c>
+      <c r="B112" t="s">
+        <v>42</v>
       </c>
       <c r="C112" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D112" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E112" t="s">
         <v>9</v>
@@ -4496,16 +4337,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B113" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C113" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D113" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E113" t="s">
         <v>9</v>
@@ -4516,16 +4357,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B114" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C114" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D114" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E114" t="s">
         <v>9</v>
@@ -4536,16 +4377,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B115" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C115" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D115" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E115" t="s">
         <v>9</v>
@@ -4556,19 +4397,19 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>159</v>
-      </c>
-      <c r="B116" t="s">
-        <v>46</v>
+        <v>407</v>
+      </c>
+      <c r="B116" s="3">
+        <v>1</v>
       </c>
       <c r="C116" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D116" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E116" t="s">
-        <v>9</v>
+        <v>389</v>
       </c>
       <c r="F116" t="s">
         <v>9</v>
@@ -4576,19 +4417,19 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>159</v>
-      </c>
-      <c r="B117" t="s">
-        <v>48</v>
+        <v>407</v>
+      </c>
+      <c r="B117" s="3">
+        <v>2</v>
       </c>
       <c r="C117" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D117" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E117" t="s">
-        <v>9</v>
+        <v>390</v>
       </c>
       <c r="F117" t="s">
         <v>9</v>
@@ -4596,19 +4437,19 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B118" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C118" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D118" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E118" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F118" t="s">
         <v>9</v>
@@ -4616,19 +4457,19 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B119" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D119" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E119" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F119" t="s">
         <v>9</v>
@@ -4636,19 +4477,19 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B120" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C120" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D120" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E120" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F120" t="s">
         <v>9</v>
@@ -4656,19 +4497,19 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B121" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C121" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D121" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E121" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="F121" t="s">
         <v>9</v>
@@ -4676,19 +4517,19 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B122" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C122" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D122" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E122" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="F122" t="s">
         <v>9</v>
@@ -4696,19 +4537,19 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B123" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C123" t="s">
-        <v>213</v>
-      </c>
-      <c r="D123" t="s">
         <v>214</v>
       </c>
+      <c r="D123" s="9" t="s">
+        <v>413</v>
+      </c>
       <c r="E123" t="s">
-        <v>397</v>
+        <v>215</v>
       </c>
       <c r="F123" t="s">
         <v>9</v>
@@ -4716,56 +4557,50 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B124" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C124" t="s">
-        <v>215</v>
-      </c>
-      <c r="D124" t="s">
-        <v>216</v>
+        <v>396</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>400</v>
       </c>
       <c r="E124" t="s">
-        <v>400</v>
-      </c>
-      <c r="F124" t="s">
-        <v>9</v>
+        <v>397</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B125" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C125" t="s">
-        <v>217</v>
+        <v>398</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="E125" t="s">
-        <v>218</v>
-      </c>
-      <c r="F125" t="s">
-        <v>9</v>
+        <v>401</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B126" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C126" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E126" t="s">
         <v>402</v>
@@ -4773,115 +4608,121 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
+        <v>407</v>
+      </c>
+      <c r="B127" s="3">
+        <v>12</v>
+      </c>
+      <c r="C127" t="s">
+        <v>411</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="E127" t="s">
         <v>412</v>
-      </c>
-      <c r="B127" s="3">
-        <v>10</v>
-      </c>
-      <c r="C127" t="s">
-        <v>403</v>
-      </c>
-      <c r="D127" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="E127" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B128" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C128" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="E128" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B129" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C129" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="E129" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B130" s="3">
-        <v>13</v>
-      </c>
-      <c r="C130" t="s">
-        <v>420</v>
+        <v>15</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>408</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="E130" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>412</v>
+        <v>216</v>
       </c>
       <c r="B131" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C131" t="s">
-        <v>408</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>411</v>
+        <v>217</v>
+      </c>
+      <c r="D131" t="s">
+        <v>218</v>
+      </c>
+      <c r="E131" t="s">
+        <v>9</v>
+      </c>
+      <c r="F131" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>412</v>
+        <v>216</v>
       </c>
       <c r="B132" s="3">
-        <v>15</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>415</v>
+        <v>2</v>
+      </c>
+      <c r="C132" t="s">
+        <v>219</v>
+      </c>
+      <c r="D132" t="s">
+        <v>220</v>
       </c>
       <c r="E132" t="s">
-        <v>414</v>
+        <v>9</v>
+      </c>
+      <c r="F132" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B133" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C133" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D133" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E133" t="s">
         <v>9</v>
@@ -4892,16 +4733,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B134" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D134" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E134" t="s">
         <v>9</v>
@@ -4912,16 +4753,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B135" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C135" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D135" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E135" t="s">
         <v>9</v>
@@ -4932,16 +4773,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B136" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C136" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D136" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E136" t="s">
         <v>9</v>
@@ -4952,16 +4793,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B137" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C137" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D137" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E137" t="s">
         <v>9</v>
@@ -4972,16 +4813,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B138" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C138" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D138" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E138" t="s">
         <v>9</v>
@@ -4992,16 +4833,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B139" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C139" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D139" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E139" t="s">
         <v>9</v>
@@ -5012,16 +4853,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B140" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C140" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D140" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E140" t="s">
         <v>9</v>
@@ -5032,16 +4873,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B141" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C141" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D141" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E141" t="s">
         <v>9</v>
@@ -5052,16 +4893,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>219</v>
-      </c>
-      <c r="B142" s="3">
-        <v>10</v>
+        <v>239</v>
+      </c>
+      <c r="B142" s="4">
+        <v>1</v>
       </c>
       <c r="C142" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D142" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E142" t="s">
         <v>9</v>
@@ -5072,16 +4913,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>219</v>
-      </c>
-      <c r="B143" s="3">
-        <v>11</v>
+        <v>239</v>
+      </c>
+      <c r="B143" s="4">
+        <v>2</v>
       </c>
       <c r="C143" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D143" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E143" t="s">
         <v>9</v>
@@ -5092,16 +4933,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B144" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C144" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D144" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E144" t="s">
         <v>9</v>
@@ -5112,16 +4953,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B145" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D145" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E145" t="s">
         <v>9</v>
@@ -5132,16 +4973,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B146" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C146" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D146" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E146" t="s">
         <v>9</v>
@@ -5152,16 +4993,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B147" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C147" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D147" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E147" t="s">
         <v>9</v>
@@ -5172,16 +5013,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B148" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C148" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D148" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E148" t="s">
         <v>9</v>
@@ -5192,16 +5033,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B149" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D149" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E149" t="s">
         <v>9</v>
@@ -5212,16 +5053,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B150" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C150" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D150" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E150" t="s">
         <v>9</v>
@@ -5232,16 +5073,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B151" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C151" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D151" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E151" t="s">
         <v>9</v>
@@ -5252,16 +5093,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B152" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D152" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E152" t="s">
         <v>9</v>
@@ -5272,16 +5113,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B153" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C153" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D153" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E153" t="s">
         <v>9</v>
@@ -5292,16 +5133,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B154" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C154" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D154" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E154" t="s">
         <v>9</v>
@@ -5312,16 +5153,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B155" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C155" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D155" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E155" t="s">
         <v>9</v>
@@ -5332,16 +5173,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B156" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C156" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D156" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E156" t="s">
         <v>9</v>
@@ -5352,16 +5193,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B157" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C157" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D157" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E157" t="s">
         <v>9</v>
@@ -5372,16 +5213,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B158" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C158" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D158" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E158" t="s">
         <v>9</v>
@@ -5392,30 +5233,24 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>242</v>
-      </c>
-      <c r="B159" s="4">
-        <v>17</v>
+        <v>417</v>
+      </c>
+      <c r="B159" s="2">
+        <v>1</v>
       </c>
       <c r="C159" t="s">
-        <v>273</v>
-      </c>
-      <c r="D159" t="s">
-        <v>274</v>
-      </c>
-      <c r="E159" t="s">
-        <v>9</v>
-      </c>
-      <c r="F159" t="s">
-        <v>9</v>
+        <v>418</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>242</v>
-      </c>
-      <c r="B160" s="4">
-        <v>18</v>
+        <v>274</v>
+      </c>
+      <c r="B160" s="2">
+        <v>2</v>
       </c>
       <c r="C160" t="s">
         <v>275</v>
@@ -5432,10 +5267,10 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>242</v>
-      </c>
-      <c r="B161" s="4">
-        <v>19</v>
+        <v>274</v>
+      </c>
+      <c r="B161" s="2">
+        <v>3</v>
       </c>
       <c r="C161" t="s">
         <v>277</v>
@@ -5452,30 +5287,36 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>423</v>
+        <v>274</v>
       </c>
       <c r="B162" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C162" t="s">
-        <v>424</v>
-      </c>
-      <c r="D162" s="5" t="s">
-        <v>425</v>
+        <v>279</v>
+      </c>
+      <c r="D162" t="s">
+        <v>280</v>
+      </c>
+      <c r="E162" t="s">
+        <v>9</v>
+      </c>
+      <c r="F162" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B163" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C163" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D163" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E163" t="s">
         <v>9</v>
@@ -5486,16 +5327,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B164" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C164" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D164" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E164" t="s">
         <v>9</v>
@@ -5506,16 +5347,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B165" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C165" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D165" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E165" t="s">
         <v>9</v>
@@ -5526,16 +5367,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B166" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D166" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E166" t="s">
         <v>9</v>
@@ -5546,16 +5387,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B167" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C167" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D167" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E167" t="s">
         <v>9</v>
@@ -5566,16 +5407,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B168" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C168" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D168" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E168" t="s">
         <v>9</v>
@@ -5586,16 +5427,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B169" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C169" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D169" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E169" t="s">
         <v>9</v>
@@ -5606,16 +5447,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B170" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C170" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D170" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E170" t="s">
         <v>9</v>
@@ -5626,16 +5467,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B171" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C171" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D171" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E171" t="s">
         <v>9</v>
@@ -5646,16 +5487,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B172" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C172" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D172" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E172" t="s">
         <v>9</v>
@@ -5666,16 +5507,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>279</v>
-      </c>
-      <c r="B173" s="2">
-        <v>12</v>
+        <v>274</v>
+      </c>
+      <c r="B173" s="4">
+        <v>15</v>
       </c>
       <c r="C173" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D173" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E173" t="s">
         <v>9</v>
@@ -5686,19 +5527,19 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>279</v>
-      </c>
-      <c r="B174" s="2">
-        <v>13</v>
+        <v>303</v>
+      </c>
+      <c r="B174" t="s">
+        <v>7</v>
       </c>
       <c r="C174" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D174" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E174" t="s">
-        <v>9</v>
+        <v>306</v>
       </c>
       <c r="F174" t="s">
         <v>9</v>
@@ -5706,19 +5547,19 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>279</v>
-      </c>
-      <c r="B175" s="2">
-        <v>14</v>
+        <v>303</v>
+      </c>
+      <c r="B175" t="s">
+        <v>10</v>
       </c>
       <c r="C175" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D175" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E175" t="s">
-        <v>9</v>
+        <v>309</v>
       </c>
       <c r="F175" t="s">
         <v>9</v>
@@ -5726,19 +5567,19 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>279</v>
-      </c>
-      <c r="B176" s="4">
-        <v>15</v>
+        <v>303</v>
+      </c>
+      <c r="B176" t="s">
+        <v>12</v>
       </c>
       <c r="C176" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D176" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E176" t="s">
-        <v>9</v>
+        <v>312</v>
       </c>
       <c r="F176" t="s">
         <v>9</v>
@@ -5746,19 +5587,19 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B177" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C177" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D177" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E177" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F177" t="s">
         <v>9</v>
@@ -5766,19 +5607,19 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B178" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C178" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D178" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E178" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F178" t="s">
         <v>9</v>
@@ -5786,19 +5627,19 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B179" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C179" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D179" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E179" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F179" t="s">
         <v>9</v>
@@ -5806,19 +5647,19 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B180" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C180" t="s">
-        <v>318</v>
-      </c>
-      <c r="D180" t="s">
-        <v>319</v>
+        <v>322</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>421</v>
       </c>
       <c r="E180" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F180" t="s">
         <v>9</v>
@@ -5826,19 +5667,19 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B181" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C181" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D181" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E181" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F181" t="s">
         <v>9</v>
@@ -5846,19 +5687,19 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B182" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C182" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D182" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E182" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F182" t="s">
         <v>9</v>
@@ -5866,19 +5707,19 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B183" t="s">
-        <v>20</v>
-      </c>
-      <c r="C183" t="s">
-        <v>327</v>
-      </c>
-      <c r="D183" s="5" t="s">
-        <v>427</v>
+        <v>26</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D183" t="s">
+        <v>337</v>
       </c>
       <c r="E183" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F183" t="s">
         <v>9</v>
@@ -5886,19 +5727,19 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B184" t="s">
-        <v>22</v>
-      </c>
-      <c r="C184" t="s">
-        <v>329</v>
+        <v>28</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>339</v>
       </c>
       <c r="D184" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="E184" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F184" t="s">
         <v>9</v>
@@ -5906,19 +5747,19 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B185" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C185" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="D185" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="E185" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="F185" t="s">
         <v>9</v>
@@ -5926,19 +5767,19 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B186" t="s">
-        <v>26</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>341</v>
+        <v>32</v>
+      </c>
+      <c r="C186" t="s">
+        <v>347</v>
       </c>
       <c r="D186" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E186" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F186" t="s">
         <v>9</v>
@@ -5946,19 +5787,19 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B187" t="s">
-        <v>28</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>344</v>
+        <v>34</v>
+      </c>
+      <c r="C187" t="s">
+        <v>350</v>
       </c>
       <c r="D187" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="E187" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="F187" t="s">
         <v>9</v>
@@ -5966,19 +5807,19 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B188" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C188" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D188" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E188" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F188" t="s">
         <v>9</v>
@@ -5986,19 +5827,19 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B189" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C189" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="D189" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="E189" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="F189" t="s">
         <v>9</v>
@@ -6006,19 +5847,19 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B190" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C190" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="D190" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="E190" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="F190" t="s">
         <v>9</v>
@@ -6026,19 +5867,19 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B191" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C191" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="D191" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="E191" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="F191" t="s">
         <v>9</v>
@@ -6046,19 +5887,19 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B192" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C192" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="D192" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="E192" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="F192" t="s">
         <v>9</v>
@@ -6066,19 +5907,19 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B193" t="s">
-        <v>40</v>
-      </c>
-      <c r="C193" t="s">
-        <v>370</v>
+        <v>46</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="D193" t="s">
-        <v>371</v>
+        <v>334</v>
       </c>
       <c r="E193" t="s">
-        <v>372</v>
+        <v>335</v>
       </c>
       <c r="F193" t="s">
         <v>9</v>
@@ -6086,19 +5927,19 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B194" t="s">
-        <v>42</v>
-      </c>
-      <c r="C194" t="s">
-        <v>373</v>
+        <v>48</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="D194" t="s">
-        <v>374</v>
+        <v>331</v>
       </c>
       <c r="E194" t="s">
-        <v>375</v>
+        <v>332</v>
       </c>
       <c r="F194" t="s">
         <v>9</v>
@@ -6106,19 +5947,19 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B195" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C195" t="s">
-        <v>361</v>
-      </c>
-      <c r="D195" t="s">
-        <v>362</v>
+        <v>342</v>
+      </c>
+      <c r="D195" s="5" t="s">
+        <v>420</v>
       </c>
       <c r="E195" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="F195" t="s">
         <v>9</v>
@@ -6126,19 +5967,19 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B196" t="s">
-        <v>46</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>338</v>
+        <v>52</v>
+      </c>
+      <c r="C196" t="s">
+        <v>359</v>
       </c>
       <c r="D196" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="E196" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="F196" t="s">
         <v>9</v>
@@ -6146,19 +5987,19 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B197" t="s">
-        <v>48</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>335</v>
+        <v>54</v>
+      </c>
+      <c r="C197" t="s">
+        <v>386</v>
       </c>
       <c r="D197" t="s">
-        <v>336</v>
+        <v>387</v>
       </c>
       <c r="E197" t="s">
-        <v>337</v>
+        <v>388</v>
       </c>
       <c r="F197" t="s">
         <v>9</v>
@@ -6166,19 +6007,19 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B198" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C198" t="s">
-        <v>347</v>
-      </c>
-      <c r="D198" s="5" t="s">
-        <v>426</v>
+        <v>371</v>
+      </c>
+      <c r="D198" t="s">
+        <v>372</v>
       </c>
       <c r="E198" t="s">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="F198" t="s">
         <v>9</v>
@@ -6186,19 +6027,19 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B199" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C199" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="D199" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="E199" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="F199" t="s">
         <v>9</v>
@@ -6206,19 +6047,19 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B200" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C200" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="D200" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="E200" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="F200" t="s">
         <v>9</v>
@@ -6226,19 +6067,19 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B201" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C201" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D201" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E201" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F201" t="s">
         <v>9</v>
@@ -6246,89 +6087,33 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B202" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C202" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D202" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E202" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F202" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6">
-      <c r="A203" t="s">
-        <v>308</v>
-      </c>
-      <c r="B203" t="s">
-        <v>60</v>
-      </c>
-      <c r="C203" t="s">
-        <v>382</v>
-      </c>
-      <c r="D203" t="s">
-        <v>383</v>
-      </c>
-      <c r="E203" t="s">
-        <v>384</v>
-      </c>
-      <c r="F203" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6">
-      <c r="A204" t="s">
-        <v>308</v>
-      </c>
-      <c r="B204" t="s">
-        <v>62</v>
-      </c>
-      <c r="C204" t="s">
-        <v>385</v>
-      </c>
-      <c r="D204" t="s">
-        <v>386</v>
-      </c>
-      <c r="E204" t="s">
-        <v>387</v>
-      </c>
-      <c r="F204" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6">
-      <c r="A205" t="s">
-        <v>308</v>
-      </c>
-      <c r="B205" t="s">
-        <v>64</v>
-      </c>
-      <c r="C205" t="s">
-        <v>388</v>
-      </c>
-      <c r="D205" t="s">
-        <v>389</v>
-      </c>
-      <c r="E205" t="s">
-        <v>390</v>
-      </c>
-      <c r="F205" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D127" r:id="rId1" xr:uid="{008428E7-DEC2-4303-9DF9-89D4D3D60D9D}"/>
+    <hyperlink ref="D123" r:id="rId2" xr:uid="{F17880A3-1ED6-4287-A26D-44EB851968C1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/journal/journal_list.xlsx
+++ b/journal/journal_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C155514-2676-4D65-9A8C-67546DC53BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4445C27-5523-4F12-B4AE-51050EC7CA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="538">
   <si>
     <t>Category</t>
   </si>
@@ -281,9 +281,6 @@
     <t>40</t>
   </si>
   <si>
-    <t>Transportation Research, Series B: Methodological</t>
-  </si>
-  <si>
     <t>41</t>
   </si>
   <si>
@@ -422,9 +419,6 @@
     <t>Artificial Intelligence Review</t>
   </si>
   <si>
-    <t>Frontiers of Engineering Management</t>
-  </si>
-  <si>
     <t>Journal of Systems Science and Systems Engineering</t>
   </si>
   <si>
@@ -1738,6 +1732,25 @@
   </si>
   <si>
     <t>https://onlinelibrary.wiley.com/journal/15221970?af=R</t>
+  </si>
+  <si>
+    <t>Transportation Research, Part B: Methodological</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transportation Research Part A: Policy and Practice</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=0965-8564&amp;sortBy=date&amp;show=25</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Engineering Management</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1807,7 +1820,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1835,6 +1848,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2069,7 +2085,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="JournalListTable" displayName="JournalListTable" ref="A1:F202">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="JournalListTable" displayName="JournalListTable" ref="A1:F203">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Category"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Order"/>
@@ -2231,12 +2247,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F202"/>
+  <dimension ref="A1:F203"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="3" max="3" width="83" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="64.5546875" customWidth="1"/>
     <col min="5" max="5" width="118.21875" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
@@ -2273,7 +2289,7 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -2290,7 +2306,7 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
@@ -2307,7 +2323,7 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -2324,7 +2340,7 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
@@ -2341,7 +2357,7 @@
         <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
@@ -2358,7 +2374,7 @@
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
@@ -2375,7 +2391,7 @@
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -2392,7 +2408,7 @@
         <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
@@ -2409,7 +2425,7 @@
         <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
@@ -2426,7 +2442,7 @@
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
@@ -2443,7 +2459,7 @@
         <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
@@ -2460,7 +2476,7 @@
         <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
@@ -2477,7 +2493,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
@@ -2494,7 +2510,7 @@
         <v>35</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
@@ -2511,7 +2527,7 @@
         <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F16" t="s">
         <v>9</v>
@@ -2528,7 +2544,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
@@ -2545,7 +2561,7 @@
         <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F18" t="s">
         <v>9</v>
@@ -2562,7 +2578,7 @@
         <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
@@ -2579,7 +2595,7 @@
         <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
@@ -2596,7 +2612,7 @@
         <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
@@ -2613,7 +2629,7 @@
         <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
@@ -2630,7 +2646,7 @@
         <v>51</v>
       </c>
       <c r="D23" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F23" t="s">
         <v>9</v>
@@ -2647,7 +2663,7 @@
         <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F24" t="s">
         <v>9</v>
@@ -2664,7 +2680,7 @@
         <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F25" t="s">
         <v>9</v>
@@ -2681,7 +2697,7 @@
         <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
@@ -2698,7 +2714,7 @@
         <v>59</v>
       </c>
       <c r="D27" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
@@ -2715,7 +2731,7 @@
         <v>61</v>
       </c>
       <c r="D28" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
@@ -2732,7 +2748,7 @@
         <v>63</v>
       </c>
       <c r="D29" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
@@ -2746,10 +2762,10 @@
         <v>64</v>
       </c>
       <c r="C30" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="28.8">
@@ -2763,7 +2779,7 @@
         <v>65</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
@@ -2780,7 +2796,7 @@
         <v>67</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
@@ -2797,7 +2813,7 @@
         <v>69</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
@@ -2811,10 +2827,10 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
@@ -2831,7 +2847,7 @@
         <v>72</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F35" t="s">
         <v>9</v>
@@ -2848,7 +2864,7 @@
         <v>75</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F36" t="s">
         <v>9</v>
@@ -2862,10 +2878,10 @@
         <v>76</v>
       </c>
       <c r="C37" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
@@ -2879,10 +2895,10 @@
         <v>77</v>
       </c>
       <c r="C38" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F38" t="s">
         <v>9</v>
@@ -2896,10 +2912,10 @@
         <v>78</v>
       </c>
       <c r="C39" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D39" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
@@ -2916,7 +2932,7 @@
         <v>80</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
@@ -2930,13 +2946,10 @@
         <v>81</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>493</v>
-      </c>
-      <c r="F41" t="s">
-        <v>9</v>
+        <v>534</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="28.8">
@@ -2944,13 +2957,13 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>533</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F42" t="s">
         <v>9</v>
@@ -2961,47 +2974,47 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F43" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" ht="28.8">
       <c r="A44" t="s">
         <v>6</v>
       </c>
       <c r="B44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" t="s">
+        <v>85</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="F44" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" t="s">
+        <v>535</v>
+      </c>
+      <c r="C45" t="s">
         <v>87</v>
       </c>
-      <c r="C44" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44" t="s">
-        <v>531</v>
-      </c>
-      <c r="F44" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="28.8">
-      <c r="A45" t="s">
-        <v>89</v>
-      </c>
-      <c r="B45" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" t="s">
-        <v>90</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>496</v>
+      <c r="D45" t="s">
+        <v>529</v>
       </c>
       <c r="F45" t="s">
         <v>9</v>
@@ -3009,33 +3022,33 @@
     </row>
     <row r="46" spans="1:6" ht="28.8">
       <c r="A46" t="s">
+        <v>88</v>
+      </c>
+      <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" t="s">
         <v>89</v>
       </c>
-      <c r="B46" t="s">
+      <c r="D46" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="F46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="28.8">
+      <c r="A47" t="s">
+        <v>88</v>
+      </c>
+      <c r="B47" t="s">
         <v>10</v>
       </c>
-      <c r="C46" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>497</v>
-      </c>
-      <c r="F46" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" t="s">
-        <v>89</v>
-      </c>
-      <c r="B47" t="s">
-        <v>12</v>
-      </c>
       <c r="C47" t="s">
-        <v>96</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>498</v>
+        <v>90</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>495</v>
       </c>
       <c r="F47" t="s">
         <v>9</v>
@@ -3043,16 +3056,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>532</v>
+        <v>496</v>
       </c>
       <c r="F48" t="s">
         <v>9</v>
@@ -3060,16 +3073,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C49" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>499</v>
+        <v>530</v>
       </c>
       <c r="F49" t="s">
         <v>9</v>
@@ -3077,19 +3090,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B50" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>92</v>
-      </c>
-      <c r="D50" t="s">
-        <v>93</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
+        <v>104</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>497</v>
       </c>
       <c r="F50" t="s">
         <v>9</v>
@@ -3097,16 +3107,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B51" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D51" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E51" t="s">
         <v>9</v>
@@ -3117,16 +3127,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B52" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C52" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="D52" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E52" t="s">
         <v>9</v>
@@ -3137,16 +3147,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D53" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E53" t="s">
         <v>9</v>
@@ -3157,16 +3167,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D54" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E54" t="s">
         <v>9</v>
@@ -3177,16 +3187,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B55" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D55" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E55" t="s">
         <v>9</v>
@@ -3197,16 +3207,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B56" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C56" t="s">
         <v>100</v>
       </c>
-      <c r="D56" s="5" t="s">
-        <v>422</v>
+      <c r="D56" t="s">
+        <v>101</v>
       </c>
       <c r="E56" t="s">
         <v>9</v>
@@ -3217,16 +3227,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C57" t="s">
-        <v>106</v>
-      </c>
-      <c r="D57" t="s">
-        <v>534</v>
+        <v>99</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>420</v>
       </c>
       <c r="E57" t="s">
         <v>9</v>
@@ -3237,16 +3247,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B58" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C58" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D58" t="s">
-        <v>99</v>
+        <v>532</v>
       </c>
       <c r="E58" t="s">
         <v>9</v>
@@ -3257,16 +3267,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B59" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D59" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E59" t="s">
         <v>9</v>
@@ -3277,16 +3287,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B60" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C60" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D60" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E60" t="s">
         <v>9</v>
@@ -3297,19 +3307,19 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="B61" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C61" t="s">
-        <v>116</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>428</v>
+        <v>106</v>
+      </c>
+      <c r="D61" t="s">
+        <v>107</v>
       </c>
       <c r="E61" t="s">
-        <v>458</v>
+        <v>9</v>
       </c>
       <c r="F61" t="s">
         <v>9</v>
@@ -3317,19 +3327,19 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
+        <v>114</v>
+      </c>
+      <c r="B62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" t="s">
         <v>115</v>
       </c>
-      <c r="B62" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" t="s">
-        <v>117</v>
-      </c>
       <c r="D62" s="5" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E62" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F62" t="s">
         <v>9</v>
@@ -3337,19 +3347,19 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E63" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F63" t="s">
         <v>9</v>
@@ -3357,19 +3367,19 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B64" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E64" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F64" t="s">
         <v>9</v>
@@ -3377,19 +3387,19 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B65" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C65" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E65" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F65" t="s">
         <v>9</v>
@@ -3397,19 +3407,19 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B66" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C66" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E66" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F66" t="s">
         <v>9</v>
@@ -3417,19 +3427,19 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B67" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C67" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E67" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F67" t="s">
         <v>9</v>
@@ -3437,19 +3447,19 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B68" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C68" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E68" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F68" t="s">
         <v>9</v>
@@ -3457,19 +3467,19 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B69" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C69" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E69" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F69" t="s">
         <v>9</v>
@@ -3477,19 +3487,19 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B70" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C70" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E70" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F70" t="s">
         <v>9</v>
@@ -3497,19 +3507,19 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B71" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E71" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F71" t="s">
         <v>9</v>
@@ -3517,19 +3527,19 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C72" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E72" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F72" t="s">
         <v>9</v>
@@ -3537,19 +3547,19 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B73" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C73" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E73" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F73" t="s">
         <v>9</v>
@@ -3557,19 +3567,19 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B74" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C74" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E74" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="F74" t="s">
         <v>9</v>
@@ -3577,19 +3587,19 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B75" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C75" t="s">
-        <v>130</v>
+        <v>537</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E75" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="F75" t="s">
         <v>9</v>
@@ -3597,19 +3607,19 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B76" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C76" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E76" t="s">
-        <v>132</v>
+        <v>469</v>
       </c>
       <c r="F76" t="s">
         <v>9</v>
@@ -3617,19 +3627,19 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B77" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C77" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E77" t="s">
-        <v>472</v>
+        <v>130</v>
       </c>
       <c r="F77" t="s">
         <v>9</v>
@@ -3637,19 +3647,19 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B78" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C78" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>473</v>
+        <v>442</v>
+      </c>
+      <c r="E78" t="s">
+        <v>470</v>
       </c>
       <c r="F78" t="s">
         <v>9</v>
@@ -3657,19 +3667,19 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B79" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C79" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="E79" t="s">
-        <v>474</v>
+        <v>443</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>471</v>
       </c>
       <c r="F79" t="s">
         <v>9</v>
@@ -3677,19 +3687,19 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B80" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C80" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E80" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F80" t="s">
         <v>9</v>
@@ -3697,19 +3707,19 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B81" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C81" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E81" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F81" t="s">
         <v>9</v>
@@ -3717,19 +3727,19 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B82" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C82" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>477</v>
+        <v>446</v>
+      </c>
+      <c r="E82" t="s">
+        <v>474</v>
       </c>
       <c r="F82" t="s">
         <v>9</v>
@@ -3737,19 +3747,19 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B83" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C83" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="E83" t="s">
-        <v>478</v>
+        <v>447</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>475</v>
       </c>
       <c r="F83" t="s">
         <v>9</v>
@@ -3757,19 +3767,19 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B84" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C84" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E84" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F84" t="s">
         <v>9</v>
@@ -3777,19 +3787,19 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B85" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C85" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E85" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F85" t="s">
         <v>9</v>
@@ -3797,19 +3807,19 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B86" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C86" t="s">
-        <v>142</v>
-      </c>
-      <c r="D86" t="s">
-        <v>143</v>
+        <v>139</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>450</v>
       </c>
       <c r="E86" t="s">
-        <v>9</v>
+        <v>478</v>
       </c>
       <c r="F86" t="s">
         <v>9</v>
@@ -3817,16 +3827,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B87" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C87" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D87" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E87" t="s">
         <v>9</v>
@@ -3837,16 +3847,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B88" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C88" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D88" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E88" t="s">
         <v>9</v>
@@ -3857,16 +3867,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B89" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C89" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D89" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E89" t="s">
         <v>9</v>
@@ -3877,10 +3887,10 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B90" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C90" t="s">
         <v>148</v>
@@ -3897,19 +3907,19 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B91" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C91" t="s">
-        <v>152</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>481</v>
+        <v>146</v>
+      </c>
+      <c r="D91" t="s">
+        <v>147</v>
+      </c>
+      <c r="E91" t="s">
+        <v>9</v>
       </c>
       <c r="F91" t="s">
         <v>9</v>
@@ -3917,19 +3927,19 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B92" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C92" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="E92" t="s">
-        <v>482</v>
+        <v>451</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>479</v>
       </c>
       <c r="F92" t="s">
         <v>9</v>
@@ -3937,19 +3947,19 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B93" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C93" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E93" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F93" t="s">
         <v>9</v>
@@ -3957,19 +3967,19 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B94" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C94" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E94" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F94" t="s">
         <v>9</v>
@@ -3977,19 +3987,19 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="B95" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="C95" t="s">
-        <v>157</v>
-      </c>
-      <c r="D95" t="s">
-        <v>158</v>
+        <v>153</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>454</v>
       </c>
       <c r="E95" t="s">
-        <v>9</v>
+        <v>482</v>
       </c>
       <c r="F95" t="s">
         <v>9</v>
@@ -3997,16 +4007,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
+        <v>154</v>
+      </c>
+      <c r="B96" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" t="s">
+        <v>155</v>
+      </c>
+      <c r="D96" t="s">
         <v>156</v>
-      </c>
-      <c r="B96" t="s">
-        <v>10</v>
-      </c>
-      <c r="C96" t="s">
-        <v>159</v>
-      </c>
-      <c r="D96" t="s">
-        <v>160</v>
       </c>
       <c r="E96" t="s">
         <v>9</v>
@@ -4017,16 +4027,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B97" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C97" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D97" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E97" t="s">
         <v>9</v>
@@ -4037,16 +4047,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B98" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C98" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D98" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E98" t="s">
         <v>9</v>
@@ -4057,16 +4067,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B99" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C99" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D99" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E99" t="s">
         <v>9</v>
@@ -4077,16 +4087,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B100" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C100" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D100" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E100" t="s">
         <v>9</v>
@@ -4097,16 +4107,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B101" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C101" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D101" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E101" t="s">
         <v>9</v>
@@ -4117,16 +4127,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B102" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C102" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D102" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E102" t="s">
         <v>9</v>
@@ -4137,16 +4147,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B103" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C103" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D103" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E103" t="s">
         <v>9</v>
@@ -4157,16 +4167,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B104" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C104" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D104" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E104" t="s">
         <v>9</v>
@@ -4177,16 +4187,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B105" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C105" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D105" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E105" t="s">
         <v>9</v>
@@ -4197,16 +4207,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B106" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C106" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D106" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E106" t="s">
         <v>9</v>
@@ -4217,16 +4227,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B107" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C107" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D107" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E107" t="s">
         <v>9</v>
@@ -4237,19 +4247,19 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B108" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C108" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D108" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E108" t="s">
-        <v>185</v>
+        <v>9</v>
       </c>
       <c r="F108" t="s">
         <v>9</v>
@@ -4257,19 +4267,19 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>156</v>
-      </c>
-      <c r="B109" s="2">
-        <v>15</v>
+        <v>154</v>
+      </c>
+      <c r="B109" t="s">
+        <v>34</v>
       </c>
       <c r="C109" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D109" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E109" t="s">
-        <v>9</v>
+        <v>183</v>
       </c>
       <c r="F109" t="s">
         <v>9</v>
@@ -4277,16 +4287,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B110" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C110" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D110" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E110" t="s">
         <v>9</v>
@@ -4297,16 +4307,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>156</v>
-      </c>
-      <c r="B111" t="s">
-        <v>40</v>
+        <v>154</v>
+      </c>
+      <c r="B111" s="2">
+        <v>16</v>
       </c>
       <c r="C111" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D111" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E111" t="s">
         <v>9</v>
@@ -4317,16 +4327,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B112" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C112" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D112" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E112" t="s">
         <v>9</v>
@@ -4337,16 +4347,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B113" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C113" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D113" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E113" t="s">
         <v>9</v>
@@ -4357,16 +4367,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B114" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C114" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D114" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E114" t="s">
         <v>9</v>
@@ -4377,16 +4387,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B115" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C115" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D115" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E115" t="s">
         <v>9</v>
@@ -4397,19 +4407,19 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>407</v>
-      </c>
-      <c r="B116" s="3">
-        <v>1</v>
+        <v>154</v>
+      </c>
+      <c r="B116" t="s">
+        <v>48</v>
       </c>
       <c r="C116" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D116" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E116" t="s">
-        <v>389</v>
+        <v>9</v>
       </c>
       <c r="F116" t="s">
         <v>9</v>
@@ -4417,19 +4427,19 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B117" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C117" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D117" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E117" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F117" t="s">
         <v>9</v>
@@ -4437,19 +4447,19 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B118" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C118" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D118" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E118" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F118" t="s">
         <v>9</v>
@@ -4457,19 +4467,19 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B119" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C119" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D119" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E119" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="F119" t="s">
         <v>9</v>
@@ -4477,19 +4487,19 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B120" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D120" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E120" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F120" t="s">
         <v>9</v>
@@ -4497,19 +4507,19 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B121" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C121" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D121" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E121" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F121" t="s">
         <v>9</v>
@@ -4517,19 +4527,19 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B122" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C122" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D122" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E122" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="F122" t="s">
         <v>9</v>
@@ -4537,19 +4547,19 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B123" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C123" t="s">
-        <v>214</v>
-      </c>
-      <c r="D123" s="9" t="s">
-        <v>413</v>
+        <v>210</v>
+      </c>
+      <c r="D123" t="s">
+        <v>211</v>
       </c>
       <c r="E123" t="s">
-        <v>215</v>
+        <v>393</v>
       </c>
       <c r="F123" t="s">
         <v>9</v>
@@ -4557,152 +4567,152 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B124" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C124" t="s">
-        <v>396</v>
-      </c>
-      <c r="D124" s="5" t="s">
-        <v>400</v>
+        <v>212</v>
+      </c>
+      <c r="D124" s="9" t="s">
+        <v>411</v>
       </c>
       <c r="E124" t="s">
-        <v>397</v>
+        <v>213</v>
+      </c>
+      <c r="F124" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B125" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C125" t="s">
+        <v>394</v>
+      </c>
+      <c r="D125" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="D125" s="5" t="s">
-        <v>399</v>
-      </c>
       <c r="E125" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B126" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C126" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="E126" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B127" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C127" t="s">
-        <v>411</v>
-      </c>
-      <c r="D127" s="9" t="s">
-        <v>533</v>
+        <v>403</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>402</v>
       </c>
       <c r="E127" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B128" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C128" t="s">
-        <v>414</v>
-      </c>
-      <c r="D128" s="5" t="s">
-        <v>416</v>
+        <v>409</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>531</v>
       </c>
       <c r="E128" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B129" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C129" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>406</v>
+        <v>414</v>
+      </c>
+      <c r="E129" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B130" s="3">
-        <v>15</v>
-      </c>
-      <c r="C130" s="6" t="s">
-        <v>408</v>
+        <v>14</v>
+      </c>
+      <c r="C130" t="s">
+        <v>401</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="E130" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>216</v>
+        <v>405</v>
       </c>
       <c r="B131" s="3">
-        <v>1</v>
-      </c>
-      <c r="C131" t="s">
-        <v>217</v>
-      </c>
-      <c r="D131" t="s">
-        <v>218</v>
+        <v>15</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>408</v>
       </c>
       <c r="E131" t="s">
-        <v>9</v>
-      </c>
-      <c r="F131" t="s">
-        <v>9</v>
+        <v>407</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
+        <v>214</v>
+      </c>
+      <c r="B132" s="3">
+        <v>1</v>
+      </c>
+      <c r="C132" t="s">
+        <v>215</v>
+      </c>
+      <c r="D132" t="s">
         <v>216</v>
-      </c>
-      <c r="B132" s="3">
-        <v>2</v>
-      </c>
-      <c r="C132" t="s">
-        <v>219</v>
-      </c>
-      <c r="D132" t="s">
-        <v>220</v>
       </c>
       <c r="E132" t="s">
         <v>9</v>
@@ -4713,16 +4723,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B133" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C133" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D133" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E133" t="s">
         <v>9</v>
@@ -4733,16 +4743,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B134" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C134" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D134" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E134" t="s">
         <v>9</v>
@@ -4753,16 +4763,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B135" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D135" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E135" t="s">
         <v>9</v>
@@ -4773,16 +4783,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B136" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C136" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D136" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E136" t="s">
         <v>9</v>
@@ -4793,16 +4803,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B137" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C137" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D137" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E137" t="s">
         <v>9</v>
@@ -4813,16 +4823,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B138" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C138" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D138" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E138" t="s">
         <v>9</v>
@@ -4833,16 +4843,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B139" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C139" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D139" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E139" t="s">
         <v>9</v>
@@ -4853,16 +4863,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B140" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C140" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D140" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E140" t="s">
         <v>9</v>
@@ -4873,16 +4883,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B141" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C141" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D141" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E141" t="s">
         <v>9</v>
@@ -4893,16 +4903,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>239</v>
-      </c>
-      <c r="B142" s="4">
-        <v>1</v>
+        <v>214</v>
+      </c>
+      <c r="B142" s="3">
+        <v>11</v>
       </c>
       <c r="C142" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D142" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E142" t="s">
         <v>9</v>
@@ -4913,16 +4923,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
+        <v>237</v>
+      </c>
+      <c r="B143" s="4">
+        <v>1</v>
+      </c>
+      <c r="C143" t="s">
+        <v>238</v>
+      </c>
+      <c r="D143" t="s">
         <v>239</v>
-      </c>
-      <c r="B143" s="4">
-        <v>2</v>
-      </c>
-      <c r="C143" t="s">
-        <v>242</v>
-      </c>
-      <c r="D143" t="s">
-        <v>243</v>
       </c>
       <c r="E143" t="s">
         <v>9</v>
@@ -4933,16 +4943,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B144" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C144" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D144" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E144" t="s">
         <v>9</v>
@@ -4953,16 +4963,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B145" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C145" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D145" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E145" t="s">
         <v>9</v>
@@ -4973,16 +4983,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B146" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C146" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D146" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E146" t="s">
         <v>9</v>
@@ -4993,16 +5003,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B147" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C147" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D147" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E147" t="s">
         <v>9</v>
@@ -5013,16 +5023,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B148" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C148" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D148" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E148" t="s">
         <v>9</v>
@@ -5033,16 +5043,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B149" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C149" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D149" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E149" t="s">
         <v>9</v>
@@ -5053,16 +5063,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B150" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D150" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E150" t="s">
         <v>9</v>
@@ -5073,16 +5083,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B151" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C151" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D151" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E151" t="s">
         <v>9</v>
@@ -5093,16 +5103,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B152" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C152" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D152" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E152" t="s">
         <v>9</v>
@@ -5113,16 +5123,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B153" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C153" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D153" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E153" t="s">
         <v>9</v>
@@ -5133,16 +5143,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B154" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C154" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E154" t="s">
         <v>9</v>
@@ -5153,16 +5163,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B155" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C155" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D155" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E155" t="s">
         <v>9</v>
@@ -5173,16 +5183,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B156" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C156" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D156" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E156" t="s">
         <v>9</v>
@@ -5193,16 +5203,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B157" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C157" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D157" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E157" t="s">
         <v>9</v>
@@ -5213,16 +5223,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B158" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C158" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D158" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E158" t="s">
         <v>9</v>
@@ -5233,50 +5243,50 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>417</v>
-      </c>
-      <c r="B159" s="2">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="B159" s="4">
+        <v>18</v>
       </c>
       <c r="C159" t="s">
-        <v>418</v>
-      </c>
-      <c r="D159" s="5" t="s">
-        <v>419</v>
+        <v>270</v>
+      </c>
+      <c r="D159" t="s">
+        <v>271</v>
+      </c>
+      <c r="E159" t="s">
+        <v>9</v>
+      </c>
+      <c r="F159" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>274</v>
+        <v>415</v>
       </c>
       <c r="B160" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C160" t="s">
-        <v>275</v>
-      </c>
-      <c r="D160" t="s">
-        <v>276</v>
-      </c>
-      <c r="E160" t="s">
-        <v>9</v>
-      </c>
-      <c r="F160" t="s">
-        <v>9</v>
+        <v>416</v>
+      </c>
+      <c r="D160" s="5" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
+        <v>272</v>
+      </c>
+      <c r="B161" s="2">
+        <v>2</v>
+      </c>
+      <c r="C161" t="s">
+        <v>273</v>
+      </c>
+      <c r="D161" t="s">
         <v>274</v>
-      </c>
-      <c r="B161" s="2">
-        <v>3</v>
-      </c>
-      <c r="C161" t="s">
-        <v>277</v>
-      </c>
-      <c r="D161" t="s">
-        <v>278</v>
       </c>
       <c r="E161" t="s">
         <v>9</v>
@@ -5287,16 +5297,16 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B162" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C162" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D162" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E162" t="s">
         <v>9</v>
@@ -5307,16 +5317,16 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B163" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C163" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D163" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E163" t="s">
         <v>9</v>
@@ -5327,16 +5337,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B164" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C164" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D164" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E164" t="s">
         <v>9</v>
@@ -5347,16 +5357,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B165" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C165" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D165" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E165" t="s">
         <v>9</v>
@@ -5367,16 +5377,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B166" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C166" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D166" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E166" t="s">
         <v>9</v>
@@ -5387,16 +5397,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B167" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D167" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E167" t="s">
         <v>9</v>
@@ -5407,16 +5417,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B168" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C168" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D168" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E168" t="s">
         <v>9</v>
@@ -5427,16 +5437,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B169" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C169" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D169" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E169" t="s">
         <v>9</v>
@@ -5447,16 +5457,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B170" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C170" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D170" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E170" t="s">
         <v>9</v>
@@ -5467,16 +5477,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B171" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C171" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D171" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E171" t="s">
         <v>9</v>
@@ -5487,16 +5497,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B172" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C172" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D172" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E172" t="s">
         <v>9</v>
@@ -5507,16 +5517,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>274</v>
-      </c>
-      <c r="B173" s="4">
-        <v>15</v>
+        <v>272</v>
+      </c>
+      <c r="B173" s="2">
+        <v>14</v>
       </c>
       <c r="C173" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D173" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E173" t="s">
         <v>9</v>
@@ -5527,19 +5537,19 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>303</v>
-      </c>
-      <c r="B174" t="s">
-        <v>7</v>
+        <v>272</v>
+      </c>
+      <c r="B174" s="4">
+        <v>15</v>
       </c>
       <c r="C174" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="D174" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="E174" t="s">
-        <v>306</v>
+        <v>9</v>
       </c>
       <c r="F174" t="s">
         <v>9</v>
@@ -5547,19 +5557,19 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
+        <v>301</v>
+      </c>
+      <c r="B175" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175" t="s">
+        <v>302</v>
+      </c>
+      <c r="D175" t="s">
         <v>303</v>
       </c>
-      <c r="B175" t="s">
-        <v>10</v>
-      </c>
-      <c r="C175" t="s">
-        <v>307</v>
-      </c>
-      <c r="D175" t="s">
-        <v>308</v>
-      </c>
       <c r="E175" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="F175" t="s">
         <v>9</v>
@@ -5567,19 +5577,19 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B176" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C176" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D176" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="E176" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="F176" t="s">
         <v>9</v>
@@ -5587,19 +5597,19 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B177" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C177" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D177" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E177" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="F177" t="s">
         <v>9</v>
@@ -5607,19 +5617,19 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B178" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C178" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D178" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E178" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="F178" t="s">
         <v>9</v>
@@ -5627,19 +5637,19 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B179" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C179" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D179" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E179" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="F179" t="s">
         <v>9</v>
@@ -5647,19 +5657,19 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B180" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C180" t="s">
-        <v>322</v>
-      </c>
-      <c r="D180" s="5" t="s">
-        <v>421</v>
+        <v>317</v>
+      </c>
+      <c r="D180" t="s">
+        <v>318</v>
       </c>
       <c r="E180" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F180" t="s">
         <v>9</v>
@@ -5667,19 +5677,19 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B181" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C181" t="s">
-        <v>324</v>
-      </c>
-      <c r="D181" t="s">
-        <v>325</v>
+        <v>320</v>
+      </c>
+      <c r="D181" s="5" t="s">
+        <v>419</v>
       </c>
       <c r="E181" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="F181" t="s">
         <v>9</v>
@@ -5687,19 +5697,19 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B182" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C182" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D182" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E182" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="F182" t="s">
         <v>9</v>
@@ -5707,19 +5717,19 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B183" t="s">
-        <v>26</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>336</v>
+        <v>24</v>
+      </c>
+      <c r="C183" t="s">
+        <v>325</v>
       </c>
       <c r="D183" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="E183" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="F183" t="s">
         <v>9</v>
@@ -5727,19 +5737,19 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B184" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="D184" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="E184" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="F184" t="s">
         <v>9</v>
@@ -5747,19 +5757,19 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B185" t="s">
-        <v>30</v>
-      </c>
-      <c r="C185" t="s">
-        <v>344</v>
+        <v>28</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="D185" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="E185" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F185" t="s">
         <v>9</v>
@@ -5767,19 +5777,19 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B186" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C186" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D186" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E186" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="F186" t="s">
         <v>9</v>
@@ -5787,19 +5797,19 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B187" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C187" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D187" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="E187" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="F187" t="s">
         <v>9</v>
@@ -5807,19 +5817,19 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B188" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C188" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D188" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="E188" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="F188" t="s">
         <v>9</v>
@@ -5827,19 +5837,19 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B189" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C189" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="D189" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="E189" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="F189" t="s">
         <v>9</v>
@@ -5847,19 +5857,19 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B190" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C190" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D190" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="E190" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F190" t="s">
         <v>9</v>
@@ -5867,19 +5877,19 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B191" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C191" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="D191" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E191" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="F191" t="s">
         <v>9</v>
@@ -5887,19 +5897,19 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B192" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C192" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="D192" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="E192" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="F192" t="s">
         <v>9</v>
@@ -5907,19 +5917,19 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B193" t="s">
-        <v>46</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>333</v>
+        <v>44</v>
+      </c>
+      <c r="C193" t="s">
+        <v>354</v>
       </c>
       <c r="D193" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="E193" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="F193" t="s">
         <v>9</v>
@@ -5927,19 +5937,19 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B194" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D194" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E194" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F194" t="s">
         <v>9</v>
@@ -5947,19 +5957,19 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B195" t="s">
-        <v>50</v>
-      </c>
-      <c r="C195" t="s">
-        <v>342</v>
-      </c>
-      <c r="D195" s="5" t="s">
-        <v>420</v>
+        <v>48</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D195" t="s">
+        <v>329</v>
       </c>
       <c r="E195" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="F195" t="s">
         <v>9</v>
@@ -5967,19 +5977,19 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B196" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C196" t="s">
-        <v>359</v>
-      </c>
-      <c r="D196" t="s">
-        <v>360</v>
+        <v>340</v>
+      </c>
+      <c r="D196" s="5" t="s">
+        <v>418</v>
       </c>
       <c r="E196" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="F196" t="s">
         <v>9</v>
@@ -5987,19 +5997,19 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B197" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C197" t="s">
-        <v>386</v>
+        <v>357</v>
       </c>
       <c r="D197" t="s">
-        <v>387</v>
+        <v>358</v>
       </c>
       <c r="E197" t="s">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="F197" t="s">
         <v>9</v>
@@ -6007,19 +6017,19 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B198" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C198" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="D198" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="E198" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="F198" t="s">
         <v>9</v>
@@ -6027,19 +6037,19 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B199" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C199" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="D199" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E199" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="F199" t="s">
         <v>9</v>
@@ -6047,19 +6057,19 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B200" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C200" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="D200" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="E200" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="F200" t="s">
         <v>9</v>
@@ -6067,19 +6077,19 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B201" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C201" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D201" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E201" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="F201" t="s">
         <v>9</v>
@@ -6087,33 +6097,54 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B202" t="s">
+        <v>62</v>
+      </c>
+      <c r="C202" t="s">
+        <v>378</v>
+      </c>
+      <c r="D202" t="s">
+        <v>379</v>
+      </c>
+      <c r="E202" t="s">
+        <v>380</v>
+      </c>
+      <c r="F202" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" t="s">
+        <v>301</v>
+      </c>
+      <c r="B203" t="s">
         <v>64</v>
       </c>
-      <c r="C202" t="s">
+      <c r="C203" t="s">
+        <v>381</v>
+      </c>
+      <c r="D203" t="s">
+        <v>382</v>
+      </c>
+      <c r="E203" t="s">
         <v>383</v>
       </c>
-      <c r="D202" t="s">
-        <v>384</v>
-      </c>
-      <c r="E202" t="s">
-        <v>385</v>
-      </c>
-      <c r="F202" t="s">
+      <c r="F203" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D127" r:id="rId1" xr:uid="{008428E7-DEC2-4303-9DF9-89D4D3D60D9D}"/>
-    <hyperlink ref="D123" r:id="rId2" xr:uid="{F17880A3-1ED6-4287-A26D-44EB851968C1}"/>
+    <hyperlink ref="D128" r:id="rId1" xr:uid="{008428E7-DEC2-4303-9DF9-89D4D3D60D9D}"/>
+    <hyperlink ref="D124" r:id="rId2" xr:uid="{F17880A3-1ED6-4287-A26D-44EB851968C1}"/>
+    <hyperlink ref="D41" r:id="rId3" xr:uid="{D34990F5-47F9-4314-A0A9-A886A5DDCD73}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>